--- a/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.5.認証・認可.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.5.認証・認可.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2BE662F-744A-4A4B-8583-11AC3595D993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFF0B48-F7E1-4237-818A-F0C242FAFBE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1155" yWindow="-120" windowWidth="27765" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="7.5.認証・認可" sheetId="4" r:id="rId1"/>
@@ -1556,10 +1556,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>https://nablarch.github.io/docs/5u21/doc/application_framework/application_framework/libraries/permission_check.html</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>Nablarchの認可チェックの詳細に関しては、下記Nablarchガイドの【7.15. 認可チェック】を参照のこと。</t>
     <rPh sb="9" eb="11">
       <t>ニンカ</t>
@@ -1939,6 +1935,10 @@
     <rPh sb="43" eb="45">
       <t>セイギョ</t>
     </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/libraries/permission_check.html</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1949,7 +1949,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2009,6 +2009,14 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color theme="10"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
       <color theme="10"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -2336,9 +2344,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2351,185 +2356,188 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3169,9 +3177,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3209,9 +3217,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3244,26 +3252,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3296,26 +3287,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3493,144 +3467,144 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AI771"/>
-  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="3.6328125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="3.625" style="4"/>
+    <col min="1" max="16384" width="3.6328125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="85"/>
-      <c r="J1" s="85"/>
-      <c r="K1" s="85"/>
-      <c r="L1" s="85"/>
-      <c r="M1" s="85"/>
-      <c r="N1" s="85"/>
-      <c r="O1" s="86"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="50"/>
       <c r="P1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q1" s="2"/>
-      <c r="R1" s="87" t="s">
+      <c r="R1" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="S1" s="88"/>
-      <c r="T1" s="88"/>
-      <c r="U1" s="88"/>
-      <c r="V1" s="88"/>
-      <c r="W1" s="88"/>
-      <c r="X1" s="89"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="52"/>
+      <c r="V1" s="52"/>
+      <c r="W1" s="52"/>
+      <c r="X1" s="53"/>
       <c r="Y1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="90"/>
-      <c r="AB1" s="91"/>
-      <c r="AC1" s="91"/>
-      <c r="AD1" s="91"/>
-      <c r="AE1" s="92"/>
-      <c r="AF1" s="81"/>
-      <c r="AG1" s="82"/>
-      <c r="AH1" s="82"/>
-      <c r="AI1" s="83"/>
-    </row>
-    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AA1" s="54"/>
+      <c r="AB1" s="55"/>
+      <c r="AC1" s="55"/>
+      <c r="AD1" s="55"/>
+      <c r="AE1" s="56"/>
+      <c r="AF1" s="45"/>
+      <c r="AG1" s="46"/>
+      <c r="AH1" s="46"/>
+      <c r="AI1" s="47"/>
+    </row>
+    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="7"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="94"/>
-      <c r="M2" s="94"/>
-      <c r="N2" s="94"/>
-      <c r="O2" s="95"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="58"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="59"/>
       <c r="P2" s="8" t="s">
         <v>4</v>
       </c>
       <c r="Q2" s="9"/>
-      <c r="R2" s="96" t="s">
+      <c r="R2" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="S2" s="97"/>
-      <c r="T2" s="97"/>
-      <c r="U2" s="97"/>
-      <c r="V2" s="97"/>
-      <c r="W2" s="97"/>
-      <c r="X2" s="98"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="61"/>
+      <c r="W2" s="61"/>
+      <c r="X2" s="62"/>
       <c r="Y2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="90"/>
-      <c r="AB2" s="91"/>
-      <c r="AC2" s="91"/>
-      <c r="AD2" s="91"/>
-      <c r="AE2" s="92"/>
-      <c r="AF2" s="81"/>
-      <c r="AG2" s="82"/>
-      <c r="AH2" s="82"/>
-      <c r="AI2" s="83"/>
-    </row>
-    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AA2" s="54"/>
+      <c r="AB2" s="55"/>
+      <c r="AC2" s="55"/>
+      <c r="AD2" s="55"/>
+      <c r="AE2" s="56"/>
+      <c r="AF2" s="45"/>
+      <c r="AG2" s="46"/>
+      <c r="AH2" s="46"/>
+      <c r="AI2" s="47"/>
+    </row>
+    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="11"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="102"/>
-      <c r="O3" s="102"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
       <c r="P3" s="12"/>
       <c r="Q3" s="13"/>
-      <c r="R3" s="99"/>
-      <c r="S3" s="100"/>
-      <c r="T3" s="100"/>
-      <c r="U3" s="100"/>
-      <c r="V3" s="100"/>
-      <c r="W3" s="100"/>
-      <c r="X3" s="101"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="64"/>
+      <c r="W3" s="64"/>
+      <c r="X3" s="65"/>
       <c r="Y3" s="12" t="s">
         <v>8</v>
       </c>
       <c r="Z3" s="14"/>
-      <c r="AA3" s="90"/>
-      <c r="AB3" s="91"/>
-      <c r="AC3" s="91"/>
-      <c r="AD3" s="91"/>
-      <c r="AE3" s="92"/>
-      <c r="AF3" s="81"/>
-      <c r="AG3" s="82"/>
-      <c r="AH3" s="82"/>
-      <c r="AI3" s="83"/>
-    </row>
-    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AA3" s="54"/>
+      <c r="AB3" s="55"/>
+      <c r="AC3" s="55"/>
+      <c r="AD3" s="55"/>
+      <c r="AE3" s="56"/>
+      <c r="AF3" s="45"/>
+      <c r="AG3" s="46"/>
+      <c r="AH3" s="46"/>
+      <c r="AI3" s="47"/>
+    </row>
+    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="15" t="s">
         <v>13</v>
       </c>
@@ -3638,8 +3612,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="15" t="str">
         <f>$B$5&amp;"5."</f>
         <v>7.5.</v>
@@ -3648,8 +3622,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D9" s="15" t="str">
         <f>$C$7&amp;"1."</f>
         <v>7.5.1.</v>
@@ -3658,7 +3632,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D10" s="15"/>
       <c r="E10" s="15" t="str">
         <f>$D$9&amp;"1."</f>
@@ -3669,23 +3643,23 @@
         <v>認証機能概要</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F11" s="4" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F12" s="4" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F13" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="15" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E15" s="15" t="str">
         <f>$D$9&amp;"2."</f>
         <v>7.5.1.2.</v>
@@ -3695,7 +3669,7 @@
         <v>認証方法</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F16" s="16"/>
       <c r="G16" s="16"/>
       <c r="H16" s="16"/>
@@ -3726,7 +3700,7 @@
       <c r="AG16" s="16"/>
       <c r="AH16" s="16"/>
     </row>
-    <row r="17" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F17" s="18" t="s">
         <v>27</v>
       </c>
@@ -3763,19 +3737,19 @@
       <c r="AG17" s="19"/>
       <c r="AH17" s="20"/>
     </row>
-    <row r="18" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F18" s="29" t="s">
         <v>20</v>
       </c>
       <c r="G18" s="30"/>
       <c r="H18" s="30"/>
       <c r="I18" s="30"/>
-      <c r="J18" s="78" t="s">
+      <c r="J18" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="79"/>
-      <c r="L18" s="79"/>
-      <c r="M18" s="80"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="43"/>
+      <c r="M18" s="44"/>
       <c r="N18" s="30" t="s">
         <v>25</v>
       </c>
@@ -3800,7 +3774,7 @@
       <c r="AG18" s="30"/>
       <c r="AH18" s="31"/>
     </row>
-    <row r="19" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F19" s="29"/>
       <c r="G19" s="30"/>
       <c r="H19" s="30"/>
@@ -3833,7 +3807,7 @@
       <c r="AG19" s="30"/>
       <c r="AH19" s="31"/>
     </row>
-    <row r="20" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F20" s="29"/>
       <c r="G20" s="30"/>
       <c r="H20" s="30"/>
@@ -3866,7 +3840,7 @@
       <c r="AG20" s="30"/>
       <c r="AH20" s="31"/>
     </row>
-    <row r="21" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F21" s="29"/>
       <c r="G21" s="30"/>
       <c r="H21" s="30"/>
@@ -3897,19 +3871,19 @@
       <c r="AG21" s="30"/>
       <c r="AH21" s="31"/>
     </row>
-    <row r="22" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F22" s="35" t="s">
         <v>91</v>
       </c>
       <c r="G22" s="36"/>
       <c r="H22" s="36"/>
       <c r="I22" s="36"/>
-      <c r="J22" s="78" t="s">
+      <c r="J22" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="K22" s="79"/>
-      <c r="L22" s="79"/>
-      <c r="M22" s="80"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="43"/>
+      <c r="M22" s="44"/>
       <c r="N22" s="36" t="s">
         <v>24</v>
       </c>
@@ -3934,7 +3908,7 @@
       <c r="AG22" s="36"/>
       <c r="AH22" s="37"/>
     </row>
-    <row r="23" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F23" s="29"/>
       <c r="G23" s="30"/>
       <c r="H23" s="30"/>
@@ -3967,7 +3941,7 @@
       <c r="AG23" s="30"/>
       <c r="AH23" s="31"/>
     </row>
-    <row r="24" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F24" s="29"/>
       <c r="G24" s="30"/>
       <c r="H24" s="30"/>
@@ -4000,7 +3974,7 @@
       <c r="AG24" s="30"/>
       <c r="AH24" s="31"/>
     </row>
-    <row r="25" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F25" s="29"/>
       <c r="G25" s="30"/>
       <c r="H25" s="30"/>
@@ -4033,7 +4007,7 @@
       <c r="AG25" s="30"/>
       <c r="AH25" s="31"/>
     </row>
-    <row r="26" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F26" s="29"/>
       <c r="G26" s="30"/>
       <c r="H26" s="30"/>
@@ -4064,7 +4038,7 @@
       <c r="AG26" s="30"/>
       <c r="AH26" s="31"/>
     </row>
-    <row r="27" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F27" s="29"/>
       <c r="G27" s="30"/>
       <c r="H27" s="30"/>
@@ -4097,7 +4071,7 @@
       <c r="AG27" s="30"/>
       <c r="AH27" s="31"/>
     </row>
-    <row r="28" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F28" s="29"/>
       <c r="G28" s="30"/>
       <c r="H28" s="30"/>
@@ -4130,7 +4104,7 @@
       <c r="AG28" s="30"/>
       <c r="AH28" s="31"/>
     </row>
-    <row r="29" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F29" s="32"/>
       <c r="G29" s="33"/>
       <c r="H29" s="33"/>
@@ -4161,7 +4135,7 @@
       <c r="AG29" s="33"/>
       <c r="AH29" s="34"/>
     </row>
-    <row r="30" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F30" s="16"/>
       <c r="G30" s="16"/>
       <c r="H30" s="16"/>
@@ -4192,7 +4166,7 @@
       <c r="AG30" s="16"/>
       <c r="AH30" s="16"/>
     </row>
-    <row r="31" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F31" s="16"/>
       <c r="G31" s="16"/>
       <c r="H31" s="16"/>
@@ -4223,7 +4197,7 @@
       <c r="AG31" s="16"/>
       <c r="AH31" s="16"/>
     </row>
-    <row r="32" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E32" s="15" t="str">
         <f>$D$9&amp;"3."</f>
         <v>7.5.1.3.</v>
@@ -4233,7 +4207,7 @@
         <v>認証機能詳細</v>
       </c>
     </row>
-    <row r="33" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F33" s="15" t="s">
         <v>9</v>
       </c>
@@ -4241,52 +4215,52 @@
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F34" s="15"/>
       <c r="G34" s="4" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F35" s="15"/>
       <c r="G35" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="36" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="36" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F36" s="15"/>
       <c r="G36" s="4" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="37" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F37" s="15"/>
       <c r="G37" s="4" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="38" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F38" s="15"/>
       <c r="G38" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F39" s="15"/>
       <c r="G39" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F40" s="15"/>
     </row>
-    <row r="41" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F41" s="15"/>
     </row>
-    <row r="42" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F42" s="15"/>
     </row>
-    <row r="43" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F43" s="15"/>
       <c r="G43" s="15" t="s">
         <v>66</v>
@@ -4295,79 +4269,79 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F44" s="15"/>
       <c r="G44" s="15"/>
       <c r="H44" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="45" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F45" s="15"/>
       <c r="G45" s="15"/>
       <c r="H45" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="46" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F46" s="15"/>
       <c r="G46" s="15"/>
     </row>
-    <row r="47" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F47" s="15"/>
       <c r="G47" s="15"/>
     </row>
-    <row r="48" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F48" s="15"/>
       <c r="G48" s="15"/>
     </row>
-    <row r="49" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F49" s="15"/>
       <c r="G49" s="15"/>
     </row>
-    <row r="50" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F50" s="15"/>
       <c r="G50" s="15"/>
     </row>
-    <row r="51" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F51" s="15"/>
       <c r="G51" s="15"/>
     </row>
-    <row r="52" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F52" s="15"/>
       <c r="G52" s="15"/>
     </row>
-    <row r="53" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F53" s="15"/>
       <c r="G53" s="15"/>
     </row>
-    <row r="54" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F54" s="15"/>
       <c r="G54" s="15"/>
     </row>
-    <row r="55" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F55" s="15"/>
       <c r="G55" s="15"/>
     </row>
-    <row r="56" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F56" s="15"/>
       <c r="G56" s="15"/>
     </row>
-    <row r="57" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F57" s="15"/>
       <c r="G57" s="15"/>
     </row>
-    <row r="58" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F58" s="15"/>
       <c r="G58" s="15"/>
     </row>
-    <row r="59" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F59" s="15"/>
     </row>
-    <row r="60" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F60" s="15"/>
     </row>
-    <row r="61" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F61" s="15"/>
       <c r="G61" s="15" t="s">
         <v>37</v>
@@ -4376,61 +4350,61 @@
         <v>58</v>
       </c>
     </row>
-    <row r="62" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F62" s="15"/>
       <c r="H62" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="63" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F63" s="15"/>
       <c r="H63" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="64" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F64" s="15"/>
     </row>
-    <row r="65" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F65" s="15"/>
     </row>
-    <row r="66" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F66" s="15"/>
     </row>
-    <row r="67" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F67" s="15"/>
     </row>
-    <row r="68" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F68" s="15"/>
     </row>
-    <row r="69" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F69" s="15"/>
     </row>
-    <row r="70" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F70" s="15"/>
     </row>
-    <row r="71" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F71" s="15"/>
     </row>
-    <row r="72" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F72" s="15"/>
     </row>
-    <row r="73" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F73" s="15"/>
     </row>
-    <row r="74" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F74" s="15"/>
     </row>
-    <row r="75" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F75" s="15"/>
     </row>
-    <row r="76" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F76" s="15"/>
     </row>
-    <row r="77" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F77" s="15"/>
     </row>
-    <row r="78" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F78" s="15"/>
       <c r="G78" s="15" t="s">
         <v>38</v>
@@ -4439,55 +4413,55 @@
         <v>33</v>
       </c>
     </row>
-    <row r="79" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F79" s="15"/>
       <c r="H79" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F80" s="15"/>
     </row>
-    <row r="81" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F81" s="15"/>
     </row>
-    <row r="82" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F82" s="15"/>
     </row>
-    <row r="83" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F83" s="15"/>
     </row>
-    <row r="84" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F84" s="15"/>
     </row>
-    <row r="85" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F85" s="15"/>
     </row>
-    <row r="86" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F86" s="15"/>
     </row>
-    <row r="87" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F87" s="15"/>
     </row>
-    <row r="88" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F88" s="15"/>
     </row>
-    <row r="89" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F89" s="15"/>
     </row>
-    <row r="90" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F90" s="15"/>
     </row>
-    <row r="91" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F91" s="15"/>
     </row>
-    <row r="92" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F92" s="15"/>
     </row>
-    <row r="93" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F93" s="15"/>
     </row>
-    <row r="94" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F94" s="15"/>
       <c r="G94" s="15" t="s">
         <v>39</v>
@@ -4496,7 +4470,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="95" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F95" s="15"/>
       <c r="H95" s="15" t="s">
         <v>40</v>
@@ -4505,25 +4479,25 @@
         <v>36</v>
       </c>
     </row>
-    <row r="96" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F96" s="15"/>
       <c r="I96" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="97" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F97" s="15"/>
       <c r="I97" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="98" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F98" s="15"/>
     </row>
-    <row r="99" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F99" s="15"/>
     </row>
-    <row r="100" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F100" s="15" t="s">
         <v>29</v>
       </c>
@@ -4531,22 +4505,22 @@
         <v>93</v>
       </c>
     </row>
-    <row r="101" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F101" s="15"/>
       <c r="G101" s="4" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="102" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="102" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F102" s="15"/>
       <c r="G102" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="103" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="103" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F103" s="15"/>
     </row>
-    <row r="104" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F104" s="15"/>
       <c r="G104" s="15" t="s">
         <v>31</v>
@@ -4555,16 +4529,16 @@
         <v>124</v>
       </c>
     </row>
-    <row r="105" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F105" s="15"/>
       <c r="H105" s="4" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="106" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F106" s="15"/>
     </row>
-    <row r="107" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F107" s="15"/>
       <c r="H107" s="4" t="s">
         <v>126</v>
@@ -4573,22 +4547,22 @@
         <v>118</v>
       </c>
     </row>
-    <row r="108" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F108" s="15"/>
       <c r="L108" s="4" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="109" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F109" s="15"/>
       <c r="L109" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="110" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F110" s="15"/>
     </row>
-    <row r="111" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F111" s="15"/>
       <c r="H111" s="4" t="s">
         <v>127</v>
@@ -4597,19 +4571,19 @@
         <v>128</v>
       </c>
     </row>
-    <row r="112" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F112" s="15"/>
       <c r="L112" s="4" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="113" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F113" s="15"/>
     </row>
-    <row r="114" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F114" s="15"/>
     </row>
-    <row r="115" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F115" s="15"/>
       <c r="G115" s="15" t="s">
         <v>31</v>
@@ -4618,22 +4592,22 @@
         <v>130</v>
       </c>
     </row>
-    <row r="116" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F116" s="15"/>
       <c r="H116" s="4" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="117" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F117" s="15"/>
       <c r="H117" s="4" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="118" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F118" s="15"/>
     </row>
-    <row r="119" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F119" s="15"/>
       <c r="H119" s="15" t="s">
         <v>61</v>
@@ -4642,65 +4616,65 @@
         <v>41</v>
       </c>
     </row>
-    <row r="120" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F120" s="15"/>
       <c r="I120" s="4" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="121" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F121" s="15"/>
       <c r="I121" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="122" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F122" s="15"/>
       <c r="I122" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="123" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F123" s="15"/>
     </row>
-    <row r="124" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F124" s="15"/>
       <c r="I124" s="22"/>
     </row>
-    <row r="125" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F125" s="15"/>
     </row>
-    <row r="126" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F126" s="15"/>
     </row>
-    <row r="127" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F127" s="15"/>
     </row>
-    <row r="128" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F128" s="15"/>
     </row>
-    <row r="129" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F129" s="15"/>
     </row>
-    <row r="130" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F130" s="15"/>
     </row>
-    <row r="131" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F131" s="15"/>
     </row>
-    <row r="132" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F132" s="15"/>
     </row>
-    <row r="133" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F133" s="15"/>
     </row>
-    <row r="134" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F134" s="15"/>
     </row>
-    <row r="135" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F135" s="15"/>
     </row>
-    <row r="136" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F136" s="15"/>
       <c r="H136" s="15" t="s">
         <v>62</v>
@@ -4709,55 +4683,55 @@
         <v>58</v>
       </c>
     </row>
-    <row r="137" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F137" s="15"/>
       <c r="I137" s="4" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="138" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F138" s="15"/>
       <c r="I138" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="139" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F139" s="15"/>
     </row>
-    <row r="140" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F140" s="15"/>
     </row>
-    <row r="141" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F141" s="15"/>
     </row>
-    <row r="142" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F142" s="15"/>
     </row>
-    <row r="143" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="143" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F143" s="15"/>
     </row>
-    <row r="144" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="144" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F144" s="15"/>
     </row>
-    <row r="145" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="145" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F145" s="15"/>
     </row>
-    <row r="146" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="146" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F146" s="15"/>
     </row>
-    <row r="147" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="147" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F147" s="15"/>
     </row>
-    <row r="148" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="148" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F148" s="15"/>
     </row>
-    <row r="149" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="149" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F149" s="15"/>
     </row>
-    <row r="150" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F150" s="15"/>
     </row>
-    <row r="151" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F151" s="15"/>
       <c r="H151" s="15" t="s">
         <v>63</v>
@@ -4766,58 +4740,58 @@
         <v>34</v>
       </c>
     </row>
-    <row r="152" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="152" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F152" s="15"/>
       <c r="I152" s="4" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="153" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="153" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F153" s="15"/>
     </row>
-    <row r="154" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="154" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F154" s="15"/>
     </row>
-    <row r="155" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="155" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F155" s="15"/>
     </row>
-    <row r="156" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="156" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F156" s="15"/>
     </row>
-    <row r="157" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="157" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F157" s="15"/>
     </row>
-    <row r="158" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="158" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F158" s="15"/>
     </row>
-    <row r="159" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="159" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F159" s="15"/>
     </row>
-    <row r="160" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="160" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F160" s="15"/>
     </row>
-    <row r="161" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="161" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F161" s="15"/>
     </row>
-    <row r="162" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="162" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F162" s="15"/>
     </row>
-    <row r="163" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="163" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F163" s="15"/>
     </row>
-    <row r="164" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="164" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F164" s="15"/>
     </row>
-    <row r="165" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="165" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F165" s="15"/>
     </row>
-    <row r="166" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="166" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F166" s="15"/>
     </row>
-    <row r="167" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="167" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F167" s="15"/>
     </row>
-    <row r="168" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="168" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F168" s="15"/>
       <c r="H168" s="15" t="s">
         <v>60</v>
@@ -4826,7 +4800,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="169" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="169" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F169" s="15"/>
       <c r="I169" s="15" t="s">
         <v>64</v>
@@ -4835,16 +4809,16 @@
         <v>36</v>
       </c>
     </row>
-    <row r="170" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="170" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F170" s="15"/>
       <c r="J170" s="4" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="171" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="171" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F171" s="15"/>
     </row>
-    <row r="172" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="172" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F172" s="15"/>
       <c r="G172" s="15" t="s">
         <v>32</v>
@@ -4853,22 +4827,22 @@
         <v>134</v>
       </c>
     </row>
-    <row r="173" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="173" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F173" s="15"/>
       <c r="H173" s="4" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="174" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="174" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F174" s="15"/>
       <c r="H174" s="4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="175" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="175" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F175" s="15"/>
     </row>
-    <row r="176" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="176" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F176" s="15"/>
       <c r="H176" s="15" t="s">
         <v>65</v>
@@ -4877,61 +4851,61 @@
         <v>41</v>
       </c>
     </row>
-    <row r="177" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="177" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F177" s="15"/>
       <c r="I177" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="178" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="178" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F178" s="15"/>
       <c r="I178" s="4" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="179" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="179" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F179" s="15"/>
       <c r="I179" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="180" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="180" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F180" s="15"/>
     </row>
-    <row r="181" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="181" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F181" s="15"/>
     </row>
-    <row r="182" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="182" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F182" s="15"/>
     </row>
-    <row r="183" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F183" s="15"/>
     </row>
-    <row r="184" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="184" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F184" s="15"/>
     </row>
-    <row r="185" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="185" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F185" s="15"/>
     </row>
-    <row r="186" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F186" s="15"/>
     </row>
-    <row r="187" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F187" s="15"/>
     </row>
-    <row r="188" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="188" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F188" s="15"/>
     </row>
-    <row r="189" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="189" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F189" s="15"/>
     </row>
-    <row r="190" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="190" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F190" s="15"/>
     </row>
-    <row r="191" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="191" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F191" s="15"/>
     </row>
-    <row r="192" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="192" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F192" s="15"/>
       <c r="H192" s="15" t="s">
         <v>68</v>
@@ -4940,22 +4914,22 @@
         <v>58</v>
       </c>
     </row>
-    <row r="193" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="193" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F193" s="15"/>
       <c r="I193" s="21" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="194" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="194" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F194" s="15"/>
     </row>
-    <row r="195" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="195" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F195" s="15"/>
     </row>
-    <row r="196" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="196" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F196" s="15"/>
     </row>
-    <row r="197" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="197" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F197" s="15"/>
       <c r="H197" s="15" t="s">
         <v>70</v>
@@ -4964,85 +4938,85 @@
         <v>34</v>
       </c>
     </row>
-    <row r="198" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="198" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F198" s="15"/>
       <c r="I198" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="199" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="199" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F199" s="15"/>
     </row>
-    <row r="200" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="200" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F200" s="15"/>
     </row>
-    <row r="201" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="201" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F201" s="15"/>
     </row>
-    <row r="202" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="202" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F202" s="15"/>
     </row>
-    <row r="203" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="203" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F203" s="15"/>
     </row>
-    <row r="204" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="204" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F204" s="15"/>
     </row>
-    <row r="205" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="205" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F205" s="15"/>
     </row>
-    <row r="206" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="206" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F206" s="15"/>
     </row>
-    <row r="207" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="207" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F207" s="15"/>
     </row>
-    <row r="208" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="208" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F208" s="15"/>
     </row>
-    <row r="209" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="209" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F209" s="15"/>
     </row>
-    <row r="210" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="210" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F210" s="15"/>
     </row>
-    <row r="211" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="211" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F211" s="15"/>
     </row>
-    <row r="212" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="212" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F212" s="15"/>
     </row>
-    <row r="213" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="213" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F213" s="15"/>
     </row>
-    <row r="214" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="214" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F214" s="15"/>
     </row>
-    <row r="215" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="215" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F215" s="15"/>
     </row>
-    <row r="216" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="216" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F216" s="15"/>
     </row>
-    <row r="217" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="217" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F217" s="15"/>
     </row>
-    <row r="218" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="218" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F218" s="15"/>
     </row>
-    <row r="219" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="219" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F219" s="15"/>
     </row>
-    <row r="220" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="220" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F220" s="15"/>
     </row>
-    <row r="221" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="221" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F221" s="15"/>
     </row>
-    <row r="222" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="222" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F222" s="15"/>
     </row>
-    <row r="223" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="223" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F223" s="15"/>
       <c r="H223" s="15" t="s">
         <v>71</v>
@@ -5051,7 +5025,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="224" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="224" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F224" s="15"/>
       <c r="I224" s="15" t="s">
         <v>72</v>
@@ -5060,28 +5034,28 @@
         <v>36</v>
       </c>
     </row>
-    <row r="225" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="225" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F225" s="15"/>
       <c r="J225" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="226" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="226" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F226" s="15"/>
       <c r="J226" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="227" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="227" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F227" s="15"/>
       <c r="J227" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="228" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="228" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F228" s="15"/>
     </row>
-    <row r="229" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="229" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F229" s="15"/>
       <c r="I229" s="15" t="s">
         <v>73</v>
@@ -5090,25 +5064,25 @@
         <v>139</v>
       </c>
     </row>
-    <row r="230" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="230" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F230" s="15"/>
       <c r="J230" s="4" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="231" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="231" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F231" s="15"/>
       <c r="J231" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="232" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="232" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F232" s="15"/>
     </row>
-    <row r="233" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="233" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F233" s="15"/>
     </row>
-    <row r="234" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="234" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D234" s="15" t="str">
         <f>$C$7&amp;"2."</f>
         <v>7.5.2.</v>
@@ -5117,7 +5091,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="235" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="235" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D235" s="15"/>
       <c r="E235" s="15" t="str">
         <f>$D$234&amp;"1."</f>
@@ -5128,22 +5102,22 @@
         <v>認可機能概要</v>
       </c>
     </row>
-    <row r="236" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="236" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D236" s="15"/>
       <c r="F236" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="237" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="237" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D237" s="15"/>
       <c r="F237" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="238" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="238" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D238" s="15"/>
     </row>
-    <row r="239" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="239" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D239" s="15"/>
       <c r="E239" s="15" t="str">
         <f>$D$234&amp;"2."</f>
@@ -5154,7 +5128,7 @@
         <v>認可方法</v>
       </c>
     </row>
-    <row r="240" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="240" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F240" s="17"/>
       <c r="G240" s="17"/>
       <c r="H240" s="17"/>
@@ -5185,7 +5159,7 @@
       <c r="AG240" s="17"/>
       <c r="AH240" s="17"/>
     </row>
-    <row r="241" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="241" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F241" s="17"/>
       <c r="G241" s="17"/>
       <c r="H241" s="17"/>
@@ -5216,7 +5190,7 @@
       <c r="AG241" s="17"/>
       <c r="AH241" s="17"/>
     </row>
-    <row r="242" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="242" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F242" s="18" t="s">
         <v>27</v>
       </c>
@@ -5253,7 +5227,7 @@
       <c r="AG242" s="19"/>
       <c r="AH242" s="20"/>
     </row>
-    <row r="243" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="243" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F243" s="29" t="s">
         <v>15</v>
       </c>
@@ -5290,7 +5264,7 @@
       <c r="AG243" s="30"/>
       <c r="AH243" s="31"/>
     </row>
-    <row r="244" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="244" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F244" s="29"/>
       <c r="G244" s="30"/>
       <c r="H244" s="30"/>
@@ -5321,7 +5295,7 @@
       <c r="AG244" s="30"/>
       <c r="AH244" s="31"/>
     </row>
-    <row r="245" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="245" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F245" s="29"/>
       <c r="G245" s="30"/>
       <c r="H245" s="30"/>
@@ -5352,7 +5326,7 @@
       <c r="AG245" s="30"/>
       <c r="AH245" s="31"/>
     </row>
-    <row r="246" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="246" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F246" s="35" t="s">
         <v>91</v>
       </c>
@@ -5389,7 +5363,7 @@
       <c r="AG246" s="36"/>
       <c r="AH246" s="37"/>
     </row>
-    <row r="247" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="247" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F247" s="29"/>
       <c r="G247" s="30"/>
       <c r="H247" s="30"/>
@@ -5420,7 +5394,7 @@
       <c r="AG247" s="30"/>
       <c r="AH247" s="31"/>
     </row>
-    <row r="248" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="248" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F248" s="32"/>
       <c r="G248" s="33"/>
       <c r="H248" s="33"/>
@@ -5451,7 +5425,7 @@
       <c r="AG248" s="33"/>
       <c r="AH248" s="34"/>
     </row>
-    <row r="249" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="249" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F249" s="17"/>
       <c r="G249" s="17"/>
       <c r="H249" s="17"/>
@@ -5482,7 +5456,7 @@
       <c r="AG249" s="17"/>
       <c r="AH249" s="17"/>
     </row>
-    <row r="250" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="250" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F250" s="17"/>
       <c r="G250" s="17"/>
       <c r="H250" s="17"/>
@@ -5513,10 +5487,10 @@
       <c r="AG250" s="17"/>
       <c r="AH250" s="17"/>
     </row>
-    <row r="251" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="251" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D251" s="15"/>
     </row>
-    <row r="252" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="252" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D252" s="15"/>
       <c r="E252" s="15" t="str">
         <f>$D$234&amp;"3."</f>
@@ -5527,91 +5501,91 @@
         <v>認可機能詳細</v>
       </c>
     </row>
-    <row r="253" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="253" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D253" s="15"/>
       <c r="E253" s="15"/>
       <c r="F253" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="254" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="254" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D254" s="15"/>
       <c r="E254" s="15"/>
       <c r="F254" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="255" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="255" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D255" s="15"/>
       <c r="E255" s="15"/>
     </row>
-    <row r="256" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="256" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D256" s="15"/>
       <c r="E256" s="15"/>
     </row>
-    <row r="257" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="257" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D257" s="15"/>
       <c r="E257" s="15"/>
     </row>
-    <row r="258" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="258" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D258" s="15"/>
       <c r="E258" s="15"/>
     </row>
-    <row r="259" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="259" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D259" s="15"/>
       <c r="E259" s="15"/>
     </row>
-    <row r="260" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="260" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D260" s="15"/>
       <c r="E260" s="15"/>
     </row>
-    <row r="261" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="261" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D261" s="15"/>
       <c r="E261" s="15"/>
     </row>
-    <row r="262" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="262" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D262" s="15"/>
       <c r="E262" s="15"/>
     </row>
-    <row r="263" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="263" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D263" s="15"/>
       <c r="E263" s="15"/>
     </row>
-    <row r="264" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="264" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D264" s="15"/>
       <c r="E264" s="15"/>
     </row>
-    <row r="265" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="265" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D265" s="15"/>
       <c r="E265" s="15"/>
     </row>
-    <row r="266" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="266" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D266" s="15"/>
       <c r="E266" s="15"/>
     </row>
-    <row r="267" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="267" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D267" s="15"/>
       <c r="E267" s="15"/>
       <c r="G267" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="268" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="268" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D268" s="15"/>
       <c r="E268" s="15"/>
     </row>
-    <row r="269" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="269" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D269" s="15"/>
       <c r="E269" s="15"/>
-      <c r="G269" s="38" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="270" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G269" s="102" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="270" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D270" s="15"/>
       <c r="E270" s="15"/>
     </row>
-    <row r="271" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="271" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D271" s="15"/>
       <c r="E271" s="15"/>
       <c r="F271" s="21" t="s">
@@ -5621,39 +5595,39 @@
         <v>56</v>
       </c>
     </row>
-    <row r="272" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="272" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D272" s="15"/>
       <c r="E272" s="15"/>
       <c r="G272" s="4" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="273" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="273" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D273" s="15"/>
       <c r="E273" s="15"/>
       <c r="G273" s="4" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="274" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="274" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D274" s="15"/>
       <c r="E274" s="15"/>
       <c r="G274" s="4" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="275" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="275" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D275" s="15"/>
       <c r="E275" s="15"/>
       <c r="G275" s="4" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="276" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="276" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D276" s="15"/>
       <c r="E276" s="15"/>
     </row>
-    <row r="277" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="277" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D277" s="15"/>
       <c r="E277" s="15"/>
       <c r="F277" s="21" t="s">
@@ -5663,607 +5637,607 @@
         <v>96</v>
       </c>
     </row>
-    <row r="278" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="278" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D278" s="15"/>
       <c r="E278" s="15"/>
       <c r="G278" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="279" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="279" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D279" s="15"/>
       <c r="E279" s="15"/>
       <c r="G279" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="280" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="280" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D280" s="15"/>
       <c r="E280" s="15"/>
       <c r="G280" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="281" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="281" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D281" s="15"/>
       <c r="E281" s="15"/>
     </row>
-    <row r="282" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="282" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D282" s="15"/>
       <c r="E282" s="15"/>
       <c r="G282" s="22" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="283" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="283" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D283" s="15"/>
       <c r="E283" s="15"/>
-      <c r="H283" s="46" t="s">
+      <c r="H283" s="70" t="s">
+        <v>155</v>
+      </c>
+      <c r="I283" s="70"/>
+      <c r="J283" s="70"/>
+      <c r="K283" s="70"/>
+      <c r="L283" s="70" t="s">
         <v>156</v>
       </c>
-      <c r="I283" s="46"/>
-      <c r="J283" s="46"/>
-      <c r="K283" s="46"/>
-      <c r="L283" s="46" t="s">
-        <v>157</v>
-      </c>
-      <c r="M283" s="46"/>
-      <c r="N283" s="46"/>
-      <c r="O283" s="46"/>
-      <c r="P283" s="46"/>
-      <c r="Q283" s="46"/>
-      <c r="R283" s="46"/>
-      <c r="S283" s="46"/>
-      <c r="T283" s="46"/>
-      <c r="U283" s="46"/>
-      <c r="V283" s="46"/>
-      <c r="W283" s="46"/>
-      <c r="X283" s="46"/>
-      <c r="Y283" s="46"/>
-      <c r="Z283" s="46"/>
-      <c r="AA283" s="46"/>
-    </row>
-    <row r="284" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M283" s="70"/>
+      <c r="N283" s="70"/>
+      <c r="O283" s="70"/>
+      <c r="P283" s="70"/>
+      <c r="Q283" s="70"/>
+      <c r="R283" s="70"/>
+      <c r="S283" s="70"/>
+      <c r="T283" s="70"/>
+      <c r="U283" s="70"/>
+      <c r="V283" s="70"/>
+      <c r="W283" s="70"/>
+      <c r="X283" s="70"/>
+      <c r="Y283" s="70"/>
+      <c r="Z283" s="70"/>
+      <c r="AA283" s="70"/>
+    </row>
+    <row r="284" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D284" s="15"/>
       <c r="E284" s="15"/>
-      <c r="H284" s="45" t="s">
+      <c r="H284" s="100" t="s">
+        <v>157</v>
+      </c>
+      <c r="I284" s="100"/>
+      <c r="J284" s="100"/>
+      <c r="K284" s="100"/>
+      <c r="L284" s="100" t="s">
         <v>158</v>
       </c>
-      <c r="I284" s="45"/>
-      <c r="J284" s="45"/>
-      <c r="K284" s="45"/>
-      <c r="L284" s="45" t="s">
-        <v>159</v>
-      </c>
-      <c r="M284" s="45"/>
-      <c r="N284" s="45"/>
-      <c r="O284" s="45"/>
-      <c r="P284" s="45"/>
-      <c r="Q284" s="45"/>
-      <c r="R284" s="45"/>
-      <c r="S284" s="45"/>
-      <c r="T284" s="45"/>
-      <c r="U284" s="45"/>
-      <c r="V284" s="45"/>
-      <c r="W284" s="45"/>
-      <c r="X284" s="45"/>
-      <c r="Y284" s="45"/>
-      <c r="Z284" s="45"/>
-      <c r="AA284" s="45"/>
-    </row>
-    <row r="285" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M284" s="100"/>
+      <c r="N284" s="100"/>
+      <c r="O284" s="100"/>
+      <c r="P284" s="100"/>
+      <c r="Q284" s="100"/>
+      <c r="R284" s="100"/>
+      <c r="S284" s="100"/>
+      <c r="T284" s="100"/>
+      <c r="U284" s="100"/>
+      <c r="V284" s="100"/>
+      <c r="W284" s="100"/>
+      <c r="X284" s="100"/>
+      <c r="Y284" s="100"/>
+      <c r="Z284" s="100"/>
+      <c r="AA284" s="100"/>
+    </row>
+    <row r="285" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D285" s="15"/>
       <c r="E285" s="15"/>
-      <c r="H285" s="45" t="s">
-        <v>160</v>
-      </c>
-      <c r="I285" s="45"/>
-      <c r="J285" s="45"/>
-      <c r="K285" s="45"/>
-      <c r="L285" s="45"/>
-      <c r="M285" s="45"/>
-      <c r="N285" s="45"/>
-      <c r="O285" s="45"/>
-      <c r="P285" s="45"/>
-      <c r="Q285" s="45"/>
-      <c r="R285" s="45"/>
-      <c r="S285" s="45"/>
-      <c r="T285" s="45"/>
-      <c r="U285" s="45"/>
-      <c r="V285" s="45"/>
-      <c r="W285" s="45"/>
-      <c r="X285" s="45"/>
-      <c r="Y285" s="45"/>
-      <c r="Z285" s="45"/>
-      <c r="AA285" s="45"/>
-    </row>
-    <row r="286" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H285" s="100" t="s">
+        <v>159</v>
+      </c>
+      <c r="I285" s="100"/>
+      <c r="J285" s="100"/>
+      <c r="K285" s="100"/>
+      <c r="L285" s="100"/>
+      <c r="M285" s="100"/>
+      <c r="N285" s="100"/>
+      <c r="O285" s="100"/>
+      <c r="P285" s="100"/>
+      <c r="Q285" s="100"/>
+      <c r="R285" s="100"/>
+      <c r="S285" s="100"/>
+      <c r="T285" s="100"/>
+      <c r="U285" s="100"/>
+      <c r="V285" s="100"/>
+      <c r="W285" s="100"/>
+      <c r="X285" s="100"/>
+      <c r="Y285" s="100"/>
+      <c r="Z285" s="100"/>
+      <c r="AA285" s="100"/>
+    </row>
+    <row r="286" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D286" s="15"/>
       <c r="E286" s="15"/>
-      <c r="H286" s="45" t="s">
+      <c r="H286" s="100" t="s">
+        <v>160</v>
+      </c>
+      <c r="I286" s="100"/>
+      <c r="J286" s="100"/>
+      <c r="K286" s="100"/>
+      <c r="L286" s="100" t="s">
         <v>161</v>
       </c>
-      <c r="I286" s="45"/>
-      <c r="J286" s="45"/>
-      <c r="K286" s="45"/>
-      <c r="L286" s="45" t="s">
-        <v>162</v>
-      </c>
-      <c r="M286" s="45"/>
-      <c r="N286" s="45"/>
-      <c r="O286" s="45"/>
-      <c r="P286" s="45"/>
-      <c r="Q286" s="45"/>
-      <c r="R286" s="45"/>
-      <c r="S286" s="45"/>
-      <c r="T286" s="45"/>
-      <c r="U286" s="45"/>
-      <c r="V286" s="45"/>
-      <c r="W286" s="45"/>
-      <c r="X286" s="45"/>
-      <c r="Y286" s="45"/>
-      <c r="Z286" s="45"/>
-      <c r="AA286" s="45"/>
-    </row>
-    <row r="287" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M286" s="100"/>
+      <c r="N286" s="100"/>
+      <c r="O286" s="100"/>
+      <c r="P286" s="100"/>
+      <c r="Q286" s="100"/>
+      <c r="R286" s="100"/>
+      <c r="S286" s="100"/>
+      <c r="T286" s="100"/>
+      <c r="U286" s="100"/>
+      <c r="V286" s="100"/>
+      <c r="W286" s="100"/>
+      <c r="X286" s="100"/>
+      <c r="Y286" s="100"/>
+      <c r="Z286" s="100"/>
+      <c r="AA286" s="100"/>
+    </row>
+    <row r="287" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D287" s="15"/>
       <c r="E287" s="15"/>
-      <c r="H287" s="45" t="s">
-        <v>163</v>
-      </c>
-      <c r="I287" s="45"/>
-      <c r="J287" s="45"/>
-      <c r="K287" s="45"/>
-      <c r="L287" s="45"/>
-      <c r="M287" s="45"/>
-      <c r="N287" s="45"/>
-      <c r="O287" s="45"/>
-      <c r="P287" s="45"/>
-      <c r="Q287" s="45"/>
-      <c r="R287" s="45"/>
-      <c r="S287" s="45"/>
-      <c r="T287" s="45"/>
-      <c r="U287" s="45"/>
-      <c r="V287" s="45"/>
-      <c r="W287" s="45"/>
-      <c r="X287" s="45"/>
-      <c r="Y287" s="45"/>
-      <c r="Z287" s="45"/>
-      <c r="AA287" s="45"/>
-    </row>
-    <row r="288" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H287" s="100" t="s">
+        <v>162</v>
+      </c>
+      <c r="I287" s="100"/>
+      <c r="J287" s="100"/>
+      <c r="K287" s="100"/>
+      <c r="L287" s="100"/>
+      <c r="M287" s="100"/>
+      <c r="N287" s="100"/>
+      <c r="O287" s="100"/>
+      <c r="P287" s="100"/>
+      <c r="Q287" s="100"/>
+      <c r="R287" s="100"/>
+      <c r="S287" s="100"/>
+      <c r="T287" s="100"/>
+      <c r="U287" s="100"/>
+      <c r="V287" s="100"/>
+      <c r="W287" s="100"/>
+      <c r="X287" s="100"/>
+      <c r="Y287" s="100"/>
+      <c r="Z287" s="100"/>
+      <c r="AA287" s="100"/>
+    </row>
+    <row r="288" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D288" s="15"/>
       <c r="E288" s="15"/>
-      <c r="H288" s="45" t="s">
+      <c r="H288" s="100" t="s">
+        <v>163</v>
+      </c>
+      <c r="I288" s="100"/>
+      <c r="J288" s="100"/>
+      <c r="K288" s="100"/>
+      <c r="L288" s="100" t="s">
         <v>164</v>
       </c>
-      <c r="I288" s="45"/>
-      <c r="J288" s="45"/>
-      <c r="K288" s="45"/>
-      <c r="L288" s="45" t="s">
-        <v>165</v>
-      </c>
-      <c r="M288" s="45"/>
-      <c r="N288" s="45"/>
-      <c r="O288" s="45"/>
-      <c r="P288" s="45"/>
-      <c r="Q288" s="45"/>
-      <c r="R288" s="45"/>
-      <c r="S288" s="45"/>
-      <c r="T288" s="45"/>
-      <c r="U288" s="45"/>
-      <c r="V288" s="45"/>
-      <c r="W288" s="45"/>
-      <c r="X288" s="45"/>
-      <c r="Y288" s="45"/>
-      <c r="Z288" s="45"/>
-      <c r="AA288" s="45"/>
-    </row>
-    <row r="289" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M288" s="100"/>
+      <c r="N288" s="100"/>
+      <c r="O288" s="100"/>
+      <c r="P288" s="100"/>
+      <c r="Q288" s="100"/>
+      <c r="R288" s="100"/>
+      <c r="S288" s="100"/>
+      <c r="T288" s="100"/>
+      <c r="U288" s="100"/>
+      <c r="V288" s="100"/>
+      <c r="W288" s="100"/>
+      <c r="X288" s="100"/>
+      <c r="Y288" s="100"/>
+      <c r="Z288" s="100"/>
+      <c r="AA288" s="100"/>
+    </row>
+    <row r="289" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D289" s="15"/>
       <c r="E289" s="15"/>
     </row>
-    <row r="290" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="290" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D290" s="15"/>
       <c r="E290" s="15"/>
       <c r="G290" s="22" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="291" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="291" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D291" s="15"/>
       <c r="E291" s="15"/>
-      <c r="H291" s="46" t="s">
+      <c r="H291" s="70" t="s">
+        <v>166</v>
+      </c>
+      <c r="I291" s="70"/>
+      <c r="J291" s="70"/>
+      <c r="K291" s="70" t="s">
         <v>167</v>
       </c>
-      <c r="I291" s="46"/>
-      <c r="J291" s="46"/>
-      <c r="K291" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="L291" s="46"/>
-      <c r="M291" s="46"/>
-      <c r="N291" s="46"/>
-      <c r="O291" s="46"/>
-      <c r="P291" s="46"/>
-      <c r="Q291" s="46"/>
-      <c r="R291" s="46"/>
-      <c r="S291" s="46"/>
-      <c r="T291" s="46"/>
-      <c r="U291" s="46"/>
-    </row>
-    <row r="292" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L291" s="70"/>
+      <c r="M291" s="70"/>
+      <c r="N291" s="70"/>
+      <c r="O291" s="70"/>
+      <c r="P291" s="70"/>
+      <c r="Q291" s="70"/>
+      <c r="R291" s="70"/>
+      <c r="S291" s="70"/>
+      <c r="T291" s="70"/>
+      <c r="U291" s="70"/>
+    </row>
+    <row r="292" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D292" s="15"/>
       <c r="E292" s="15"/>
-      <c r="H292" s="45" t="s">
-        <v>169</v>
-      </c>
-      <c r="I292" s="45"/>
-      <c r="J292" s="45"/>
-      <c r="K292" s="45" t="s">
-        <v>160</v>
-      </c>
-      <c r="L292" s="45"/>
-      <c r="M292" s="45"/>
-      <c r="N292" s="45"/>
-      <c r="O292" s="45"/>
-      <c r="P292" s="45"/>
-      <c r="Q292" s="45"/>
-      <c r="R292" s="45"/>
-      <c r="S292" s="45"/>
-      <c r="T292" s="45"/>
-      <c r="U292" s="45"/>
-    </row>
-    <row r="293" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H292" s="100" t="s">
+        <v>168</v>
+      </c>
+      <c r="I292" s="100"/>
+      <c r="J292" s="100"/>
+      <c r="K292" s="100" t="s">
+        <v>159</v>
+      </c>
+      <c r="L292" s="100"/>
+      <c r="M292" s="100"/>
+      <c r="N292" s="100"/>
+      <c r="O292" s="100"/>
+      <c r="P292" s="100"/>
+      <c r="Q292" s="100"/>
+      <c r="R292" s="100"/>
+      <c r="S292" s="100"/>
+      <c r="T292" s="100"/>
+      <c r="U292" s="100"/>
+    </row>
+    <row r="293" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D293" s="15"/>
       <c r="E293" s="15"/>
-      <c r="H293" s="45" t="s">
+      <c r="H293" s="100" t="s">
+        <v>169</v>
+      </c>
+      <c r="I293" s="100"/>
+      <c r="J293" s="100"/>
+      <c r="K293" s="100" t="s">
         <v>170</v>
       </c>
-      <c r="I293" s="45"/>
-      <c r="J293" s="45"/>
-      <c r="K293" s="45" t="s">
-        <v>171</v>
-      </c>
-      <c r="L293" s="45"/>
-      <c r="M293" s="45"/>
-      <c r="N293" s="45"/>
-      <c r="O293" s="45"/>
-      <c r="P293" s="45"/>
-      <c r="Q293" s="45"/>
-      <c r="R293" s="45"/>
-      <c r="S293" s="45"/>
-      <c r="T293" s="45"/>
-      <c r="U293" s="45"/>
-    </row>
-    <row r="294" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L293" s="100"/>
+      <c r="M293" s="100"/>
+      <c r="N293" s="100"/>
+      <c r="O293" s="100"/>
+      <c r="P293" s="100"/>
+      <c r="Q293" s="100"/>
+      <c r="R293" s="100"/>
+      <c r="S293" s="100"/>
+      <c r="T293" s="100"/>
+      <c r="U293" s="100"/>
+    </row>
+    <row r="294" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D294" s="15"/>
       <c r="E294" s="15"/>
-      <c r="H294" s="45" t="s">
-        <v>172</v>
-      </c>
-      <c r="I294" s="45"/>
-      <c r="J294" s="45"/>
-      <c r="K294" s="45" t="s">
-        <v>164</v>
-      </c>
-      <c r="L294" s="45"/>
-      <c r="M294" s="45"/>
-      <c r="N294" s="45"/>
-      <c r="O294" s="45"/>
-      <c r="P294" s="45"/>
-      <c r="Q294" s="45"/>
-      <c r="R294" s="45"/>
-      <c r="S294" s="45"/>
-      <c r="T294" s="45"/>
-      <c r="U294" s="45"/>
-    </row>
-    <row r="295" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H294" s="100" t="s">
+        <v>171</v>
+      </c>
+      <c r="I294" s="100"/>
+      <c r="J294" s="100"/>
+      <c r="K294" s="100" t="s">
+        <v>163</v>
+      </c>
+      <c r="L294" s="100"/>
+      <c r="M294" s="100"/>
+      <c r="N294" s="100"/>
+      <c r="O294" s="100"/>
+      <c r="P294" s="100"/>
+      <c r="Q294" s="100"/>
+      <c r="R294" s="100"/>
+      <c r="S294" s="100"/>
+      <c r="T294" s="100"/>
+      <c r="U294" s="100"/>
+    </row>
+    <row r="295" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D295" s="15"/>
       <c r="E295" s="15"/>
-      <c r="H295" s="45" t="s">
-        <v>173</v>
-      </c>
-      <c r="I295" s="45"/>
-      <c r="J295" s="45"/>
-      <c r="K295" s="45" t="s">
-        <v>161</v>
-      </c>
-      <c r="L295" s="45"/>
-      <c r="M295" s="45"/>
-      <c r="N295" s="45"/>
-      <c r="O295" s="45"/>
-      <c r="P295" s="45"/>
-      <c r="Q295" s="45"/>
-      <c r="R295" s="45"/>
-      <c r="S295" s="45"/>
-      <c r="T295" s="45"/>
-      <c r="U295" s="45"/>
-    </row>
-    <row r="296" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H295" s="100" t="s">
+        <v>172</v>
+      </c>
+      <c r="I295" s="100"/>
+      <c r="J295" s="100"/>
+      <c r="K295" s="100" t="s">
+        <v>160</v>
+      </c>
+      <c r="L295" s="100"/>
+      <c r="M295" s="100"/>
+      <c r="N295" s="100"/>
+      <c r="O295" s="100"/>
+      <c r="P295" s="100"/>
+      <c r="Q295" s="100"/>
+      <c r="R295" s="100"/>
+      <c r="S295" s="100"/>
+      <c r="T295" s="100"/>
+      <c r="U295" s="100"/>
+    </row>
+    <row r="296" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D296" s="15"/>
       <c r="E296" s="15"/>
     </row>
-    <row r="297" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="297" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D297" s="15"/>
       <c r="E297" s="15"/>
       <c r="G297" s="22" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="298" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="298" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D298" s="15"/>
       <c r="E298" s="15"/>
-      <c r="H298" s="46" t="s">
+      <c r="H298" s="70" t="s">
+        <v>174</v>
+      </c>
+      <c r="I298" s="70"/>
+      <c r="J298" s="70"/>
+      <c r="K298" s="70" t="s">
         <v>175</v>
       </c>
-      <c r="I298" s="46"/>
-      <c r="J298" s="46"/>
-      <c r="K298" s="46" t="s">
-        <v>176</v>
-      </c>
-      <c r="L298" s="46"/>
-      <c r="M298" s="46"/>
-      <c r="N298" s="46"/>
-      <c r="O298" s="46"/>
-      <c r="P298" s="46"/>
-      <c r="Q298" s="46"/>
-      <c r="R298" s="46"/>
-      <c r="S298" s="46"/>
-      <c r="T298" s="46"/>
-      <c r="U298" s="46"/>
-    </row>
-    <row r="299" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L298" s="70"/>
+      <c r="M298" s="70"/>
+      <c r="N298" s="70"/>
+      <c r="O298" s="70"/>
+      <c r="P298" s="70"/>
+      <c r="Q298" s="70"/>
+      <c r="R298" s="70"/>
+      <c r="S298" s="70"/>
+      <c r="T298" s="70"/>
+      <c r="U298" s="70"/>
+    </row>
+    <row r="299" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D299" s="15"/>
       <c r="E299" s="15"/>
-      <c r="H299" s="45" t="s">
+      <c r="H299" s="100" t="s">
+        <v>176</v>
+      </c>
+      <c r="I299" s="100"/>
+      <c r="J299" s="100"/>
+      <c r="K299" s="100" t="s">
         <v>177</v>
       </c>
-      <c r="I299" s="45"/>
-      <c r="J299" s="45"/>
-      <c r="K299" s="45" t="s">
-        <v>178</v>
-      </c>
-      <c r="L299" s="45"/>
-      <c r="M299" s="45"/>
-      <c r="N299" s="45"/>
-      <c r="O299" s="45"/>
-      <c r="P299" s="45"/>
-      <c r="Q299" s="45"/>
-      <c r="R299" s="45"/>
-      <c r="S299" s="45"/>
-      <c r="T299" s="45"/>
-      <c r="U299" s="45"/>
-    </row>
-    <row r="300" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L299" s="100"/>
+      <c r="M299" s="100"/>
+      <c r="N299" s="100"/>
+      <c r="O299" s="100"/>
+      <c r="P299" s="100"/>
+      <c r="Q299" s="100"/>
+      <c r="R299" s="100"/>
+      <c r="S299" s="100"/>
+      <c r="T299" s="100"/>
+      <c r="U299" s="100"/>
+    </row>
+    <row r="300" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D300" s="15"/>
       <c r="E300" s="15"/>
-      <c r="H300" s="45" t="s">
+      <c r="H300" s="100" t="s">
+        <v>178</v>
+      </c>
+      <c r="I300" s="100"/>
+      <c r="J300" s="100"/>
+      <c r="K300" s="100" t="s">
         <v>179</v>
       </c>
-      <c r="I300" s="45"/>
-      <c r="J300" s="45"/>
-      <c r="K300" s="45" t="s">
-        <v>180</v>
-      </c>
-      <c r="L300" s="45"/>
-      <c r="M300" s="45"/>
-      <c r="N300" s="45"/>
-      <c r="O300" s="45"/>
-      <c r="P300" s="45"/>
-      <c r="Q300" s="45"/>
-      <c r="R300" s="45"/>
-      <c r="S300" s="45"/>
-      <c r="T300" s="45"/>
-      <c r="U300" s="45"/>
-    </row>
-    <row r="301" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L300" s="100"/>
+      <c r="M300" s="100"/>
+      <c r="N300" s="100"/>
+      <c r="O300" s="100"/>
+      <c r="P300" s="100"/>
+      <c r="Q300" s="100"/>
+      <c r="R300" s="100"/>
+      <c r="S300" s="100"/>
+      <c r="T300" s="100"/>
+      <c r="U300" s="100"/>
+    </row>
+    <row r="301" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D301" s="15"/>
       <c r="E301" s="15"/>
-      <c r="H301" s="45" t="s">
+      <c r="H301" s="100" t="s">
+        <v>180</v>
+      </c>
+      <c r="I301" s="100"/>
+      <c r="J301" s="100"/>
+      <c r="K301" s="100" t="s">
         <v>181</v>
       </c>
-      <c r="I301" s="45"/>
-      <c r="J301" s="45"/>
-      <c r="K301" s="45" t="s">
-        <v>182</v>
-      </c>
-      <c r="L301" s="45"/>
-      <c r="M301" s="45"/>
-      <c r="N301" s="45"/>
-      <c r="O301" s="45"/>
-      <c r="P301" s="45"/>
-      <c r="Q301" s="45"/>
-      <c r="R301" s="45"/>
-      <c r="S301" s="45"/>
-      <c r="T301" s="45"/>
-      <c r="U301" s="45"/>
-    </row>
-    <row r="302" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L301" s="100"/>
+      <c r="M301" s="100"/>
+      <c r="N301" s="100"/>
+      <c r="O301" s="100"/>
+      <c r="P301" s="100"/>
+      <c r="Q301" s="100"/>
+      <c r="R301" s="100"/>
+      <c r="S301" s="100"/>
+      <c r="T301" s="100"/>
+      <c r="U301" s="100"/>
+    </row>
+    <row r="302" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D302" s="15"/>
       <c r="E302" s="15"/>
     </row>
-    <row r="303" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="303" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D303" s="15"/>
       <c r="E303" s="15"/>
       <c r="G303" s="4" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="304" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="304" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D304" s="15"/>
       <c r="E304" s="15"/>
     </row>
-    <row r="305" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="305" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D305" s="15"/>
       <c r="E305" s="15"/>
       <c r="F305" s="15"/>
-      <c r="H305" s="40"/>
-      <c r="I305" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="J305" s="43"/>
-      <c r="K305" s="43"/>
-      <c r="L305" s="43"/>
-      <c r="M305" s="43"/>
-    </row>
-    <row r="306" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H305" s="39"/>
+      <c r="I305" s="74" t="s">
+        <v>166</v>
+      </c>
+      <c r="J305" s="74"/>
+      <c r="K305" s="74"/>
+      <c r="L305" s="74"/>
+      <c r="M305" s="74"/>
+    </row>
+    <row r="306" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D306" s="15"/>
       <c r="E306" s="15"/>
       <c r="F306" s="15"/>
-      <c r="H306" s="44" t="s">
-        <v>175</v>
-      </c>
-      <c r="I306" s="39"/>
-      <c r="J306" s="39" t="s">
+      <c r="H306" s="101" t="s">
+        <v>174</v>
+      </c>
+      <c r="I306" s="38"/>
+      <c r="J306" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="K306" s="38" t="s">
         <v>169</v>
       </c>
-      <c r="K306" s="39" t="s">
-        <v>170</v>
-      </c>
-      <c r="L306" s="39" t="s">
+      <c r="L306" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="M306" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="M306" s="39" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="307" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="307" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D307" s="15"/>
       <c r="E307" s="15"/>
       <c r="F307" s="15"/>
-      <c r="H307" s="44"/>
-      <c r="I307" s="39" t="s">
-        <v>177</v>
-      </c>
-      <c r="J307" s="41" t="s">
-        <v>184</v>
-      </c>
-      <c r="K307" s="41" t="s">
-        <v>184</v>
-      </c>
-      <c r="L307" s="41" t="s">
-        <v>184</v>
-      </c>
-      <c r="M307" s="41" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="308" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H307" s="101"/>
+      <c r="I307" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="J307" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="K307" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="L307" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="M307" s="40" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="308" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D308" s="15"/>
       <c r="E308" s="15"/>
       <c r="F308" s="15"/>
-      <c r="H308" s="44"/>
-      <c r="I308" s="39" t="s">
-        <v>179</v>
-      </c>
-      <c r="J308" s="41" t="s">
+      <c r="H308" s="101"/>
+      <c r="I308" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="J308" s="40" t="s">
+        <v>184</v>
+      </c>
+      <c r="K308" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="L308" s="40" t="s">
+        <v>184</v>
+      </c>
+      <c r="M308" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="P308" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="K308" s="41" t="s">
-        <v>184</v>
-      </c>
-      <c r="L308" s="41" t="s">
-        <v>185</v>
-      </c>
-      <c r="M308" s="41" t="s">
-        <v>184</v>
-      </c>
-      <c r="P308" s="4" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="309" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="309" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D309" s="15"/>
       <c r="E309" s="15"/>
       <c r="F309" s="15"/>
-      <c r="H309" s="44"/>
-      <c r="I309" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="J309" s="41" t="s">
-        <v>185</v>
-      </c>
-      <c r="K309" s="41" t="s">
+      <c r="H309" s="101"/>
+      <c r="I309" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="J309" s="40" t="s">
         <v>184</v>
       </c>
-      <c r="L309" s="41" t="s">
-        <v>185</v>
-      </c>
-      <c r="M309" s="41" t="s">
-        <v>185</v>
+      <c r="K309" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="L309" s="40" t="s">
+        <v>184</v>
+      </c>
+      <c r="M309" s="40" t="s">
+        <v>184</v>
       </c>
       <c r="P309" s="4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="310" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="310" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D310" s="15"/>
       <c r="E310" s="15"/>
       <c r="F310" s="15"/>
       <c r="H310" s="15"/>
       <c r="I310" s="15"/>
-      <c r="J310" s="42"/>
-      <c r="K310" s="42"/>
-      <c r="L310" s="42"/>
-      <c r="M310" s="42"/>
-    </row>
-    <row r="311" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J310" s="41"/>
+      <c r="K310" s="41"/>
+      <c r="L310" s="41"/>
+      <c r="M310" s="41"/>
+    </row>
+    <row r="311" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D311" s="15"/>
       <c r="E311" s="15"/>
       <c r="G311" s="22" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="312" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="312" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D312" s="15"/>
       <c r="E312" s="15"/>
       <c r="G312" s="22"/>
     </row>
-    <row r="313" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="313" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D313" s="15"/>
       <c r="E313" s="15"/>
     </row>
-    <row r="314" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="314" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D314" s="15"/>
       <c r="E314" s="15"/>
     </row>
-    <row r="315" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="315" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D315" s="15"/>
       <c r="E315" s="15"/>
     </row>
-    <row r="316" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="316" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D316" s="15"/>
       <c r="E316" s="15"/>
     </row>
-    <row r="317" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="317" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D317" s="15"/>
       <c r="E317" s="15"/>
     </row>
-    <row r="318" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="318" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D318" s="15"/>
       <c r="E318" s="15"/>
     </row>
-    <row r="319" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="319" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D319" s="15"/>
       <c r="E319" s="15"/>
     </row>
-    <row r="320" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="320" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D320" s="15"/>
       <c r="E320" s="15"/>
     </row>
-    <row r="321" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="321" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D321" s="15"/>
       <c r="E321" s="15"/>
     </row>
-    <row r="322" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="322" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D322" s="15"/>
       <c r="E322" s="15"/>
     </row>
-    <row r="323" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="323" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D323" s="15"/>
     </row>
-    <row r="324" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="324" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D324" s="15" t="str">
         <f>$C$7&amp;"3."</f>
         <v>7.5.3.</v>
@@ -6272,16 +6246,16 @@
         <v>19</v>
       </c>
     </row>
-    <row r="325" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="325" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D325" s="15"/>
       <c r="E325" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="326" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="326" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D326" s="15"/>
     </row>
-    <row r="327" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="327" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D327" s="15"/>
       <c r="E327" s="23"/>
       <c r="F327" s="24"/>
@@ -6291,33 +6265,33 @@
       <c r="J327" s="24"/>
       <c r="K327" s="24"/>
       <c r="L327" s="25"/>
-      <c r="M327" s="46" t="s">
+      <c r="M327" s="70" t="s">
         <v>84</v>
       </c>
-      <c r="N327" s="46"/>
-      <c r="O327" s="46"/>
-      <c r="P327" s="46"/>
-      <c r="Q327" s="46"/>
-      <c r="R327" s="46"/>
-      <c r="S327" s="46"/>
-      <c r="T327" s="43" t="s">
+      <c r="N327" s="70"/>
+      <c r="O327" s="70"/>
+      <c r="P327" s="70"/>
+      <c r="Q327" s="70"/>
+      <c r="R327" s="70"/>
+      <c r="S327" s="70"/>
+      <c r="T327" s="74" t="s">
         <v>91</v>
       </c>
-      <c r="U327" s="43"/>
-      <c r="V327" s="43"/>
-      <c r="W327" s="43"/>
-      <c r="X327" s="43"/>
-      <c r="Y327" s="43"/>
-      <c r="Z327" s="43"/>
-      <c r="AA327" s="43"/>
-      <c r="AB327" s="43"/>
-      <c r="AC327" s="43"/>
-      <c r="AD327" s="43"/>
-      <c r="AE327" s="43"/>
-      <c r="AF327" s="43"/>
-      <c r="AG327" s="43"/>
-    </row>
-    <row r="328" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U327" s="74"/>
+      <c r="V327" s="74"/>
+      <c r="W327" s="74"/>
+      <c r="X327" s="74"/>
+      <c r="Y327" s="74"/>
+      <c r="Z327" s="74"/>
+      <c r="AA327" s="74"/>
+      <c r="AB327" s="74"/>
+      <c r="AC327" s="74"/>
+      <c r="AD327" s="74"/>
+      <c r="AE327" s="74"/>
+      <c r="AF327" s="74"/>
+      <c r="AG327" s="74"/>
+    </row>
+    <row r="328" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D328" s="15"/>
       <c r="E328" s="26"/>
       <c r="F328" s="27"/>
@@ -6327,814 +6301,879 @@
       <c r="J328" s="27"/>
       <c r="K328" s="27"/>
       <c r="L328" s="28"/>
-      <c r="M328" s="46" t="s">
+      <c r="M328" s="70" t="s">
         <v>78</v>
       </c>
-      <c r="N328" s="46"/>
-      <c r="O328" s="46"/>
-      <c r="P328" s="46"/>
-      <c r="Q328" s="46"/>
-      <c r="R328" s="46"/>
-      <c r="S328" s="46"/>
-      <c r="T328" s="46" t="s">
+      <c r="N328" s="70"/>
+      <c r="O328" s="70"/>
+      <c r="P328" s="70"/>
+      <c r="Q328" s="70"/>
+      <c r="R328" s="70"/>
+      <c r="S328" s="70"/>
+      <c r="T328" s="70" t="s">
         <v>146</v>
       </c>
-      <c r="U328" s="46"/>
-      <c r="V328" s="46"/>
-      <c r="W328" s="46"/>
-      <c r="X328" s="46"/>
-      <c r="Y328" s="46"/>
-      <c r="Z328" s="46"/>
-      <c r="AA328" s="46"/>
-      <c r="AB328" s="46" t="s">
+      <c r="U328" s="70"/>
+      <c r="V328" s="70"/>
+      <c r="W328" s="70"/>
+      <c r="X328" s="70"/>
+      <c r="Y328" s="70"/>
+      <c r="Z328" s="70"/>
+      <c r="AA328" s="70"/>
+      <c r="AB328" s="70" t="s">
         <v>147</v>
       </c>
-      <c r="AC328" s="46"/>
-      <c r="AD328" s="46"/>
-      <c r="AE328" s="46"/>
-      <c r="AF328" s="46"/>
-      <c r="AG328" s="46"/>
-    </row>
-    <row r="329" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AC328" s="70"/>
+      <c r="AD328" s="70"/>
+      <c r="AE328" s="70"/>
+      <c r="AF328" s="70"/>
+      <c r="AG328" s="70"/>
+    </row>
+    <row r="329" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D329" s="15"/>
-      <c r="E329" s="75" t="s">
+      <c r="E329" s="67" t="s">
         <v>143</v>
       </c>
-      <c r="F329" s="75"/>
-      <c r="G329" s="75"/>
-      <c r="H329" s="75"/>
-      <c r="I329" s="75"/>
-      <c r="J329" s="75"/>
-      <c r="K329" s="54" t="s">
+      <c r="F329" s="67"/>
+      <c r="G329" s="67"/>
+      <c r="H329" s="67"/>
+      <c r="I329" s="67"/>
+      <c r="J329" s="67"/>
+      <c r="K329" s="71" t="s">
         <v>74</v>
       </c>
-      <c r="L329" s="55"/>
-      <c r="M329" s="50" t="s">
+      <c r="L329" s="72"/>
+      <c r="M329" s="96" t="s">
         <v>105</v>
       </c>
-      <c r="N329" s="50"/>
-      <c r="O329" s="50"/>
-      <c r="P329" s="50"/>
-      <c r="Q329" s="50"/>
-      <c r="R329" s="50"/>
-      <c r="S329" s="50"/>
-      <c r="T329" s="65" t="s">
+      <c r="N329" s="96"/>
+      <c r="O329" s="96"/>
+      <c r="P329" s="96"/>
+      <c r="Q329" s="96"/>
+      <c r="R329" s="96"/>
+      <c r="S329" s="96"/>
+      <c r="T329" s="84" t="s">
         <v>99</v>
       </c>
-      <c r="U329" s="66"/>
-      <c r="V329" s="66"/>
-      <c r="W329" s="66"/>
-      <c r="X329" s="66"/>
-      <c r="Y329" s="66"/>
-      <c r="Z329" s="66"/>
-      <c r="AA329" s="67"/>
-      <c r="AB329" s="56" t="s">
+      <c r="U329" s="85"/>
+      <c r="V329" s="85"/>
+      <c r="W329" s="85"/>
+      <c r="X329" s="85"/>
+      <c r="Y329" s="85"/>
+      <c r="Z329" s="85"/>
+      <c r="AA329" s="86"/>
+      <c r="AB329" s="75" t="s">
         <v>79</v>
       </c>
-      <c r="AC329" s="57"/>
-      <c r="AD329" s="57"/>
-      <c r="AE329" s="57"/>
-      <c r="AF329" s="57"/>
-      <c r="AG329" s="58"/>
-    </row>
-    <row r="330" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AC329" s="76"/>
+      <c r="AD329" s="76"/>
+      <c r="AE329" s="76"/>
+      <c r="AF329" s="76"/>
+      <c r="AG329" s="77"/>
+    </row>
+    <row r="330" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D330" s="15"/>
-      <c r="E330" s="76"/>
-      <c r="F330" s="76"/>
-      <c r="G330" s="76"/>
-      <c r="H330" s="76"/>
-      <c r="I330" s="76"/>
-      <c r="J330" s="76"/>
-      <c r="K330" s="54" t="s">
+      <c r="E330" s="68"/>
+      <c r="F330" s="68"/>
+      <c r="G330" s="68"/>
+      <c r="H330" s="68"/>
+      <c r="I330" s="68"/>
+      <c r="J330" s="68"/>
+      <c r="K330" s="71" t="s">
         <v>106</v>
       </c>
-      <c r="L330" s="55"/>
-      <c r="M330" s="50" t="s">
+      <c r="L330" s="72"/>
+      <c r="M330" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="N330" s="50"/>
-      <c r="O330" s="50"/>
-      <c r="P330" s="50"/>
-      <c r="Q330" s="50"/>
-      <c r="R330" s="50"/>
-      <c r="S330" s="50"/>
-      <c r="T330" s="68"/>
-      <c r="U330" s="69"/>
-      <c r="V330" s="69"/>
-      <c r="W330" s="69"/>
-      <c r="X330" s="69"/>
-      <c r="Y330" s="69"/>
-      <c r="Z330" s="69"/>
-      <c r="AA330" s="70"/>
-      <c r="AB330" s="59"/>
-      <c r="AC330" s="60"/>
-      <c r="AD330" s="60"/>
-      <c r="AE330" s="60"/>
-      <c r="AF330" s="60"/>
-      <c r="AG330" s="61"/>
-    </row>
-    <row r="331" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="N330" s="96"/>
+      <c r="O330" s="96"/>
+      <c r="P330" s="96"/>
+      <c r="Q330" s="96"/>
+      <c r="R330" s="96"/>
+      <c r="S330" s="96"/>
+      <c r="T330" s="87"/>
+      <c r="U330" s="88"/>
+      <c r="V330" s="88"/>
+      <c r="W330" s="88"/>
+      <c r="X330" s="88"/>
+      <c r="Y330" s="88"/>
+      <c r="Z330" s="88"/>
+      <c r="AA330" s="89"/>
+      <c r="AB330" s="78"/>
+      <c r="AC330" s="79"/>
+      <c r="AD330" s="79"/>
+      <c r="AE330" s="79"/>
+      <c r="AF330" s="79"/>
+      <c r="AG330" s="80"/>
+    </row>
+    <row r="331" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D331" s="15"/>
-      <c r="E331" s="76"/>
-      <c r="F331" s="76"/>
-      <c r="G331" s="76"/>
-      <c r="H331" s="76"/>
-      <c r="I331" s="76"/>
-      <c r="J331" s="76"/>
-      <c r="K331" s="54" t="s">
+      <c r="E331" s="68"/>
+      <c r="F331" s="68"/>
+      <c r="G331" s="68"/>
+      <c r="H331" s="68"/>
+      <c r="I331" s="68"/>
+      <c r="J331" s="68"/>
+      <c r="K331" s="71" t="s">
         <v>107</v>
       </c>
-      <c r="L331" s="55"/>
-      <c r="M331" s="50" t="s">
+      <c r="L331" s="72"/>
+      <c r="M331" s="96" t="s">
         <v>108</v>
       </c>
-      <c r="N331" s="50"/>
-      <c r="O331" s="50"/>
-      <c r="P331" s="50"/>
-      <c r="Q331" s="50"/>
-      <c r="R331" s="50"/>
-      <c r="S331" s="50"/>
-      <c r="T331" s="68"/>
-      <c r="U331" s="69"/>
-      <c r="V331" s="69"/>
-      <c r="W331" s="69"/>
-      <c r="X331" s="69"/>
-      <c r="Y331" s="69"/>
-      <c r="Z331" s="69"/>
-      <c r="AA331" s="70"/>
-      <c r="AB331" s="59"/>
-      <c r="AC331" s="60"/>
-      <c r="AD331" s="60"/>
-      <c r="AE331" s="60"/>
-      <c r="AF331" s="60"/>
-      <c r="AG331" s="61"/>
-    </row>
-    <row r="332" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="N331" s="96"/>
+      <c r="O331" s="96"/>
+      <c r="P331" s="96"/>
+      <c r="Q331" s="96"/>
+      <c r="R331" s="96"/>
+      <c r="S331" s="96"/>
+      <c r="T331" s="87"/>
+      <c r="U331" s="88"/>
+      <c r="V331" s="88"/>
+      <c r="W331" s="88"/>
+      <c r="X331" s="88"/>
+      <c r="Y331" s="88"/>
+      <c r="Z331" s="88"/>
+      <c r="AA331" s="89"/>
+      <c r="AB331" s="78"/>
+      <c r="AC331" s="79"/>
+      <c r="AD331" s="79"/>
+      <c r="AE331" s="79"/>
+      <c r="AF331" s="79"/>
+      <c r="AG331" s="80"/>
+    </row>
+    <row r="332" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D332" s="15"/>
-      <c r="E332" s="77"/>
-      <c r="F332" s="77"/>
-      <c r="G332" s="77"/>
-      <c r="H332" s="77"/>
-      <c r="I332" s="77"/>
-      <c r="J332" s="77"/>
-      <c r="K332" s="54" t="s">
+      <c r="E332" s="69"/>
+      <c r="F332" s="69"/>
+      <c r="G332" s="69"/>
+      <c r="H332" s="69"/>
+      <c r="I332" s="69"/>
+      <c r="J332" s="69"/>
+      <c r="K332" s="71" t="s">
         <v>76</v>
       </c>
-      <c r="L332" s="55"/>
-      <c r="M332" s="50" t="s">
+      <c r="L332" s="72"/>
+      <c r="M332" s="96" t="s">
         <v>110</v>
       </c>
-      <c r="N332" s="50"/>
-      <c r="O332" s="50"/>
-      <c r="P332" s="50"/>
-      <c r="Q332" s="50"/>
-      <c r="R332" s="50"/>
-      <c r="S332" s="50"/>
-      <c r="T332" s="71"/>
-      <c r="U332" s="72"/>
-      <c r="V332" s="72"/>
-      <c r="W332" s="72"/>
-      <c r="X332" s="72"/>
-      <c r="Y332" s="72"/>
-      <c r="Z332" s="72"/>
-      <c r="AA332" s="73"/>
-      <c r="AB332" s="62"/>
-      <c r="AC332" s="63"/>
-      <c r="AD332" s="63"/>
-      <c r="AE332" s="63"/>
-      <c r="AF332" s="63"/>
-      <c r="AG332" s="64"/>
-    </row>
-    <row r="333" spans="4:33" ht="29.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="N332" s="96"/>
+      <c r="O332" s="96"/>
+      <c r="P332" s="96"/>
+      <c r="Q332" s="96"/>
+      <c r="R332" s="96"/>
+      <c r="S332" s="96"/>
+      <c r="T332" s="90"/>
+      <c r="U332" s="91"/>
+      <c r="V332" s="91"/>
+      <c r="W332" s="91"/>
+      <c r="X332" s="91"/>
+      <c r="Y332" s="91"/>
+      <c r="Z332" s="91"/>
+      <c r="AA332" s="92"/>
+      <c r="AB332" s="81"/>
+      <c r="AC332" s="82"/>
+      <c r="AD332" s="82"/>
+      <c r="AE332" s="82"/>
+      <c r="AF332" s="82"/>
+      <c r="AG332" s="83"/>
+    </row>
+    <row r="333" spans="4:33" ht="29.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D333" s="15"/>
-      <c r="E333" s="54" t="s">
+      <c r="E333" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="F333" s="74"/>
-      <c r="G333" s="74"/>
-      <c r="H333" s="74"/>
-      <c r="I333" s="74"/>
-      <c r="J333" s="74"/>
-      <c r="K333" s="74"/>
-      <c r="L333" s="55"/>
-      <c r="M333" s="50" t="s">
+      <c r="F333" s="73"/>
+      <c r="G333" s="73"/>
+      <c r="H333" s="73"/>
+      <c r="I333" s="73"/>
+      <c r="J333" s="73"/>
+      <c r="K333" s="73"/>
+      <c r="L333" s="72"/>
+      <c r="M333" s="96" t="s">
         <v>108</v>
       </c>
-      <c r="N333" s="50"/>
-      <c r="O333" s="50"/>
-      <c r="P333" s="50"/>
-      <c r="Q333" s="50"/>
-      <c r="R333" s="50"/>
-      <c r="S333" s="50"/>
-      <c r="T333" s="51" t="s">
+      <c r="N333" s="96"/>
+      <c r="O333" s="96"/>
+      <c r="P333" s="96"/>
+      <c r="Q333" s="96"/>
+      <c r="R333" s="96"/>
+      <c r="S333" s="96"/>
+      <c r="T333" s="97" t="s">
         <v>100</v>
       </c>
-      <c r="U333" s="52"/>
-      <c r="V333" s="52"/>
-      <c r="W333" s="52"/>
-      <c r="X333" s="52"/>
-      <c r="Y333" s="52"/>
-      <c r="Z333" s="52"/>
-      <c r="AA333" s="53"/>
-      <c r="AB333" s="50" t="s">
+      <c r="U333" s="98"/>
+      <c r="V333" s="98"/>
+      <c r="W333" s="98"/>
+      <c r="X333" s="98"/>
+      <c r="Y333" s="98"/>
+      <c r="Z333" s="98"/>
+      <c r="AA333" s="99"/>
+      <c r="AB333" s="96" t="s">
         <v>79</v>
       </c>
-      <c r="AC333" s="50"/>
-      <c r="AD333" s="50"/>
-      <c r="AE333" s="50"/>
-      <c r="AF333" s="50"/>
-      <c r="AG333" s="50"/>
-    </row>
-    <row r="334" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AC333" s="96"/>
+      <c r="AD333" s="96"/>
+      <c r="AE333" s="96"/>
+      <c r="AF333" s="96"/>
+      <c r="AG333" s="96"/>
+    </row>
+    <row r="334" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D334" s="15"/>
-      <c r="E334" s="54" t="s">
+      <c r="E334" s="71" t="s">
         <v>80</v>
       </c>
-      <c r="F334" s="74"/>
-      <c r="G334" s="74"/>
-      <c r="H334" s="74"/>
-      <c r="I334" s="74"/>
-      <c r="J334" s="74"/>
-      <c r="K334" s="74"/>
-      <c r="L334" s="55"/>
-      <c r="M334" s="50" t="s">
+      <c r="F334" s="73"/>
+      <c r="G334" s="73"/>
+      <c r="H334" s="73"/>
+      <c r="I334" s="73"/>
+      <c r="J334" s="73"/>
+      <c r="K334" s="73"/>
+      <c r="L334" s="72"/>
+      <c r="M334" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="N334" s="50"/>
-      <c r="O334" s="50"/>
-      <c r="P334" s="50"/>
-      <c r="Q334" s="50"/>
-      <c r="R334" s="50"/>
-      <c r="S334" s="50"/>
-      <c r="T334" s="50" t="s">
+      <c r="N334" s="96"/>
+      <c r="O334" s="96"/>
+      <c r="P334" s="96"/>
+      <c r="Q334" s="96"/>
+      <c r="R334" s="96"/>
+      <c r="S334" s="96"/>
+      <c r="T334" s="96" t="s">
         <v>81</v>
       </c>
-      <c r="U334" s="50"/>
-      <c r="V334" s="50"/>
-      <c r="W334" s="50"/>
-      <c r="X334" s="50"/>
-      <c r="Y334" s="50"/>
-      <c r="Z334" s="50"/>
-      <c r="AA334" s="50"/>
-      <c r="AB334" s="50" t="s">
+      <c r="U334" s="96"/>
+      <c r="V334" s="96"/>
+      <c r="W334" s="96"/>
+      <c r="X334" s="96"/>
+      <c r="Y334" s="96"/>
+      <c r="Z334" s="96"/>
+      <c r="AA334" s="96"/>
+      <c r="AB334" s="96" t="s">
         <v>82</v>
       </c>
-      <c r="AC334" s="50"/>
-      <c r="AD334" s="50"/>
-      <c r="AE334" s="50"/>
-      <c r="AF334" s="50"/>
-      <c r="AG334" s="50"/>
-    </row>
-    <row r="335" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AC334" s="96"/>
+      <c r="AD334" s="96"/>
+      <c r="AE334" s="96"/>
+      <c r="AF334" s="96"/>
+      <c r="AG334" s="96"/>
+    </row>
+    <row r="335" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D335" s="15"/>
-      <c r="E335" s="75" t="s">
+      <c r="E335" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="F335" s="75"/>
-      <c r="G335" s="75"/>
-      <c r="H335" s="75"/>
-      <c r="I335" s="75"/>
-      <c r="J335" s="75"/>
-      <c r="K335" s="54" t="s">
+      <c r="F335" s="67"/>
+      <c r="G335" s="67"/>
+      <c r="H335" s="67"/>
+      <c r="I335" s="67"/>
+      <c r="J335" s="67"/>
+      <c r="K335" s="71" t="s">
         <v>74</v>
       </c>
-      <c r="L335" s="55"/>
-      <c r="M335" s="47" t="s">
+      <c r="L335" s="72"/>
+      <c r="M335" s="93" t="s">
         <v>85</v>
       </c>
-      <c r="N335" s="48"/>
-      <c r="O335" s="48"/>
-      <c r="P335" s="48"/>
-      <c r="Q335" s="48"/>
-      <c r="R335" s="48"/>
-      <c r="S335" s="49"/>
-      <c r="T335" s="47" t="s">
+      <c r="N335" s="94"/>
+      <c r="O335" s="94"/>
+      <c r="P335" s="94"/>
+      <c r="Q335" s="94"/>
+      <c r="R335" s="94"/>
+      <c r="S335" s="95"/>
+      <c r="T335" s="93" t="s">
         <v>85</v>
       </c>
-      <c r="U335" s="48"/>
-      <c r="V335" s="48"/>
-      <c r="W335" s="48"/>
-      <c r="X335" s="48"/>
-      <c r="Y335" s="48"/>
-      <c r="Z335" s="48"/>
-      <c r="AA335" s="48"/>
-      <c r="AB335" s="48"/>
-      <c r="AC335" s="48"/>
-      <c r="AD335" s="48"/>
-      <c r="AE335" s="48"/>
-      <c r="AF335" s="48"/>
-      <c r="AG335" s="49"/>
-    </row>
-    <row r="336" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U335" s="94"/>
+      <c r="V335" s="94"/>
+      <c r="W335" s="94"/>
+      <c r="X335" s="94"/>
+      <c r="Y335" s="94"/>
+      <c r="Z335" s="94"/>
+      <c r="AA335" s="94"/>
+      <c r="AB335" s="94"/>
+      <c r="AC335" s="94"/>
+      <c r="AD335" s="94"/>
+      <c r="AE335" s="94"/>
+      <c r="AF335" s="94"/>
+      <c r="AG335" s="95"/>
+    </row>
+    <row r="336" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D336" s="15"/>
-      <c r="E336" s="76"/>
-      <c r="F336" s="76"/>
-      <c r="G336" s="76"/>
-      <c r="H336" s="76"/>
-      <c r="I336" s="76"/>
-      <c r="J336" s="76"/>
-      <c r="K336" s="54" t="s">
+      <c r="E336" s="68"/>
+      <c r="F336" s="68"/>
+      <c r="G336" s="68"/>
+      <c r="H336" s="68"/>
+      <c r="I336" s="68"/>
+      <c r="J336" s="68"/>
+      <c r="K336" s="71" t="s">
         <v>75</v>
       </c>
-      <c r="L336" s="55"/>
-      <c r="M336" s="47"/>
-      <c r="N336" s="48"/>
-      <c r="O336" s="48"/>
-      <c r="P336" s="48"/>
-      <c r="Q336" s="48"/>
-      <c r="R336" s="48"/>
-      <c r="S336" s="49"/>
-      <c r="T336" s="47"/>
-      <c r="U336" s="48"/>
-      <c r="V336" s="48"/>
-      <c r="W336" s="48"/>
-      <c r="X336" s="48"/>
-      <c r="Y336" s="48"/>
-      <c r="Z336" s="48"/>
-      <c r="AA336" s="48"/>
-      <c r="AB336" s="48"/>
-      <c r="AC336" s="48"/>
-      <c r="AD336" s="48"/>
-      <c r="AE336" s="48"/>
-      <c r="AF336" s="48"/>
-      <c r="AG336" s="49"/>
-    </row>
-    <row r="337" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L336" s="72"/>
+      <c r="M336" s="93"/>
+      <c r="N336" s="94"/>
+      <c r="O336" s="94"/>
+      <c r="P336" s="94"/>
+      <c r="Q336" s="94"/>
+      <c r="R336" s="94"/>
+      <c r="S336" s="95"/>
+      <c r="T336" s="93"/>
+      <c r="U336" s="94"/>
+      <c r="V336" s="94"/>
+      <c r="W336" s="94"/>
+      <c r="X336" s="94"/>
+      <c r="Y336" s="94"/>
+      <c r="Z336" s="94"/>
+      <c r="AA336" s="94"/>
+      <c r="AB336" s="94"/>
+      <c r="AC336" s="94"/>
+      <c r="AD336" s="94"/>
+      <c r="AE336" s="94"/>
+      <c r="AF336" s="94"/>
+      <c r="AG336" s="95"/>
+    </row>
+    <row r="337" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D337" s="15"/>
-      <c r="E337" s="77"/>
-      <c r="F337" s="77"/>
-      <c r="G337" s="77"/>
-      <c r="H337" s="77"/>
-      <c r="I337" s="77"/>
-      <c r="J337" s="77"/>
-      <c r="K337" s="54" t="s">
+      <c r="E337" s="69"/>
+      <c r="F337" s="69"/>
+      <c r="G337" s="69"/>
+      <c r="H337" s="69"/>
+      <c r="I337" s="69"/>
+      <c r="J337" s="69"/>
+      <c r="K337" s="71" t="s">
         <v>76</v>
       </c>
-      <c r="L337" s="55"/>
-      <c r="M337" s="47"/>
-      <c r="N337" s="48"/>
-      <c r="O337" s="48"/>
-      <c r="P337" s="48"/>
-      <c r="Q337" s="48"/>
-      <c r="R337" s="48"/>
-      <c r="S337" s="49"/>
-      <c r="T337" s="47"/>
-      <c r="U337" s="48"/>
-      <c r="V337" s="48"/>
-      <c r="W337" s="48"/>
-      <c r="X337" s="48"/>
-      <c r="Y337" s="48"/>
-      <c r="Z337" s="48"/>
-      <c r="AA337" s="48"/>
-      <c r="AB337" s="48"/>
-      <c r="AC337" s="48"/>
-      <c r="AD337" s="48"/>
-      <c r="AE337" s="48"/>
-      <c r="AF337" s="48"/>
-      <c r="AG337" s="49"/>
-    </row>
-    <row r="338" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L337" s="72"/>
+      <c r="M337" s="93"/>
+      <c r="N337" s="94"/>
+      <c r="O337" s="94"/>
+      <c r="P337" s="94"/>
+      <c r="Q337" s="94"/>
+      <c r="R337" s="94"/>
+      <c r="S337" s="95"/>
+      <c r="T337" s="93"/>
+      <c r="U337" s="94"/>
+      <c r="V337" s="94"/>
+      <c r="W337" s="94"/>
+      <c r="X337" s="94"/>
+      <c r="Y337" s="94"/>
+      <c r="Z337" s="94"/>
+      <c r="AA337" s="94"/>
+      <c r="AB337" s="94"/>
+      <c r="AC337" s="94"/>
+      <c r="AD337" s="94"/>
+      <c r="AE337" s="94"/>
+      <c r="AF337" s="94"/>
+      <c r="AG337" s="95"/>
+    </row>
+    <row r="338" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D338" s="15"/>
     </row>
-    <row r="339" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="339" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D339" s="15"/>
     </row>
-    <row r="340" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="340" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D340" s="15"/>
     </row>
-    <row r="341" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="I305:M305"/>
+    <mergeCell ref="H306:H309"/>
+    <mergeCell ref="H299:J299"/>
+    <mergeCell ref="K299:U299"/>
+    <mergeCell ref="H300:J300"/>
+    <mergeCell ref="K300:U300"/>
+    <mergeCell ref="H301:J301"/>
+    <mergeCell ref="K301:U301"/>
+    <mergeCell ref="H294:J294"/>
+    <mergeCell ref="K294:U294"/>
+    <mergeCell ref="H295:J295"/>
+    <mergeCell ref="K295:U295"/>
+    <mergeCell ref="H298:J298"/>
+    <mergeCell ref="K298:U298"/>
+    <mergeCell ref="H291:J291"/>
+    <mergeCell ref="K291:U291"/>
+    <mergeCell ref="H292:J292"/>
+    <mergeCell ref="K292:U292"/>
+    <mergeCell ref="H293:J293"/>
+    <mergeCell ref="K293:U293"/>
+    <mergeCell ref="H286:K286"/>
+    <mergeCell ref="L286:AA287"/>
+    <mergeCell ref="H287:K287"/>
+    <mergeCell ref="H288:K288"/>
+    <mergeCell ref="L288:AA288"/>
+    <mergeCell ref="H283:K283"/>
+    <mergeCell ref="L283:AA283"/>
+    <mergeCell ref="H284:K284"/>
+    <mergeCell ref="L284:AA285"/>
+    <mergeCell ref="H285:K285"/>
+    <mergeCell ref="M335:S337"/>
+    <mergeCell ref="T335:AG337"/>
+    <mergeCell ref="M329:S329"/>
+    <mergeCell ref="M330:S330"/>
+    <mergeCell ref="M332:S332"/>
+    <mergeCell ref="M333:S333"/>
+    <mergeCell ref="M334:S334"/>
+    <mergeCell ref="AB333:AG333"/>
+    <mergeCell ref="AB334:AG334"/>
+    <mergeCell ref="T333:AA333"/>
+    <mergeCell ref="T334:AA334"/>
+    <mergeCell ref="M331:S331"/>
+    <mergeCell ref="T327:AG327"/>
+    <mergeCell ref="M327:S327"/>
+    <mergeCell ref="K329:L329"/>
+    <mergeCell ref="K330:L330"/>
+    <mergeCell ref="K332:L332"/>
+    <mergeCell ref="AB328:AG328"/>
+    <mergeCell ref="T328:AA328"/>
+    <mergeCell ref="AB329:AG332"/>
+    <mergeCell ref="T329:AA332"/>
+    <mergeCell ref="K331:L331"/>
+    <mergeCell ref="K335:L335"/>
+    <mergeCell ref="K336:L336"/>
+    <mergeCell ref="K337:L337"/>
+    <mergeCell ref="E333:L333"/>
+    <mergeCell ref="E334:L334"/>
+    <mergeCell ref="E335:J335"/>
+    <mergeCell ref="E336:J336"/>
+    <mergeCell ref="E337:J337"/>
+    <mergeCell ref="E329:J329"/>
+    <mergeCell ref="E330:J330"/>
+    <mergeCell ref="E332:J332"/>
+    <mergeCell ref="M328:S328"/>
+    <mergeCell ref="E331:J331"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="J22:M22"/>
     <mergeCell ref="AF3:AI3"/>
@@ -7148,71 +7187,6 @@
     <mergeCell ref="AF2:AI2"/>
     <mergeCell ref="E3:O3"/>
     <mergeCell ref="AA3:AE3"/>
-    <mergeCell ref="E329:J329"/>
-    <mergeCell ref="E330:J330"/>
-    <mergeCell ref="E332:J332"/>
-    <mergeCell ref="M328:S328"/>
-    <mergeCell ref="E331:J331"/>
-    <mergeCell ref="K335:L335"/>
-    <mergeCell ref="K336:L336"/>
-    <mergeCell ref="K337:L337"/>
-    <mergeCell ref="E333:L333"/>
-    <mergeCell ref="E334:L334"/>
-    <mergeCell ref="E335:J335"/>
-    <mergeCell ref="E336:J336"/>
-    <mergeCell ref="E337:J337"/>
-    <mergeCell ref="T327:AG327"/>
-    <mergeCell ref="M327:S327"/>
-    <mergeCell ref="K329:L329"/>
-    <mergeCell ref="K330:L330"/>
-    <mergeCell ref="K332:L332"/>
-    <mergeCell ref="AB328:AG328"/>
-    <mergeCell ref="T328:AA328"/>
-    <mergeCell ref="AB329:AG332"/>
-    <mergeCell ref="T329:AA332"/>
-    <mergeCell ref="K331:L331"/>
-    <mergeCell ref="M335:S337"/>
-    <mergeCell ref="T335:AG337"/>
-    <mergeCell ref="M329:S329"/>
-    <mergeCell ref="M330:S330"/>
-    <mergeCell ref="M332:S332"/>
-    <mergeCell ref="M333:S333"/>
-    <mergeCell ref="M334:S334"/>
-    <mergeCell ref="AB333:AG333"/>
-    <mergeCell ref="AB334:AG334"/>
-    <mergeCell ref="T333:AA333"/>
-    <mergeCell ref="T334:AA334"/>
-    <mergeCell ref="M331:S331"/>
-    <mergeCell ref="H283:K283"/>
-    <mergeCell ref="L283:AA283"/>
-    <mergeCell ref="H284:K284"/>
-    <mergeCell ref="L284:AA285"/>
-    <mergeCell ref="H285:K285"/>
-    <mergeCell ref="H286:K286"/>
-    <mergeCell ref="L286:AA287"/>
-    <mergeCell ref="H287:K287"/>
-    <mergeCell ref="H288:K288"/>
-    <mergeCell ref="L288:AA288"/>
-    <mergeCell ref="H291:J291"/>
-    <mergeCell ref="K291:U291"/>
-    <mergeCell ref="H292:J292"/>
-    <mergeCell ref="K292:U292"/>
-    <mergeCell ref="H293:J293"/>
-    <mergeCell ref="K293:U293"/>
-    <mergeCell ref="H294:J294"/>
-    <mergeCell ref="K294:U294"/>
-    <mergeCell ref="H295:J295"/>
-    <mergeCell ref="K295:U295"/>
-    <mergeCell ref="H298:J298"/>
-    <mergeCell ref="K298:U298"/>
-    <mergeCell ref="I305:M305"/>
-    <mergeCell ref="H306:H309"/>
-    <mergeCell ref="H299:J299"/>
-    <mergeCell ref="K299:U299"/>
-    <mergeCell ref="H300:J300"/>
-    <mergeCell ref="K300:U300"/>
-    <mergeCell ref="H301:J301"/>
-    <mergeCell ref="K301:U301"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <dataValidations disablePrompts="1" count="1">

--- a/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.5.認証・認可.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.5.認証・認可.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFF0B48-F7E1-4237-818A-F0C242FAFBE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C972993C-B034-4999-A4C8-A1AA143B3C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1556,25 +1556,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>Nablarchの認可チェックの詳細に関しては、下記Nablarchガイドの【7.15. 認可チェック】を参照のこと。</t>
-    <rPh sb="9" eb="11">
-      <t>ニンカ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>カキ</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>サンショウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>一般的なフォーム認証方式を採用する。</t>
     <rPh sb="0" eb="3">
       <t>イッパンテキ</t>
@@ -1939,6 +1920,25 @@
   </si>
   <si>
     <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/libraries/permission_check.html</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Nablarchの認可チェックの詳細に関しては、下記Nablarchガイドの【認可チェック】を参照のこと。</t>
+    <rPh sb="9" eb="11">
+      <t>ニンカ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カキ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>サンショウ</t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -2356,6 +2356,114 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2430,114 +2538,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3479,43 +3479,43 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="50"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="86"/>
       <c r="P1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q1" s="2"/>
-      <c r="R1" s="51" t="s">
+      <c r="R1" s="87" t="s">
         <v>88</v>
       </c>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="52"/>
-      <c r="V1" s="52"/>
-      <c r="W1" s="52"/>
-      <c r="X1" s="53"/>
+      <c r="S1" s="88"/>
+      <c r="T1" s="88"/>
+      <c r="U1" s="88"/>
+      <c r="V1" s="88"/>
+      <c r="W1" s="88"/>
+      <c r="X1" s="89"/>
       <c r="Y1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="54"/>
-      <c r="AB1" s="55"/>
-      <c r="AC1" s="55"/>
-      <c r="AD1" s="55"/>
-      <c r="AE1" s="56"/>
-      <c r="AF1" s="45"/>
-      <c r="AG1" s="46"/>
-      <c r="AH1" s="46"/>
-      <c r="AI1" s="47"/>
+      <c r="AA1" s="90"/>
+      <c r="AB1" s="91"/>
+      <c r="AC1" s="91"/>
+      <c r="AD1" s="91"/>
+      <c r="AE1" s="92"/>
+      <c r="AF1" s="81"/>
+      <c r="AG1" s="82"/>
+      <c r="AH1" s="82"/>
+      <c r="AI1" s="83"/>
     </row>
     <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
@@ -3524,43 +3524,43 @@
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="7"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="59"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="94"/>
+      <c r="K2" s="94"/>
+      <c r="L2" s="94"/>
+      <c r="M2" s="94"/>
+      <c r="N2" s="94"/>
+      <c r="O2" s="95"/>
       <c r="P2" s="8" t="s">
         <v>4</v>
       </c>
       <c r="Q2" s="9"/>
-      <c r="R2" s="60" t="s">
+      <c r="R2" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="62"/>
+      <c r="S2" s="97"/>
+      <c r="T2" s="97"/>
+      <c r="U2" s="97"/>
+      <c r="V2" s="97"/>
+      <c r="W2" s="97"/>
+      <c r="X2" s="98"/>
       <c r="Y2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="54"/>
-      <c r="AB2" s="55"/>
-      <c r="AC2" s="55"/>
-      <c r="AD2" s="55"/>
-      <c r="AE2" s="56"/>
-      <c r="AF2" s="45"/>
-      <c r="AG2" s="46"/>
-      <c r="AH2" s="46"/>
-      <c r="AI2" s="47"/>
+      <c r="AA2" s="90"/>
+      <c r="AB2" s="91"/>
+      <c r="AC2" s="91"/>
+      <c r="AD2" s="91"/>
+      <c r="AE2" s="92"/>
+      <c r="AF2" s="81"/>
+      <c r="AG2" s="82"/>
+      <c r="AH2" s="82"/>
+      <c r="AI2" s="83"/>
     </row>
     <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -3569,39 +3569,39 @@
       <c r="B3" s="10"/>
       <c r="C3" s="11"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="66"/>
-      <c r="K3" s="66"/>
-      <c r="L3" s="66"/>
-      <c r="M3" s="66"/>
-      <c r="N3" s="66"/>
-      <c r="O3" s="66"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="102"/>
+      <c r="M3" s="102"/>
+      <c r="N3" s="102"/>
+      <c r="O3" s="102"/>
       <c r="P3" s="12"/>
       <c r="Q3" s="13"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="64"/>
-      <c r="W3" s="64"/>
-      <c r="X3" s="65"/>
+      <c r="R3" s="99"/>
+      <c r="S3" s="100"/>
+      <c r="T3" s="100"/>
+      <c r="U3" s="100"/>
+      <c r="V3" s="100"/>
+      <c r="W3" s="100"/>
+      <c r="X3" s="101"/>
       <c r="Y3" s="12" t="s">
         <v>8</v>
       </c>
       <c r="Z3" s="14"/>
-      <c r="AA3" s="54"/>
-      <c r="AB3" s="55"/>
-      <c r="AC3" s="55"/>
-      <c r="AD3" s="55"/>
-      <c r="AE3" s="56"/>
-      <c r="AF3" s="45"/>
-      <c r="AG3" s="46"/>
-      <c r="AH3" s="46"/>
-      <c r="AI3" s="47"/>
+      <c r="AA3" s="90"/>
+      <c r="AB3" s="91"/>
+      <c r="AC3" s="91"/>
+      <c r="AD3" s="91"/>
+      <c r="AE3" s="92"/>
+      <c r="AF3" s="81"/>
+      <c r="AG3" s="82"/>
+      <c r="AH3" s="82"/>
+      <c r="AI3" s="83"/>
     </row>
     <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3744,12 +3744,12 @@
       <c r="G18" s="30"/>
       <c r="H18" s="30"/>
       <c r="I18" s="30"/>
-      <c r="J18" s="42" t="s">
+      <c r="J18" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="43"/>
-      <c r="L18" s="43"/>
-      <c r="M18" s="44"/>
+      <c r="K18" s="79"/>
+      <c r="L18" s="79"/>
+      <c r="M18" s="80"/>
       <c r="N18" s="30" t="s">
         <v>25</v>
       </c>
@@ -3878,12 +3878,12 @@
       <c r="G22" s="36"/>
       <c r="H22" s="36"/>
       <c r="I22" s="36"/>
-      <c r="J22" s="42" t="s">
+      <c r="J22" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="K22" s="43"/>
-      <c r="L22" s="43"/>
-      <c r="M22" s="44"/>
+      <c r="K22" s="79"/>
+      <c r="L22" s="79"/>
+      <c r="M22" s="80"/>
       <c r="N22" s="36" t="s">
         <v>24</v>
       </c>
@@ -4224,7 +4224,7 @@
     <row r="35" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F35" s="15"/>
       <c r="G35" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4508,13 +4508,13 @@
     <row r="101" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F101" s="15"/>
       <c r="G101" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="102" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F102" s="15"/>
       <c r="G102" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="103" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4854,7 +4854,7 @@
     <row r="177" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F177" s="15"/>
       <c r="I177" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="178" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5567,7 +5567,7 @@
       <c r="D267" s="15"/>
       <c r="E267" s="15"/>
       <c r="G267" s="4" t="s">
-        <v>149</v>
+        <v>189</v>
       </c>
     </row>
     <row r="268" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5577,8 +5577,8 @@
     <row r="269" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D269" s="15"/>
       <c r="E269" s="15"/>
-      <c r="G269" s="102" t="s">
-        <v>189</v>
+      <c r="G269" s="42" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="270" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5606,14 +5606,14 @@
       <c r="D273" s="15"/>
       <c r="E273" s="15"/>
       <c r="G273" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="274" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D274" s="15"/>
       <c r="E274" s="15"/>
       <c r="G274" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="275" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5666,172 +5666,172 @@
       <c r="D282" s="15"/>
       <c r="E282" s="15"/>
       <c r="G282" s="22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="283" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D283" s="15"/>
       <c r="E283" s="15"/>
-      <c r="H283" s="70" t="s">
+      <c r="H283" s="46" t="s">
+        <v>154</v>
+      </c>
+      <c r="I283" s="46"/>
+      <c r="J283" s="46"/>
+      <c r="K283" s="46"/>
+      <c r="L283" s="46" t="s">
         <v>155</v>
       </c>
-      <c r="I283" s="70"/>
-      <c r="J283" s="70"/>
-      <c r="K283" s="70"/>
-      <c r="L283" s="70" t="s">
-        <v>156</v>
-      </c>
-      <c r="M283" s="70"/>
-      <c r="N283" s="70"/>
-      <c r="O283" s="70"/>
-      <c r="P283" s="70"/>
-      <c r="Q283" s="70"/>
-      <c r="R283" s="70"/>
-      <c r="S283" s="70"/>
-      <c r="T283" s="70"/>
-      <c r="U283" s="70"/>
-      <c r="V283" s="70"/>
-      <c r="W283" s="70"/>
-      <c r="X283" s="70"/>
-      <c r="Y283" s="70"/>
-      <c r="Z283" s="70"/>
-      <c r="AA283" s="70"/>
+      <c r="M283" s="46"/>
+      <c r="N283" s="46"/>
+      <c r="O283" s="46"/>
+      <c r="P283" s="46"/>
+      <c r="Q283" s="46"/>
+      <c r="R283" s="46"/>
+      <c r="S283" s="46"/>
+      <c r="T283" s="46"/>
+      <c r="U283" s="46"/>
+      <c r="V283" s="46"/>
+      <c r="W283" s="46"/>
+      <c r="X283" s="46"/>
+      <c r="Y283" s="46"/>
+      <c r="Z283" s="46"/>
+      <c r="AA283" s="46"/>
     </row>
     <row r="284" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D284" s="15"/>
       <c r="E284" s="15"/>
-      <c r="H284" s="100" t="s">
+      <c r="H284" s="45" t="s">
+        <v>156</v>
+      </c>
+      <c r="I284" s="45"/>
+      <c r="J284" s="45"/>
+      <c r="K284" s="45"/>
+      <c r="L284" s="45" t="s">
         <v>157</v>
       </c>
-      <c r="I284" s="100"/>
-      <c r="J284" s="100"/>
-      <c r="K284" s="100"/>
-      <c r="L284" s="100" t="s">
-        <v>158</v>
-      </c>
-      <c r="M284" s="100"/>
-      <c r="N284" s="100"/>
-      <c r="O284" s="100"/>
-      <c r="P284" s="100"/>
-      <c r="Q284" s="100"/>
-      <c r="R284" s="100"/>
-      <c r="S284" s="100"/>
-      <c r="T284" s="100"/>
-      <c r="U284" s="100"/>
-      <c r="V284" s="100"/>
-      <c r="W284" s="100"/>
-      <c r="X284" s="100"/>
-      <c r="Y284" s="100"/>
-      <c r="Z284" s="100"/>
-      <c r="AA284" s="100"/>
+      <c r="M284" s="45"/>
+      <c r="N284" s="45"/>
+      <c r="O284" s="45"/>
+      <c r="P284" s="45"/>
+      <c r="Q284" s="45"/>
+      <c r="R284" s="45"/>
+      <c r="S284" s="45"/>
+      <c r="T284" s="45"/>
+      <c r="U284" s="45"/>
+      <c r="V284" s="45"/>
+      <c r="W284" s="45"/>
+      <c r="X284" s="45"/>
+      <c r="Y284" s="45"/>
+      <c r="Z284" s="45"/>
+      <c r="AA284" s="45"/>
     </row>
     <row r="285" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D285" s="15"/>
       <c r="E285" s="15"/>
-      <c r="H285" s="100" t="s">
-        <v>159</v>
-      </c>
-      <c r="I285" s="100"/>
-      <c r="J285" s="100"/>
-      <c r="K285" s="100"/>
-      <c r="L285" s="100"/>
-      <c r="M285" s="100"/>
-      <c r="N285" s="100"/>
-      <c r="O285" s="100"/>
-      <c r="P285" s="100"/>
-      <c r="Q285" s="100"/>
-      <c r="R285" s="100"/>
-      <c r="S285" s="100"/>
-      <c r="T285" s="100"/>
-      <c r="U285" s="100"/>
-      <c r="V285" s="100"/>
-      <c r="W285" s="100"/>
-      <c r="X285" s="100"/>
-      <c r="Y285" s="100"/>
-      <c r="Z285" s="100"/>
-      <c r="AA285" s="100"/>
+      <c r="H285" s="45" t="s">
+        <v>158</v>
+      </c>
+      <c r="I285" s="45"/>
+      <c r="J285" s="45"/>
+      <c r="K285" s="45"/>
+      <c r="L285" s="45"/>
+      <c r="M285" s="45"/>
+      <c r="N285" s="45"/>
+      <c r="O285" s="45"/>
+      <c r="P285" s="45"/>
+      <c r="Q285" s="45"/>
+      <c r="R285" s="45"/>
+      <c r="S285" s="45"/>
+      <c r="T285" s="45"/>
+      <c r="U285" s="45"/>
+      <c r="V285" s="45"/>
+      <c r="W285" s="45"/>
+      <c r="X285" s="45"/>
+      <c r="Y285" s="45"/>
+      <c r="Z285" s="45"/>
+      <c r="AA285" s="45"/>
     </row>
     <row r="286" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D286" s="15"/>
       <c r="E286" s="15"/>
-      <c r="H286" s="100" t="s">
+      <c r="H286" s="45" t="s">
+        <v>159</v>
+      </c>
+      <c r="I286" s="45"/>
+      <c r="J286" s="45"/>
+      <c r="K286" s="45"/>
+      <c r="L286" s="45" t="s">
         <v>160</v>
       </c>
-      <c r="I286" s="100"/>
-      <c r="J286" s="100"/>
-      <c r="K286" s="100"/>
-      <c r="L286" s="100" t="s">
-        <v>161</v>
-      </c>
-      <c r="M286" s="100"/>
-      <c r="N286" s="100"/>
-      <c r="O286" s="100"/>
-      <c r="P286" s="100"/>
-      <c r="Q286" s="100"/>
-      <c r="R286" s="100"/>
-      <c r="S286" s="100"/>
-      <c r="T286" s="100"/>
-      <c r="U286" s="100"/>
-      <c r="V286" s="100"/>
-      <c r="W286" s="100"/>
-      <c r="X286" s="100"/>
-      <c r="Y286" s="100"/>
-      <c r="Z286" s="100"/>
-      <c r="AA286" s="100"/>
+      <c r="M286" s="45"/>
+      <c r="N286" s="45"/>
+      <c r="O286" s="45"/>
+      <c r="P286" s="45"/>
+      <c r="Q286" s="45"/>
+      <c r="R286" s="45"/>
+      <c r="S286" s="45"/>
+      <c r="T286" s="45"/>
+      <c r="U286" s="45"/>
+      <c r="V286" s="45"/>
+      <c r="W286" s="45"/>
+      <c r="X286" s="45"/>
+      <c r="Y286" s="45"/>
+      <c r="Z286" s="45"/>
+      <c r="AA286" s="45"/>
     </row>
     <row r="287" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D287" s="15"/>
       <c r="E287" s="15"/>
-      <c r="H287" s="100" t="s">
-        <v>162</v>
-      </c>
-      <c r="I287" s="100"/>
-      <c r="J287" s="100"/>
-      <c r="K287" s="100"/>
-      <c r="L287" s="100"/>
-      <c r="M287" s="100"/>
-      <c r="N287" s="100"/>
-      <c r="O287" s="100"/>
-      <c r="P287" s="100"/>
-      <c r="Q287" s="100"/>
-      <c r="R287" s="100"/>
-      <c r="S287" s="100"/>
-      <c r="T287" s="100"/>
-      <c r="U287" s="100"/>
-      <c r="V287" s="100"/>
-      <c r="W287" s="100"/>
-      <c r="X287" s="100"/>
-      <c r="Y287" s="100"/>
-      <c r="Z287" s="100"/>
-      <c r="AA287" s="100"/>
+      <c r="H287" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="I287" s="45"/>
+      <c r="J287" s="45"/>
+      <c r="K287" s="45"/>
+      <c r="L287" s="45"/>
+      <c r="M287" s="45"/>
+      <c r="N287" s="45"/>
+      <c r="O287" s="45"/>
+      <c r="P287" s="45"/>
+      <c r="Q287" s="45"/>
+      <c r="R287" s="45"/>
+      <c r="S287" s="45"/>
+      <c r="T287" s="45"/>
+      <c r="U287" s="45"/>
+      <c r="V287" s="45"/>
+      <c r="W287" s="45"/>
+      <c r="X287" s="45"/>
+      <c r="Y287" s="45"/>
+      <c r="Z287" s="45"/>
+      <c r="AA287" s="45"/>
     </row>
     <row r="288" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D288" s="15"/>
       <c r="E288" s="15"/>
-      <c r="H288" s="100" t="s">
+      <c r="H288" s="45" t="s">
+        <v>162</v>
+      </c>
+      <c r="I288" s="45"/>
+      <c r="J288" s="45"/>
+      <c r="K288" s="45"/>
+      <c r="L288" s="45" t="s">
         <v>163</v>
       </c>
-      <c r="I288" s="100"/>
-      <c r="J288" s="100"/>
-      <c r="K288" s="100"/>
-      <c r="L288" s="100" t="s">
-        <v>164</v>
-      </c>
-      <c r="M288" s="100"/>
-      <c r="N288" s="100"/>
-      <c r="O288" s="100"/>
-      <c r="P288" s="100"/>
-      <c r="Q288" s="100"/>
-      <c r="R288" s="100"/>
-      <c r="S288" s="100"/>
-      <c r="T288" s="100"/>
-      <c r="U288" s="100"/>
-      <c r="V288" s="100"/>
-      <c r="W288" s="100"/>
-      <c r="X288" s="100"/>
-      <c r="Y288" s="100"/>
-      <c r="Z288" s="100"/>
-      <c r="AA288" s="100"/>
+      <c r="M288" s="45"/>
+      <c r="N288" s="45"/>
+      <c r="O288" s="45"/>
+      <c r="P288" s="45"/>
+      <c r="Q288" s="45"/>
+      <c r="R288" s="45"/>
+      <c r="S288" s="45"/>
+      <c r="T288" s="45"/>
+      <c r="U288" s="45"/>
+      <c r="V288" s="45"/>
+      <c r="W288" s="45"/>
+      <c r="X288" s="45"/>
+      <c r="Y288" s="45"/>
+      <c r="Z288" s="45"/>
+      <c r="AA288" s="45"/>
     </row>
     <row r="289" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D289" s="15"/>
@@ -5841,118 +5841,118 @@
       <c r="D290" s="15"/>
       <c r="E290" s="15"/>
       <c r="G290" s="22" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="291" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D291" s="15"/>
       <c r="E291" s="15"/>
-      <c r="H291" s="70" t="s">
+      <c r="H291" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="I291" s="46"/>
+      <c r="J291" s="46"/>
+      <c r="K291" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="I291" s="70"/>
-      <c r="J291" s="70"/>
-      <c r="K291" s="70" t="s">
-        <v>167</v>
-      </c>
-      <c r="L291" s="70"/>
-      <c r="M291" s="70"/>
-      <c r="N291" s="70"/>
-      <c r="O291" s="70"/>
-      <c r="P291" s="70"/>
-      <c r="Q291" s="70"/>
-      <c r="R291" s="70"/>
-      <c r="S291" s="70"/>
-      <c r="T291" s="70"/>
-      <c r="U291" s="70"/>
+      <c r="L291" s="46"/>
+      <c r="M291" s="46"/>
+      <c r="N291" s="46"/>
+      <c r="O291" s="46"/>
+      <c r="P291" s="46"/>
+      <c r="Q291" s="46"/>
+      <c r="R291" s="46"/>
+      <c r="S291" s="46"/>
+      <c r="T291" s="46"/>
+      <c r="U291" s="46"/>
     </row>
     <row r="292" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D292" s="15"/>
       <c r="E292" s="15"/>
-      <c r="H292" s="100" t="s">
-        <v>168</v>
-      </c>
-      <c r="I292" s="100"/>
-      <c r="J292" s="100"/>
-      <c r="K292" s="100" t="s">
-        <v>159</v>
-      </c>
-      <c r="L292" s="100"/>
-      <c r="M292" s="100"/>
-      <c r="N292" s="100"/>
-      <c r="O292" s="100"/>
-      <c r="P292" s="100"/>
-      <c r="Q292" s="100"/>
-      <c r="R292" s="100"/>
-      <c r="S292" s="100"/>
-      <c r="T292" s="100"/>
-      <c r="U292" s="100"/>
+      <c r="H292" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="I292" s="45"/>
+      <c r="J292" s="45"/>
+      <c r="K292" s="45" t="s">
+        <v>158</v>
+      </c>
+      <c r="L292" s="45"/>
+      <c r="M292" s="45"/>
+      <c r="N292" s="45"/>
+      <c r="O292" s="45"/>
+      <c r="P292" s="45"/>
+      <c r="Q292" s="45"/>
+      <c r="R292" s="45"/>
+      <c r="S292" s="45"/>
+      <c r="T292" s="45"/>
+      <c r="U292" s="45"/>
     </row>
     <row r="293" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D293" s="15"/>
       <c r="E293" s="15"/>
-      <c r="H293" s="100" t="s">
+      <c r="H293" s="45" t="s">
+        <v>168</v>
+      </c>
+      <c r="I293" s="45"/>
+      <c r="J293" s="45"/>
+      <c r="K293" s="45" t="s">
         <v>169</v>
       </c>
-      <c r="I293" s="100"/>
-      <c r="J293" s="100"/>
-      <c r="K293" s="100" t="s">
-        <v>170</v>
-      </c>
-      <c r="L293" s="100"/>
-      <c r="M293" s="100"/>
-      <c r="N293" s="100"/>
-      <c r="O293" s="100"/>
-      <c r="P293" s="100"/>
-      <c r="Q293" s="100"/>
-      <c r="R293" s="100"/>
-      <c r="S293" s="100"/>
-      <c r="T293" s="100"/>
-      <c r="U293" s="100"/>
+      <c r="L293" s="45"/>
+      <c r="M293" s="45"/>
+      <c r="N293" s="45"/>
+      <c r="O293" s="45"/>
+      <c r="P293" s="45"/>
+      <c r="Q293" s="45"/>
+      <c r="R293" s="45"/>
+      <c r="S293" s="45"/>
+      <c r="T293" s="45"/>
+      <c r="U293" s="45"/>
     </row>
     <row r="294" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D294" s="15"/>
       <c r="E294" s="15"/>
-      <c r="H294" s="100" t="s">
-        <v>171</v>
-      </c>
-      <c r="I294" s="100"/>
-      <c r="J294" s="100"/>
-      <c r="K294" s="100" t="s">
-        <v>163</v>
-      </c>
-      <c r="L294" s="100"/>
-      <c r="M294" s="100"/>
-      <c r="N294" s="100"/>
-      <c r="O294" s="100"/>
-      <c r="P294" s="100"/>
-      <c r="Q294" s="100"/>
-      <c r="R294" s="100"/>
-      <c r="S294" s="100"/>
-      <c r="T294" s="100"/>
-      <c r="U294" s="100"/>
+      <c r="H294" s="45" t="s">
+        <v>170</v>
+      </c>
+      <c r="I294" s="45"/>
+      <c r="J294" s="45"/>
+      <c r="K294" s="45" t="s">
+        <v>162</v>
+      </c>
+      <c r="L294" s="45"/>
+      <c r="M294" s="45"/>
+      <c r="N294" s="45"/>
+      <c r="O294" s="45"/>
+      <c r="P294" s="45"/>
+      <c r="Q294" s="45"/>
+      <c r="R294" s="45"/>
+      <c r="S294" s="45"/>
+      <c r="T294" s="45"/>
+      <c r="U294" s="45"/>
     </row>
     <row r="295" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D295" s="15"/>
       <c r="E295" s="15"/>
-      <c r="H295" s="100" t="s">
-        <v>172</v>
-      </c>
-      <c r="I295" s="100"/>
-      <c r="J295" s="100"/>
-      <c r="K295" s="100" t="s">
-        <v>160</v>
-      </c>
-      <c r="L295" s="100"/>
-      <c r="M295" s="100"/>
-      <c r="N295" s="100"/>
-      <c r="O295" s="100"/>
-      <c r="P295" s="100"/>
-      <c r="Q295" s="100"/>
-      <c r="R295" s="100"/>
-      <c r="S295" s="100"/>
-      <c r="T295" s="100"/>
-      <c r="U295" s="100"/>
+      <c r="H295" s="45" t="s">
+        <v>171</v>
+      </c>
+      <c r="I295" s="45"/>
+      <c r="J295" s="45"/>
+      <c r="K295" s="45" t="s">
+        <v>159</v>
+      </c>
+      <c r="L295" s="45"/>
+      <c r="M295" s="45"/>
+      <c r="N295" s="45"/>
+      <c r="O295" s="45"/>
+      <c r="P295" s="45"/>
+      <c r="Q295" s="45"/>
+      <c r="R295" s="45"/>
+      <c r="S295" s="45"/>
+      <c r="T295" s="45"/>
+      <c r="U295" s="45"/>
     </row>
     <row r="296" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D296" s="15"/>
@@ -5962,96 +5962,96 @@
       <c r="D297" s="15"/>
       <c r="E297" s="15"/>
       <c r="G297" s="22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="298" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D298" s="15"/>
       <c r="E298" s="15"/>
-      <c r="H298" s="70" t="s">
+      <c r="H298" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="I298" s="46"/>
+      <c r="J298" s="46"/>
+      <c r="K298" s="46" t="s">
         <v>174</v>
       </c>
-      <c r="I298" s="70"/>
-      <c r="J298" s="70"/>
-      <c r="K298" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L298" s="70"/>
-      <c r="M298" s="70"/>
-      <c r="N298" s="70"/>
-      <c r="O298" s="70"/>
-      <c r="P298" s="70"/>
-      <c r="Q298" s="70"/>
-      <c r="R298" s="70"/>
-      <c r="S298" s="70"/>
-      <c r="T298" s="70"/>
-      <c r="U298" s="70"/>
+      <c r="L298" s="46"/>
+      <c r="M298" s="46"/>
+      <c r="N298" s="46"/>
+      <c r="O298" s="46"/>
+      <c r="P298" s="46"/>
+      <c r="Q298" s="46"/>
+      <c r="R298" s="46"/>
+      <c r="S298" s="46"/>
+      <c r="T298" s="46"/>
+      <c r="U298" s="46"/>
     </row>
     <row r="299" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D299" s="15"/>
       <c r="E299" s="15"/>
-      <c r="H299" s="100" t="s">
+      <c r="H299" s="45" t="s">
+        <v>175</v>
+      </c>
+      <c r="I299" s="45"/>
+      <c r="J299" s="45"/>
+      <c r="K299" s="45" t="s">
         <v>176</v>
       </c>
-      <c r="I299" s="100"/>
-      <c r="J299" s="100"/>
-      <c r="K299" s="100" t="s">
-        <v>177</v>
-      </c>
-      <c r="L299" s="100"/>
-      <c r="M299" s="100"/>
-      <c r="N299" s="100"/>
-      <c r="O299" s="100"/>
-      <c r="P299" s="100"/>
-      <c r="Q299" s="100"/>
-      <c r="R299" s="100"/>
-      <c r="S299" s="100"/>
-      <c r="T299" s="100"/>
-      <c r="U299" s="100"/>
+      <c r="L299" s="45"/>
+      <c r="M299" s="45"/>
+      <c r="N299" s="45"/>
+      <c r="O299" s="45"/>
+      <c r="P299" s="45"/>
+      <c r="Q299" s="45"/>
+      <c r="R299" s="45"/>
+      <c r="S299" s="45"/>
+      <c r="T299" s="45"/>
+      <c r="U299" s="45"/>
     </row>
     <row r="300" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D300" s="15"/>
       <c r="E300" s="15"/>
-      <c r="H300" s="100" t="s">
+      <c r="H300" s="45" t="s">
+        <v>177</v>
+      </c>
+      <c r="I300" s="45"/>
+      <c r="J300" s="45"/>
+      <c r="K300" s="45" t="s">
         <v>178</v>
       </c>
-      <c r="I300" s="100"/>
-      <c r="J300" s="100"/>
-      <c r="K300" s="100" t="s">
-        <v>179</v>
-      </c>
-      <c r="L300" s="100"/>
-      <c r="M300" s="100"/>
-      <c r="N300" s="100"/>
-      <c r="O300" s="100"/>
-      <c r="P300" s="100"/>
-      <c r="Q300" s="100"/>
-      <c r="R300" s="100"/>
-      <c r="S300" s="100"/>
-      <c r="T300" s="100"/>
-      <c r="U300" s="100"/>
+      <c r="L300" s="45"/>
+      <c r="M300" s="45"/>
+      <c r="N300" s="45"/>
+      <c r="O300" s="45"/>
+      <c r="P300" s="45"/>
+      <c r="Q300" s="45"/>
+      <c r="R300" s="45"/>
+      <c r="S300" s="45"/>
+      <c r="T300" s="45"/>
+      <c r="U300" s="45"/>
     </row>
     <row r="301" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D301" s="15"/>
       <c r="E301" s="15"/>
-      <c r="H301" s="100" t="s">
+      <c r="H301" s="45" t="s">
+        <v>179</v>
+      </c>
+      <c r="I301" s="45"/>
+      <c r="J301" s="45"/>
+      <c r="K301" s="45" t="s">
         <v>180</v>
       </c>
-      <c r="I301" s="100"/>
-      <c r="J301" s="100"/>
-      <c r="K301" s="100" t="s">
-        <v>181</v>
-      </c>
-      <c r="L301" s="100"/>
-      <c r="M301" s="100"/>
-      <c r="N301" s="100"/>
-      <c r="O301" s="100"/>
-      <c r="P301" s="100"/>
-      <c r="Q301" s="100"/>
-      <c r="R301" s="100"/>
-      <c r="S301" s="100"/>
-      <c r="T301" s="100"/>
-      <c r="U301" s="100"/>
+      <c r="L301" s="45"/>
+      <c r="M301" s="45"/>
+      <c r="N301" s="45"/>
+      <c r="O301" s="45"/>
+      <c r="P301" s="45"/>
+      <c r="Q301" s="45"/>
+      <c r="R301" s="45"/>
+      <c r="S301" s="45"/>
+      <c r="T301" s="45"/>
+      <c r="U301" s="45"/>
     </row>
     <row r="302" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D302" s="15"/>
@@ -6061,7 +6061,7 @@
       <c r="D303" s="15"/>
       <c r="E303" s="15"/>
       <c r="G303" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="304" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6073,102 +6073,102 @@
       <c r="E305" s="15"/>
       <c r="F305" s="15"/>
       <c r="H305" s="39"/>
-      <c r="I305" s="74" t="s">
-        <v>166</v>
-      </c>
-      <c r="J305" s="74"/>
-      <c r="K305" s="74"/>
-      <c r="L305" s="74"/>
-      <c r="M305" s="74"/>
+      <c r="I305" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="J305" s="43"/>
+      <c r="K305" s="43"/>
+      <c r="L305" s="43"/>
+      <c r="M305" s="43"/>
     </row>
     <row r="306" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D306" s="15"/>
       <c r="E306" s="15"/>
       <c r="F306" s="15"/>
-      <c r="H306" s="101" t="s">
-        <v>174</v>
+      <c r="H306" s="44" t="s">
+        <v>173</v>
       </c>
       <c r="I306" s="38"/>
       <c r="J306" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="K306" s="38" t="s">
         <v>168</v>
       </c>
-      <c r="K306" s="38" t="s">
-        <v>169</v>
-      </c>
       <c r="L306" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="M306" s="38" t="s">
         <v>171</v>
-      </c>
-      <c r="M306" s="38" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="307" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D307" s="15"/>
       <c r="E307" s="15"/>
       <c r="F307" s="15"/>
-      <c r="H307" s="101"/>
+      <c r="H307" s="44"/>
       <c r="I307" s="38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J307" s="40" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K307" s="40" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L307" s="40" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M307" s="40" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="308" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D308" s="15"/>
       <c r="E308" s="15"/>
       <c r="F308" s="15"/>
-      <c r="H308" s="101"/>
+      <c r="H308" s="44"/>
       <c r="I308" s="38" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J308" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="K308" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="L308" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="M308" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="P308" s="4" t="s">
         <v>184</v>
-      </c>
-      <c r="K308" s="40" t="s">
-        <v>183</v>
-      </c>
-      <c r="L308" s="40" t="s">
-        <v>184</v>
-      </c>
-      <c r="M308" s="40" t="s">
-        <v>183</v>
-      </c>
-      <c r="P308" s="4" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="309" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D309" s="15"/>
       <c r="E309" s="15"/>
       <c r="F309" s="15"/>
-      <c r="H309" s="101"/>
+      <c r="H309" s="44"/>
       <c r="I309" s="38" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J309" s="40" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K309" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="L309" s="40" t="s">
         <v>183</v>
       </c>
-      <c r="L309" s="40" t="s">
-        <v>184</v>
-      </c>
       <c r="M309" s="40" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P309" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="310" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6265,31 +6265,31 @@
       <c r="J327" s="24"/>
       <c r="K327" s="24"/>
       <c r="L327" s="25"/>
-      <c r="M327" s="70" t="s">
+      <c r="M327" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="N327" s="70"/>
-      <c r="O327" s="70"/>
-      <c r="P327" s="70"/>
-      <c r="Q327" s="70"/>
-      <c r="R327" s="70"/>
-      <c r="S327" s="70"/>
-      <c r="T327" s="74" t="s">
+      <c r="N327" s="46"/>
+      <c r="O327" s="46"/>
+      <c r="P327" s="46"/>
+      <c r="Q327" s="46"/>
+      <c r="R327" s="46"/>
+      <c r="S327" s="46"/>
+      <c r="T327" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="U327" s="74"/>
-      <c r="V327" s="74"/>
-      <c r="W327" s="74"/>
-      <c r="X327" s="74"/>
-      <c r="Y327" s="74"/>
-      <c r="Z327" s="74"/>
-      <c r="AA327" s="74"/>
-      <c r="AB327" s="74"/>
-      <c r="AC327" s="74"/>
-      <c r="AD327" s="74"/>
-      <c r="AE327" s="74"/>
-      <c r="AF327" s="74"/>
-      <c r="AG327" s="74"/>
+      <c r="U327" s="43"/>
+      <c r="V327" s="43"/>
+      <c r="W327" s="43"/>
+      <c r="X327" s="43"/>
+      <c r="Y327" s="43"/>
+      <c r="Z327" s="43"/>
+      <c r="AA327" s="43"/>
+      <c r="AB327" s="43"/>
+      <c r="AC327" s="43"/>
+      <c r="AD327" s="43"/>
+      <c r="AE327" s="43"/>
+      <c r="AF327" s="43"/>
+      <c r="AG327" s="43"/>
     </row>
     <row r="328" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D328" s="15"/>
@@ -6301,371 +6301,371 @@
       <c r="J328" s="27"/>
       <c r="K328" s="27"/>
       <c r="L328" s="28"/>
-      <c r="M328" s="70" t="s">
+      <c r="M328" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="N328" s="70"/>
-      <c r="O328" s="70"/>
-      <c r="P328" s="70"/>
-      <c r="Q328" s="70"/>
-      <c r="R328" s="70"/>
-      <c r="S328" s="70"/>
-      <c r="T328" s="70" t="s">
+      <c r="N328" s="46"/>
+      <c r="O328" s="46"/>
+      <c r="P328" s="46"/>
+      <c r="Q328" s="46"/>
+      <c r="R328" s="46"/>
+      <c r="S328" s="46"/>
+      <c r="T328" s="46" t="s">
         <v>146</v>
       </c>
-      <c r="U328" s="70"/>
-      <c r="V328" s="70"/>
-      <c r="W328" s="70"/>
-      <c r="X328" s="70"/>
-      <c r="Y328" s="70"/>
-      <c r="Z328" s="70"/>
-      <c r="AA328" s="70"/>
-      <c r="AB328" s="70" t="s">
+      <c r="U328" s="46"/>
+      <c r="V328" s="46"/>
+      <c r="W328" s="46"/>
+      <c r="X328" s="46"/>
+      <c r="Y328" s="46"/>
+      <c r="Z328" s="46"/>
+      <c r="AA328" s="46"/>
+      <c r="AB328" s="46" t="s">
         <v>147</v>
       </c>
-      <c r="AC328" s="70"/>
-      <c r="AD328" s="70"/>
-      <c r="AE328" s="70"/>
-      <c r="AF328" s="70"/>
-      <c r="AG328" s="70"/>
+      <c r="AC328" s="46"/>
+      <c r="AD328" s="46"/>
+      <c r="AE328" s="46"/>
+      <c r="AF328" s="46"/>
+      <c r="AG328" s="46"/>
     </row>
     <row r="329" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D329" s="15"/>
-      <c r="E329" s="67" t="s">
+      <c r="E329" s="75" t="s">
         <v>143</v>
       </c>
-      <c r="F329" s="67"/>
-      <c r="G329" s="67"/>
-      <c r="H329" s="67"/>
-      <c r="I329" s="67"/>
-      <c r="J329" s="67"/>
-      <c r="K329" s="71" t="s">
+      <c r="F329" s="75"/>
+      <c r="G329" s="75"/>
+      <c r="H329" s="75"/>
+      <c r="I329" s="75"/>
+      <c r="J329" s="75"/>
+      <c r="K329" s="54" t="s">
         <v>74</v>
       </c>
-      <c r="L329" s="72"/>
-      <c r="M329" s="96" t="s">
+      <c r="L329" s="55"/>
+      <c r="M329" s="50" t="s">
         <v>105</v>
       </c>
-      <c r="N329" s="96"/>
-      <c r="O329" s="96"/>
-      <c r="P329" s="96"/>
-      <c r="Q329" s="96"/>
-      <c r="R329" s="96"/>
-      <c r="S329" s="96"/>
-      <c r="T329" s="84" t="s">
+      <c r="N329" s="50"/>
+      <c r="O329" s="50"/>
+      <c r="P329" s="50"/>
+      <c r="Q329" s="50"/>
+      <c r="R329" s="50"/>
+      <c r="S329" s="50"/>
+      <c r="T329" s="65" t="s">
         <v>99</v>
       </c>
-      <c r="U329" s="85"/>
-      <c r="V329" s="85"/>
-      <c r="W329" s="85"/>
-      <c r="X329" s="85"/>
-      <c r="Y329" s="85"/>
-      <c r="Z329" s="85"/>
-      <c r="AA329" s="86"/>
-      <c r="AB329" s="75" t="s">
+      <c r="U329" s="66"/>
+      <c r="V329" s="66"/>
+      <c r="W329" s="66"/>
+      <c r="X329" s="66"/>
+      <c r="Y329" s="66"/>
+      <c r="Z329" s="66"/>
+      <c r="AA329" s="67"/>
+      <c r="AB329" s="56" t="s">
         <v>79</v>
       </c>
-      <c r="AC329" s="76"/>
-      <c r="AD329" s="76"/>
-      <c r="AE329" s="76"/>
-      <c r="AF329" s="76"/>
-      <c r="AG329" s="77"/>
+      <c r="AC329" s="57"/>
+      <c r="AD329" s="57"/>
+      <c r="AE329" s="57"/>
+      <c r="AF329" s="57"/>
+      <c r="AG329" s="58"/>
     </row>
     <row r="330" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D330" s="15"/>
-      <c r="E330" s="68"/>
-      <c r="F330" s="68"/>
-      <c r="G330" s="68"/>
-      <c r="H330" s="68"/>
-      <c r="I330" s="68"/>
-      <c r="J330" s="68"/>
-      <c r="K330" s="71" t="s">
+      <c r="E330" s="76"/>
+      <c r="F330" s="76"/>
+      <c r="G330" s="76"/>
+      <c r="H330" s="76"/>
+      <c r="I330" s="76"/>
+      <c r="J330" s="76"/>
+      <c r="K330" s="54" t="s">
         <v>106</v>
       </c>
-      <c r="L330" s="72"/>
-      <c r="M330" s="96" t="s">
+      <c r="L330" s="55"/>
+      <c r="M330" s="50" t="s">
         <v>109</v>
       </c>
-      <c r="N330" s="96"/>
-      <c r="O330" s="96"/>
-      <c r="P330" s="96"/>
-      <c r="Q330" s="96"/>
-      <c r="R330" s="96"/>
-      <c r="S330" s="96"/>
-      <c r="T330" s="87"/>
-      <c r="U330" s="88"/>
-      <c r="V330" s="88"/>
-      <c r="W330" s="88"/>
-      <c r="X330" s="88"/>
-      <c r="Y330" s="88"/>
-      <c r="Z330" s="88"/>
-      <c r="AA330" s="89"/>
-      <c r="AB330" s="78"/>
-      <c r="AC330" s="79"/>
-      <c r="AD330" s="79"/>
-      <c r="AE330" s="79"/>
-      <c r="AF330" s="79"/>
-      <c r="AG330" s="80"/>
+      <c r="N330" s="50"/>
+      <c r="O330" s="50"/>
+      <c r="P330" s="50"/>
+      <c r="Q330" s="50"/>
+      <c r="R330" s="50"/>
+      <c r="S330" s="50"/>
+      <c r="T330" s="68"/>
+      <c r="U330" s="69"/>
+      <c r="V330" s="69"/>
+      <c r="W330" s="69"/>
+      <c r="X330" s="69"/>
+      <c r="Y330" s="69"/>
+      <c r="Z330" s="69"/>
+      <c r="AA330" s="70"/>
+      <c r="AB330" s="59"/>
+      <c r="AC330" s="60"/>
+      <c r="AD330" s="60"/>
+      <c r="AE330" s="60"/>
+      <c r="AF330" s="60"/>
+      <c r="AG330" s="61"/>
     </row>
     <row r="331" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D331" s="15"/>
-      <c r="E331" s="68"/>
-      <c r="F331" s="68"/>
-      <c r="G331" s="68"/>
-      <c r="H331" s="68"/>
-      <c r="I331" s="68"/>
-      <c r="J331" s="68"/>
-      <c r="K331" s="71" t="s">
+      <c r="E331" s="76"/>
+      <c r="F331" s="76"/>
+      <c r="G331" s="76"/>
+      <c r="H331" s="76"/>
+      <c r="I331" s="76"/>
+      <c r="J331" s="76"/>
+      <c r="K331" s="54" t="s">
         <v>107</v>
       </c>
-      <c r="L331" s="72"/>
-      <c r="M331" s="96" t="s">
+      <c r="L331" s="55"/>
+      <c r="M331" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="N331" s="96"/>
-      <c r="O331" s="96"/>
-      <c r="P331" s="96"/>
-      <c r="Q331" s="96"/>
-      <c r="R331" s="96"/>
-      <c r="S331" s="96"/>
-      <c r="T331" s="87"/>
-      <c r="U331" s="88"/>
-      <c r="V331" s="88"/>
-      <c r="W331" s="88"/>
-      <c r="X331" s="88"/>
-      <c r="Y331" s="88"/>
-      <c r="Z331" s="88"/>
-      <c r="AA331" s="89"/>
-      <c r="AB331" s="78"/>
-      <c r="AC331" s="79"/>
-      <c r="AD331" s="79"/>
-      <c r="AE331" s="79"/>
-      <c r="AF331" s="79"/>
-      <c r="AG331" s="80"/>
+      <c r="N331" s="50"/>
+      <c r="O331" s="50"/>
+      <c r="P331" s="50"/>
+      <c r="Q331" s="50"/>
+      <c r="R331" s="50"/>
+      <c r="S331" s="50"/>
+      <c r="T331" s="68"/>
+      <c r="U331" s="69"/>
+      <c r="V331" s="69"/>
+      <c r="W331" s="69"/>
+      <c r="X331" s="69"/>
+      <c r="Y331" s="69"/>
+      <c r="Z331" s="69"/>
+      <c r="AA331" s="70"/>
+      <c r="AB331" s="59"/>
+      <c r="AC331" s="60"/>
+      <c r="AD331" s="60"/>
+      <c r="AE331" s="60"/>
+      <c r="AF331" s="60"/>
+      <c r="AG331" s="61"/>
     </row>
     <row r="332" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D332" s="15"/>
-      <c r="E332" s="69"/>
-      <c r="F332" s="69"/>
-      <c r="G332" s="69"/>
-      <c r="H332" s="69"/>
-      <c r="I332" s="69"/>
-      <c r="J332" s="69"/>
-      <c r="K332" s="71" t="s">
+      <c r="E332" s="77"/>
+      <c r="F332" s="77"/>
+      <c r="G332" s="77"/>
+      <c r="H332" s="77"/>
+      <c r="I332" s="77"/>
+      <c r="J332" s="77"/>
+      <c r="K332" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="L332" s="72"/>
-      <c r="M332" s="96" t="s">
+      <c r="L332" s="55"/>
+      <c r="M332" s="50" t="s">
         <v>110</v>
       </c>
-      <c r="N332" s="96"/>
-      <c r="O332" s="96"/>
-      <c r="P332" s="96"/>
-      <c r="Q332" s="96"/>
-      <c r="R332" s="96"/>
-      <c r="S332" s="96"/>
-      <c r="T332" s="90"/>
-      <c r="U332" s="91"/>
-      <c r="V332" s="91"/>
-      <c r="W332" s="91"/>
-      <c r="X332" s="91"/>
-      <c r="Y332" s="91"/>
-      <c r="Z332" s="91"/>
-      <c r="AA332" s="92"/>
-      <c r="AB332" s="81"/>
-      <c r="AC332" s="82"/>
-      <c r="AD332" s="82"/>
-      <c r="AE332" s="82"/>
-      <c r="AF332" s="82"/>
-      <c r="AG332" s="83"/>
+      <c r="N332" s="50"/>
+      <c r="O332" s="50"/>
+      <c r="P332" s="50"/>
+      <c r="Q332" s="50"/>
+      <c r="R332" s="50"/>
+      <c r="S332" s="50"/>
+      <c r="T332" s="71"/>
+      <c r="U332" s="72"/>
+      <c r="V332" s="72"/>
+      <c r="W332" s="72"/>
+      <c r="X332" s="72"/>
+      <c r="Y332" s="72"/>
+      <c r="Z332" s="72"/>
+      <c r="AA332" s="73"/>
+      <c r="AB332" s="62"/>
+      <c r="AC332" s="63"/>
+      <c r="AD332" s="63"/>
+      <c r="AE332" s="63"/>
+      <c r="AF332" s="63"/>
+      <c r="AG332" s="64"/>
     </row>
     <row r="333" spans="4:33" ht="29.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D333" s="15"/>
-      <c r="E333" s="71" t="s">
+      <c r="E333" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="F333" s="73"/>
-      <c r="G333" s="73"/>
-      <c r="H333" s="73"/>
-      <c r="I333" s="73"/>
-      <c r="J333" s="73"/>
-      <c r="K333" s="73"/>
-      <c r="L333" s="72"/>
-      <c r="M333" s="96" t="s">
+      <c r="F333" s="74"/>
+      <c r="G333" s="74"/>
+      <c r="H333" s="74"/>
+      <c r="I333" s="74"/>
+      <c r="J333" s="74"/>
+      <c r="K333" s="74"/>
+      <c r="L333" s="55"/>
+      <c r="M333" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="N333" s="96"/>
-      <c r="O333" s="96"/>
-      <c r="P333" s="96"/>
-      <c r="Q333" s="96"/>
-      <c r="R333" s="96"/>
-      <c r="S333" s="96"/>
-      <c r="T333" s="97" t="s">
+      <c r="N333" s="50"/>
+      <c r="O333" s="50"/>
+      <c r="P333" s="50"/>
+      <c r="Q333" s="50"/>
+      <c r="R333" s="50"/>
+      <c r="S333" s="50"/>
+      <c r="T333" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="U333" s="98"/>
-      <c r="V333" s="98"/>
-      <c r="W333" s="98"/>
-      <c r="X333" s="98"/>
-      <c r="Y333" s="98"/>
-      <c r="Z333" s="98"/>
-      <c r="AA333" s="99"/>
-      <c r="AB333" s="96" t="s">
+      <c r="U333" s="52"/>
+      <c r="V333" s="52"/>
+      <c r="W333" s="52"/>
+      <c r="X333" s="52"/>
+      <c r="Y333" s="52"/>
+      <c r="Z333" s="52"/>
+      <c r="AA333" s="53"/>
+      <c r="AB333" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="AC333" s="96"/>
-      <c r="AD333" s="96"/>
-      <c r="AE333" s="96"/>
-      <c r="AF333" s="96"/>
-      <c r="AG333" s="96"/>
+      <c r="AC333" s="50"/>
+      <c r="AD333" s="50"/>
+      <c r="AE333" s="50"/>
+      <c r="AF333" s="50"/>
+      <c r="AG333" s="50"/>
     </row>
     <row r="334" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D334" s="15"/>
-      <c r="E334" s="71" t="s">
+      <c r="E334" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="F334" s="73"/>
-      <c r="G334" s="73"/>
-      <c r="H334" s="73"/>
-      <c r="I334" s="73"/>
-      <c r="J334" s="73"/>
-      <c r="K334" s="73"/>
-      <c r="L334" s="72"/>
-      <c r="M334" s="96" t="s">
+      <c r="F334" s="74"/>
+      <c r="G334" s="74"/>
+      <c r="H334" s="74"/>
+      <c r="I334" s="74"/>
+      <c r="J334" s="74"/>
+      <c r="K334" s="74"/>
+      <c r="L334" s="55"/>
+      <c r="M334" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="N334" s="96"/>
-      <c r="O334" s="96"/>
-      <c r="P334" s="96"/>
-      <c r="Q334" s="96"/>
-      <c r="R334" s="96"/>
-      <c r="S334" s="96"/>
-      <c r="T334" s="96" t="s">
+      <c r="N334" s="50"/>
+      <c r="O334" s="50"/>
+      <c r="P334" s="50"/>
+      <c r="Q334" s="50"/>
+      <c r="R334" s="50"/>
+      <c r="S334" s="50"/>
+      <c r="T334" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="U334" s="96"/>
-      <c r="V334" s="96"/>
-      <c r="W334" s="96"/>
-      <c r="X334" s="96"/>
-      <c r="Y334" s="96"/>
-      <c r="Z334" s="96"/>
-      <c r="AA334" s="96"/>
-      <c r="AB334" s="96" t="s">
+      <c r="U334" s="50"/>
+      <c r="V334" s="50"/>
+      <c r="W334" s="50"/>
+      <c r="X334" s="50"/>
+      <c r="Y334" s="50"/>
+      <c r="Z334" s="50"/>
+      <c r="AA334" s="50"/>
+      <c r="AB334" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="AC334" s="96"/>
-      <c r="AD334" s="96"/>
-      <c r="AE334" s="96"/>
-      <c r="AF334" s="96"/>
-      <c r="AG334" s="96"/>
+      <c r="AC334" s="50"/>
+      <c r="AD334" s="50"/>
+      <c r="AE334" s="50"/>
+      <c r="AF334" s="50"/>
+      <c r="AG334" s="50"/>
     </row>
     <row r="335" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D335" s="15"/>
-      <c r="E335" s="67" t="s">
+      <c r="E335" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="F335" s="67"/>
-      <c r="G335" s="67"/>
-      <c r="H335" s="67"/>
-      <c r="I335" s="67"/>
-      <c r="J335" s="67"/>
-      <c r="K335" s="71" t="s">
+      <c r="F335" s="75"/>
+      <c r="G335" s="75"/>
+      <c r="H335" s="75"/>
+      <c r="I335" s="75"/>
+      <c r="J335" s="75"/>
+      <c r="K335" s="54" t="s">
         <v>74</v>
       </c>
-      <c r="L335" s="72"/>
-      <c r="M335" s="93" t="s">
+      <c r="L335" s="55"/>
+      <c r="M335" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="N335" s="94"/>
-      <c r="O335" s="94"/>
-      <c r="P335" s="94"/>
-      <c r="Q335" s="94"/>
-      <c r="R335" s="94"/>
-      <c r="S335" s="95"/>
-      <c r="T335" s="93" t="s">
+      <c r="N335" s="48"/>
+      <c r="O335" s="48"/>
+      <c r="P335" s="48"/>
+      <c r="Q335" s="48"/>
+      <c r="R335" s="48"/>
+      <c r="S335" s="49"/>
+      <c r="T335" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="U335" s="94"/>
-      <c r="V335" s="94"/>
-      <c r="W335" s="94"/>
-      <c r="X335" s="94"/>
-      <c r="Y335" s="94"/>
-      <c r="Z335" s="94"/>
-      <c r="AA335" s="94"/>
-      <c r="AB335" s="94"/>
-      <c r="AC335" s="94"/>
-      <c r="AD335" s="94"/>
-      <c r="AE335" s="94"/>
-      <c r="AF335" s="94"/>
-      <c r="AG335" s="95"/>
+      <c r="U335" s="48"/>
+      <c r="V335" s="48"/>
+      <c r="W335" s="48"/>
+      <c r="X335" s="48"/>
+      <c r="Y335" s="48"/>
+      <c r="Z335" s="48"/>
+      <c r="AA335" s="48"/>
+      <c r="AB335" s="48"/>
+      <c r="AC335" s="48"/>
+      <c r="AD335" s="48"/>
+      <c r="AE335" s="48"/>
+      <c r="AF335" s="48"/>
+      <c r="AG335" s="49"/>
     </row>
     <row r="336" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D336" s="15"/>
-      <c r="E336" s="68"/>
-      <c r="F336" s="68"/>
-      <c r="G336" s="68"/>
-      <c r="H336" s="68"/>
-      <c r="I336" s="68"/>
-      <c r="J336" s="68"/>
-      <c r="K336" s="71" t="s">
+      <c r="E336" s="76"/>
+      <c r="F336" s="76"/>
+      <c r="G336" s="76"/>
+      <c r="H336" s="76"/>
+      <c r="I336" s="76"/>
+      <c r="J336" s="76"/>
+      <c r="K336" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="L336" s="72"/>
-      <c r="M336" s="93"/>
-      <c r="N336" s="94"/>
-      <c r="O336" s="94"/>
-      <c r="P336" s="94"/>
-      <c r="Q336" s="94"/>
-      <c r="R336" s="94"/>
-      <c r="S336" s="95"/>
-      <c r="T336" s="93"/>
-      <c r="U336" s="94"/>
-      <c r="V336" s="94"/>
-      <c r="W336" s="94"/>
-      <c r="X336" s="94"/>
-      <c r="Y336" s="94"/>
-      <c r="Z336" s="94"/>
-      <c r="AA336" s="94"/>
-      <c r="AB336" s="94"/>
-      <c r="AC336" s="94"/>
-      <c r="AD336" s="94"/>
-      <c r="AE336" s="94"/>
-      <c r="AF336" s="94"/>
-      <c r="AG336" s="95"/>
+      <c r="L336" s="55"/>
+      <c r="M336" s="47"/>
+      <c r="N336" s="48"/>
+      <c r="O336" s="48"/>
+      <c r="P336" s="48"/>
+      <c r="Q336" s="48"/>
+      <c r="R336" s="48"/>
+      <c r="S336" s="49"/>
+      <c r="T336" s="47"/>
+      <c r="U336" s="48"/>
+      <c r="V336" s="48"/>
+      <c r="W336" s="48"/>
+      <c r="X336" s="48"/>
+      <c r="Y336" s="48"/>
+      <c r="Z336" s="48"/>
+      <c r="AA336" s="48"/>
+      <c r="AB336" s="48"/>
+      <c r="AC336" s="48"/>
+      <c r="AD336" s="48"/>
+      <c r="AE336" s="48"/>
+      <c r="AF336" s="48"/>
+      <c r="AG336" s="49"/>
     </row>
     <row r="337" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D337" s="15"/>
-      <c r="E337" s="69"/>
-      <c r="F337" s="69"/>
-      <c r="G337" s="69"/>
-      <c r="H337" s="69"/>
-      <c r="I337" s="69"/>
-      <c r="J337" s="69"/>
-      <c r="K337" s="71" t="s">
+      <c r="E337" s="77"/>
+      <c r="F337" s="77"/>
+      <c r="G337" s="77"/>
+      <c r="H337" s="77"/>
+      <c r="I337" s="77"/>
+      <c r="J337" s="77"/>
+      <c r="K337" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="L337" s="72"/>
-      <c r="M337" s="93"/>
-      <c r="N337" s="94"/>
-      <c r="O337" s="94"/>
-      <c r="P337" s="94"/>
-      <c r="Q337" s="94"/>
-      <c r="R337" s="94"/>
-      <c r="S337" s="95"/>
-      <c r="T337" s="93"/>
-      <c r="U337" s="94"/>
-      <c r="V337" s="94"/>
-      <c r="W337" s="94"/>
-      <c r="X337" s="94"/>
-      <c r="Y337" s="94"/>
-      <c r="Z337" s="94"/>
-      <c r="AA337" s="94"/>
-      <c r="AB337" s="94"/>
-      <c r="AC337" s="94"/>
-      <c r="AD337" s="94"/>
-      <c r="AE337" s="94"/>
-      <c r="AF337" s="94"/>
-      <c r="AG337" s="95"/>
+      <c r="L337" s="55"/>
+      <c r="M337" s="47"/>
+      <c r="N337" s="48"/>
+      <c r="O337" s="48"/>
+      <c r="P337" s="48"/>
+      <c r="Q337" s="48"/>
+      <c r="R337" s="48"/>
+      <c r="S337" s="49"/>
+      <c r="T337" s="47"/>
+      <c r="U337" s="48"/>
+      <c r="V337" s="48"/>
+      <c r="W337" s="48"/>
+      <c r="X337" s="48"/>
+      <c r="Y337" s="48"/>
+      <c r="Z337" s="48"/>
+      <c r="AA337" s="48"/>
+      <c r="AB337" s="48"/>
+      <c r="AC337" s="48"/>
+      <c r="AD337" s="48"/>
+      <c r="AE337" s="48"/>
+      <c r="AF337" s="48"/>
+      <c r="AG337" s="49"/>
     </row>
     <row r="338" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D338" s="15"/>
@@ -7109,71 +7109,6 @@
     <row r="771" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="I305:M305"/>
-    <mergeCell ref="H306:H309"/>
-    <mergeCell ref="H299:J299"/>
-    <mergeCell ref="K299:U299"/>
-    <mergeCell ref="H300:J300"/>
-    <mergeCell ref="K300:U300"/>
-    <mergeCell ref="H301:J301"/>
-    <mergeCell ref="K301:U301"/>
-    <mergeCell ref="H294:J294"/>
-    <mergeCell ref="K294:U294"/>
-    <mergeCell ref="H295:J295"/>
-    <mergeCell ref="K295:U295"/>
-    <mergeCell ref="H298:J298"/>
-    <mergeCell ref="K298:U298"/>
-    <mergeCell ref="H291:J291"/>
-    <mergeCell ref="K291:U291"/>
-    <mergeCell ref="H292:J292"/>
-    <mergeCell ref="K292:U292"/>
-    <mergeCell ref="H293:J293"/>
-    <mergeCell ref="K293:U293"/>
-    <mergeCell ref="H286:K286"/>
-    <mergeCell ref="L286:AA287"/>
-    <mergeCell ref="H287:K287"/>
-    <mergeCell ref="H288:K288"/>
-    <mergeCell ref="L288:AA288"/>
-    <mergeCell ref="H283:K283"/>
-    <mergeCell ref="L283:AA283"/>
-    <mergeCell ref="H284:K284"/>
-    <mergeCell ref="L284:AA285"/>
-    <mergeCell ref="H285:K285"/>
-    <mergeCell ref="M335:S337"/>
-    <mergeCell ref="T335:AG337"/>
-    <mergeCell ref="M329:S329"/>
-    <mergeCell ref="M330:S330"/>
-    <mergeCell ref="M332:S332"/>
-    <mergeCell ref="M333:S333"/>
-    <mergeCell ref="M334:S334"/>
-    <mergeCell ref="AB333:AG333"/>
-    <mergeCell ref="AB334:AG334"/>
-    <mergeCell ref="T333:AA333"/>
-    <mergeCell ref="T334:AA334"/>
-    <mergeCell ref="M331:S331"/>
-    <mergeCell ref="T327:AG327"/>
-    <mergeCell ref="M327:S327"/>
-    <mergeCell ref="K329:L329"/>
-    <mergeCell ref="K330:L330"/>
-    <mergeCell ref="K332:L332"/>
-    <mergeCell ref="AB328:AG328"/>
-    <mergeCell ref="T328:AA328"/>
-    <mergeCell ref="AB329:AG332"/>
-    <mergeCell ref="T329:AA332"/>
-    <mergeCell ref="K331:L331"/>
-    <mergeCell ref="K335:L335"/>
-    <mergeCell ref="K336:L336"/>
-    <mergeCell ref="K337:L337"/>
-    <mergeCell ref="E333:L333"/>
-    <mergeCell ref="E334:L334"/>
-    <mergeCell ref="E335:J335"/>
-    <mergeCell ref="E336:J336"/>
-    <mergeCell ref="E337:J337"/>
-    <mergeCell ref="E329:J329"/>
-    <mergeCell ref="E330:J330"/>
-    <mergeCell ref="E332:J332"/>
-    <mergeCell ref="M328:S328"/>
-    <mergeCell ref="E331:J331"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="J22:M22"/>
     <mergeCell ref="AF3:AI3"/>
@@ -7187,6 +7122,71 @@
     <mergeCell ref="AF2:AI2"/>
     <mergeCell ref="E3:O3"/>
     <mergeCell ref="AA3:AE3"/>
+    <mergeCell ref="E329:J329"/>
+    <mergeCell ref="E330:J330"/>
+    <mergeCell ref="E332:J332"/>
+    <mergeCell ref="M328:S328"/>
+    <mergeCell ref="E331:J331"/>
+    <mergeCell ref="K335:L335"/>
+    <mergeCell ref="K336:L336"/>
+    <mergeCell ref="K337:L337"/>
+    <mergeCell ref="E333:L333"/>
+    <mergeCell ref="E334:L334"/>
+    <mergeCell ref="E335:J335"/>
+    <mergeCell ref="E336:J336"/>
+    <mergeCell ref="E337:J337"/>
+    <mergeCell ref="T327:AG327"/>
+    <mergeCell ref="M327:S327"/>
+    <mergeCell ref="K329:L329"/>
+    <mergeCell ref="K330:L330"/>
+    <mergeCell ref="K332:L332"/>
+    <mergeCell ref="AB328:AG328"/>
+    <mergeCell ref="T328:AA328"/>
+    <mergeCell ref="AB329:AG332"/>
+    <mergeCell ref="T329:AA332"/>
+    <mergeCell ref="K331:L331"/>
+    <mergeCell ref="M335:S337"/>
+    <mergeCell ref="T335:AG337"/>
+    <mergeCell ref="M329:S329"/>
+    <mergeCell ref="M330:S330"/>
+    <mergeCell ref="M332:S332"/>
+    <mergeCell ref="M333:S333"/>
+    <mergeCell ref="M334:S334"/>
+    <mergeCell ref="AB333:AG333"/>
+    <mergeCell ref="AB334:AG334"/>
+    <mergeCell ref="T333:AA333"/>
+    <mergeCell ref="T334:AA334"/>
+    <mergeCell ref="M331:S331"/>
+    <mergeCell ref="H283:K283"/>
+    <mergeCell ref="L283:AA283"/>
+    <mergeCell ref="H284:K284"/>
+    <mergeCell ref="L284:AA285"/>
+    <mergeCell ref="H285:K285"/>
+    <mergeCell ref="H286:K286"/>
+    <mergeCell ref="L286:AA287"/>
+    <mergeCell ref="H287:K287"/>
+    <mergeCell ref="H288:K288"/>
+    <mergeCell ref="L288:AA288"/>
+    <mergeCell ref="H291:J291"/>
+    <mergeCell ref="K291:U291"/>
+    <mergeCell ref="H292:J292"/>
+    <mergeCell ref="K292:U292"/>
+    <mergeCell ref="H293:J293"/>
+    <mergeCell ref="K293:U293"/>
+    <mergeCell ref="H294:J294"/>
+    <mergeCell ref="K294:U294"/>
+    <mergeCell ref="H295:J295"/>
+    <mergeCell ref="K295:U295"/>
+    <mergeCell ref="H298:J298"/>
+    <mergeCell ref="K298:U298"/>
+    <mergeCell ref="I305:M305"/>
+    <mergeCell ref="H306:H309"/>
+    <mergeCell ref="H299:J299"/>
+    <mergeCell ref="K299:U299"/>
+    <mergeCell ref="H300:J300"/>
+    <mergeCell ref="K300:U300"/>
+    <mergeCell ref="H301:J301"/>
+    <mergeCell ref="K301:U301"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <dataValidations disablePrompts="1" count="1">

--- a/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.5.認証・認可.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.5.認証・認可.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2BE662F-744A-4A4B-8583-11AC3595D993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C972993C-B034-4999-A4C8-A1AA143B3C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1155" yWindow="-120" windowWidth="27765" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="7.5.認証・認可" sheetId="4" r:id="rId1"/>
@@ -1556,29 +1556,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>https://nablarch.github.io/docs/5u21/doc/application_framework/application_framework/libraries/permission_check.html</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Nablarchの認可チェックの詳細に関しては、下記Nablarchガイドの【7.15. 認可チェック】を参照のこと。</t>
-    <rPh sb="9" eb="11">
-      <t>ニンカ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>カキ</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>サンショウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>一般的なフォーム認証方式を採用する。</t>
     <rPh sb="0" eb="3">
       <t>イッパンテキ</t>
@@ -1938,6 +1915,29 @@
     </rPh>
     <rPh sb="43" eb="45">
       <t>セイギョ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/libraries/permission_check.html</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Nablarchの認可チェックの詳細に関しては、下記Nablarchガイドの【認可チェック】を参照のこと。</t>
+    <rPh sb="9" eb="11">
+      <t>ニンカ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カキ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>サンショウ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -1949,7 +1949,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2009,6 +2009,14 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color theme="10"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
       <color theme="10"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -2336,9 +2344,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2350,6 +2355,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3169,9 +3177,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3209,9 +3217,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3244,26 +3252,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3296,26 +3287,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3493,12 +3467,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AI771"/>
-  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="3.6328125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="3.625" style="4"/>
+    <col min="1" max="16384" width="3.6328125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3543,7 +3517,7 @@
       <c r="AH1" s="82"/>
       <c r="AI1" s="83"/>
     </row>
-    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
@@ -3588,7 +3562,7 @@
       <c r="AH2" s="82"/>
       <c r="AI2" s="83"/>
     </row>
-    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -3629,8 +3603,8 @@
       <c r="AH3" s="82"/>
       <c r="AI3" s="83"/>
     </row>
-    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="15" t="s">
         <v>13</v>
       </c>
@@ -3638,8 +3612,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="15" t="str">
         <f>$B$5&amp;"5."</f>
         <v>7.5.</v>
@@ -3648,8 +3622,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D9" s="15" t="str">
         <f>$C$7&amp;"1."</f>
         <v>7.5.1.</v>
@@ -3658,7 +3632,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D10" s="15"/>
       <c r="E10" s="15" t="str">
         <f>$D$9&amp;"1."</f>
@@ -3669,23 +3643,23 @@
         <v>認証機能概要</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F11" s="4" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F12" s="4" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F13" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="15" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E15" s="15" t="str">
         <f>$D$9&amp;"2."</f>
         <v>7.5.1.2.</v>
@@ -3695,7 +3669,7 @@
         <v>認証方法</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F16" s="16"/>
       <c r="G16" s="16"/>
       <c r="H16" s="16"/>
@@ -3726,7 +3700,7 @@
       <c r="AG16" s="16"/>
       <c r="AH16" s="16"/>
     </row>
-    <row r="17" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F17" s="18" t="s">
         <v>27</v>
       </c>
@@ -3763,7 +3737,7 @@
       <c r="AG17" s="19"/>
       <c r="AH17" s="20"/>
     </row>
-    <row r="18" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F18" s="29" t="s">
         <v>20</v>
       </c>
@@ -3800,7 +3774,7 @@
       <c r="AG18" s="30"/>
       <c r="AH18" s="31"/>
     </row>
-    <row r="19" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F19" s="29"/>
       <c r="G19" s="30"/>
       <c r="H19" s="30"/>
@@ -3833,7 +3807,7 @@
       <c r="AG19" s="30"/>
       <c r="AH19" s="31"/>
     </row>
-    <row r="20" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F20" s="29"/>
       <c r="G20" s="30"/>
       <c r="H20" s="30"/>
@@ -3866,7 +3840,7 @@
       <c r="AG20" s="30"/>
       <c r="AH20" s="31"/>
     </row>
-    <row r="21" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F21" s="29"/>
       <c r="G21" s="30"/>
       <c r="H21" s="30"/>
@@ -3897,7 +3871,7 @@
       <c r="AG21" s="30"/>
       <c r="AH21" s="31"/>
     </row>
-    <row r="22" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F22" s="35" t="s">
         <v>91</v>
       </c>
@@ -3934,7 +3908,7 @@
       <c r="AG22" s="36"/>
       <c r="AH22" s="37"/>
     </row>
-    <row r="23" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F23" s="29"/>
       <c r="G23" s="30"/>
       <c r="H23" s="30"/>
@@ -3967,7 +3941,7 @@
       <c r="AG23" s="30"/>
       <c r="AH23" s="31"/>
     </row>
-    <row r="24" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F24" s="29"/>
       <c r="G24" s="30"/>
       <c r="H24" s="30"/>
@@ -4000,7 +3974,7 @@
       <c r="AG24" s="30"/>
       <c r="AH24" s="31"/>
     </row>
-    <row r="25" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F25" s="29"/>
       <c r="G25" s="30"/>
       <c r="H25" s="30"/>
@@ -4033,7 +4007,7 @@
       <c r="AG25" s="30"/>
       <c r="AH25" s="31"/>
     </row>
-    <row r="26" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F26" s="29"/>
       <c r="G26" s="30"/>
       <c r="H26" s="30"/>
@@ -4064,7 +4038,7 @@
       <c r="AG26" s="30"/>
       <c r="AH26" s="31"/>
     </row>
-    <row r="27" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F27" s="29"/>
       <c r="G27" s="30"/>
       <c r="H27" s="30"/>
@@ -4097,7 +4071,7 @@
       <c r="AG27" s="30"/>
       <c r="AH27" s="31"/>
     </row>
-    <row r="28" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F28" s="29"/>
       <c r="G28" s="30"/>
       <c r="H28" s="30"/>
@@ -4130,7 +4104,7 @@
       <c r="AG28" s="30"/>
       <c r="AH28" s="31"/>
     </row>
-    <row r="29" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F29" s="32"/>
       <c r="G29" s="33"/>
       <c r="H29" s="33"/>
@@ -4161,7 +4135,7 @@
       <c r="AG29" s="33"/>
       <c r="AH29" s="34"/>
     </row>
-    <row r="30" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F30" s="16"/>
       <c r="G30" s="16"/>
       <c r="H30" s="16"/>
@@ -4192,7 +4166,7 @@
       <c r="AG30" s="16"/>
       <c r="AH30" s="16"/>
     </row>
-    <row r="31" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F31" s="16"/>
       <c r="G31" s="16"/>
       <c r="H31" s="16"/>
@@ -4223,7 +4197,7 @@
       <c r="AG31" s="16"/>
       <c r="AH31" s="16"/>
     </row>
-    <row r="32" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E32" s="15" t="str">
         <f>$D$9&amp;"3."</f>
         <v>7.5.1.3.</v>
@@ -4233,7 +4207,7 @@
         <v>認証機能詳細</v>
       </c>
     </row>
-    <row r="33" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F33" s="15" t="s">
         <v>9</v>
       </c>
@@ -4241,52 +4215,52 @@
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F34" s="15"/>
       <c r="G34" s="4" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F35" s="15"/>
       <c r="G35" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="36" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="36" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F36" s="15"/>
       <c r="G36" s="4" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="37" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F37" s="15"/>
       <c r="G37" s="4" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="38" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F38" s="15"/>
       <c r="G38" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F39" s="15"/>
       <c r="G39" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F40" s="15"/>
     </row>
-    <row r="41" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F41" s="15"/>
     </row>
-    <row r="42" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F42" s="15"/>
     </row>
-    <row r="43" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F43" s="15"/>
       <c r="G43" s="15" t="s">
         <v>66</v>
@@ -4295,79 +4269,79 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F44" s="15"/>
       <c r="G44" s="15"/>
       <c r="H44" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="45" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F45" s="15"/>
       <c r="G45" s="15"/>
       <c r="H45" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="46" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F46" s="15"/>
       <c r="G46" s="15"/>
     </row>
-    <row r="47" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F47" s="15"/>
       <c r="G47" s="15"/>
     </row>
-    <row r="48" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F48" s="15"/>
       <c r="G48" s="15"/>
     </row>
-    <row r="49" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F49" s="15"/>
       <c r="G49" s="15"/>
     </row>
-    <row r="50" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F50" s="15"/>
       <c r="G50" s="15"/>
     </row>
-    <row r="51" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F51" s="15"/>
       <c r="G51" s="15"/>
     </row>
-    <row r="52" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F52" s="15"/>
       <c r="G52" s="15"/>
     </row>
-    <row r="53" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F53" s="15"/>
       <c r="G53" s="15"/>
     </row>
-    <row r="54" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F54" s="15"/>
       <c r="G54" s="15"/>
     </row>
-    <row r="55" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F55" s="15"/>
       <c r="G55" s="15"/>
     </row>
-    <row r="56" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F56" s="15"/>
       <c r="G56" s="15"/>
     </row>
-    <row r="57" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F57" s="15"/>
       <c r="G57" s="15"/>
     </row>
-    <row r="58" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F58" s="15"/>
       <c r="G58" s="15"/>
     </row>
-    <row r="59" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F59" s="15"/>
     </row>
-    <row r="60" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F60" s="15"/>
     </row>
-    <row r="61" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F61" s="15"/>
       <c r="G61" s="15" t="s">
         <v>37</v>
@@ -4376,61 +4350,61 @@
         <v>58</v>
       </c>
     </row>
-    <row r="62" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F62" s="15"/>
       <c r="H62" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="63" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F63" s="15"/>
       <c r="H63" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="64" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F64" s="15"/>
     </row>
-    <row r="65" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F65" s="15"/>
     </row>
-    <row r="66" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F66" s="15"/>
     </row>
-    <row r="67" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F67" s="15"/>
     </row>
-    <row r="68" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F68" s="15"/>
     </row>
-    <row r="69" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F69" s="15"/>
     </row>
-    <row r="70" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F70" s="15"/>
     </row>
-    <row r="71" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F71" s="15"/>
     </row>
-    <row r="72" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F72" s="15"/>
     </row>
-    <row r="73" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F73" s="15"/>
     </row>
-    <row r="74" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F74" s="15"/>
     </row>
-    <row r="75" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F75" s="15"/>
     </row>
-    <row r="76" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F76" s="15"/>
     </row>
-    <row r="77" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F77" s="15"/>
     </row>
-    <row r="78" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F78" s="15"/>
       <c r="G78" s="15" t="s">
         <v>38</v>
@@ -4439,55 +4413,55 @@
         <v>33</v>
       </c>
     </row>
-    <row r="79" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F79" s="15"/>
       <c r="H79" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="6:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F80" s="15"/>
     </row>
-    <row r="81" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F81" s="15"/>
     </row>
-    <row r="82" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F82" s="15"/>
     </row>
-    <row r="83" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F83" s="15"/>
     </row>
-    <row r="84" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F84" s="15"/>
     </row>
-    <row r="85" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F85" s="15"/>
     </row>
-    <row r="86" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F86" s="15"/>
     </row>
-    <row r="87" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F87" s="15"/>
     </row>
-    <row r="88" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F88" s="15"/>
     </row>
-    <row r="89" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F89" s="15"/>
     </row>
-    <row r="90" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F90" s="15"/>
     </row>
-    <row r="91" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F91" s="15"/>
     </row>
-    <row r="92" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F92" s="15"/>
     </row>
-    <row r="93" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F93" s="15"/>
     </row>
-    <row r="94" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F94" s="15"/>
       <c r="G94" s="15" t="s">
         <v>39</v>
@@ -4496,7 +4470,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="95" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F95" s="15"/>
       <c r="H95" s="15" t="s">
         <v>40</v>
@@ -4505,25 +4479,25 @@
         <v>36</v>
       </c>
     </row>
-    <row r="96" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F96" s="15"/>
       <c r="I96" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="97" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F97" s="15"/>
       <c r="I97" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="98" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F98" s="15"/>
     </row>
-    <row r="99" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F99" s="15"/>
     </row>
-    <row r="100" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F100" s="15" t="s">
         <v>29</v>
       </c>
@@ -4531,22 +4505,22 @@
         <v>93</v>
       </c>
     </row>
-    <row r="101" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F101" s="15"/>
       <c r="G101" s="4" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="102" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="102" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F102" s="15"/>
       <c r="G102" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="103" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="103" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F103" s="15"/>
     </row>
-    <row r="104" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F104" s="15"/>
       <c r="G104" s="15" t="s">
         <v>31</v>
@@ -4555,16 +4529,16 @@
         <v>124</v>
       </c>
     </row>
-    <row r="105" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F105" s="15"/>
       <c r="H105" s="4" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="106" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F106" s="15"/>
     </row>
-    <row r="107" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F107" s="15"/>
       <c r="H107" s="4" t="s">
         <v>126</v>
@@ -4573,22 +4547,22 @@
         <v>118</v>
       </c>
     </row>
-    <row r="108" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F108" s="15"/>
       <c r="L108" s="4" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="109" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F109" s="15"/>
       <c r="L109" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="110" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F110" s="15"/>
     </row>
-    <row r="111" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F111" s="15"/>
       <c r="H111" s="4" t="s">
         <v>127</v>
@@ -4597,19 +4571,19 @@
         <v>128</v>
       </c>
     </row>
-    <row r="112" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="6:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F112" s="15"/>
       <c r="L112" s="4" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="113" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F113" s="15"/>
     </row>
-    <row r="114" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F114" s="15"/>
     </row>
-    <row r="115" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F115" s="15"/>
       <c r="G115" s="15" t="s">
         <v>31</v>
@@ -4618,22 +4592,22 @@
         <v>130</v>
       </c>
     </row>
-    <row r="116" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F116" s="15"/>
       <c r="H116" s="4" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="117" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F117" s="15"/>
       <c r="H117" s="4" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="118" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F118" s="15"/>
     </row>
-    <row r="119" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F119" s="15"/>
       <c r="H119" s="15" t="s">
         <v>61</v>
@@ -4642,65 +4616,65 @@
         <v>41</v>
       </c>
     </row>
-    <row r="120" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F120" s="15"/>
       <c r="I120" s="4" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="121" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F121" s="15"/>
       <c r="I121" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="122" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F122" s="15"/>
       <c r="I122" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="123" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F123" s="15"/>
     </row>
-    <row r="124" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F124" s="15"/>
       <c r="I124" s="22"/>
     </row>
-    <row r="125" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F125" s="15"/>
     </row>
-    <row r="126" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F126" s="15"/>
     </row>
-    <row r="127" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F127" s="15"/>
     </row>
-    <row r="128" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F128" s="15"/>
     </row>
-    <row r="129" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F129" s="15"/>
     </row>
-    <row r="130" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F130" s="15"/>
     </row>
-    <row r="131" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F131" s="15"/>
     </row>
-    <row r="132" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F132" s="15"/>
     </row>
-    <row r="133" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F133" s="15"/>
     </row>
-    <row r="134" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F134" s="15"/>
     </row>
-    <row r="135" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F135" s="15"/>
     </row>
-    <row r="136" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F136" s="15"/>
       <c r="H136" s="15" t="s">
         <v>62</v>
@@ -4709,55 +4683,55 @@
         <v>58</v>
       </c>
     </row>
-    <row r="137" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F137" s="15"/>
       <c r="I137" s="4" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="138" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F138" s="15"/>
       <c r="I138" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="139" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F139" s="15"/>
     </row>
-    <row r="140" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F140" s="15"/>
     </row>
-    <row r="141" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F141" s="15"/>
     </row>
-    <row r="142" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F142" s="15"/>
     </row>
-    <row r="143" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="143" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F143" s="15"/>
     </row>
-    <row r="144" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="144" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F144" s="15"/>
     </row>
-    <row r="145" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="145" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F145" s="15"/>
     </row>
-    <row r="146" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="146" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F146" s="15"/>
     </row>
-    <row r="147" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="147" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F147" s="15"/>
     </row>
-    <row r="148" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="148" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F148" s="15"/>
     </row>
-    <row r="149" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="149" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F149" s="15"/>
     </row>
-    <row r="150" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F150" s="15"/>
     </row>
-    <row r="151" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F151" s="15"/>
       <c r="H151" s="15" t="s">
         <v>63</v>
@@ -4766,58 +4740,58 @@
         <v>34</v>
       </c>
     </row>
-    <row r="152" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="152" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F152" s="15"/>
       <c r="I152" s="4" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="153" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="153" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F153" s="15"/>
     </row>
-    <row r="154" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="154" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F154" s="15"/>
     </row>
-    <row r="155" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="155" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F155" s="15"/>
     </row>
-    <row r="156" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="156" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F156" s="15"/>
     </row>
-    <row r="157" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="157" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F157" s="15"/>
     </row>
-    <row r="158" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="158" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F158" s="15"/>
     </row>
-    <row r="159" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="159" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F159" s="15"/>
     </row>
-    <row r="160" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="160" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F160" s="15"/>
     </row>
-    <row r="161" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="161" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F161" s="15"/>
     </row>
-    <row r="162" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="162" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F162" s="15"/>
     </row>
-    <row r="163" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="163" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F163" s="15"/>
     </row>
-    <row r="164" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="164" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F164" s="15"/>
     </row>
-    <row r="165" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="165" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F165" s="15"/>
     </row>
-    <row r="166" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="166" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F166" s="15"/>
     </row>
-    <row r="167" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="167" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F167" s="15"/>
     </row>
-    <row r="168" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="168" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F168" s="15"/>
       <c r="H168" s="15" t="s">
         <v>60</v>
@@ -4826,7 +4800,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="169" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="169" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F169" s="15"/>
       <c r="I169" s="15" t="s">
         <v>64</v>
@@ -4835,16 +4809,16 @@
         <v>36</v>
       </c>
     </row>
-    <row r="170" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="170" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F170" s="15"/>
       <c r="J170" s="4" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="171" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="171" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F171" s="15"/>
     </row>
-    <row r="172" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="172" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F172" s="15"/>
       <c r="G172" s="15" t="s">
         <v>32</v>
@@ -4853,22 +4827,22 @@
         <v>134</v>
       </c>
     </row>
-    <row r="173" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="173" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F173" s="15"/>
       <c r="H173" s="4" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="174" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="174" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F174" s="15"/>
       <c r="H174" s="4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="175" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="175" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F175" s="15"/>
     </row>
-    <row r="176" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="176" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F176" s="15"/>
       <c r="H176" s="15" t="s">
         <v>65</v>
@@ -4877,61 +4851,61 @@
         <v>41</v>
       </c>
     </row>
-    <row r="177" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="177" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F177" s="15"/>
       <c r="I177" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="178" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="178" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F178" s="15"/>
       <c r="I178" s="4" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="179" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="179" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F179" s="15"/>
       <c r="I179" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="180" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="180" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F180" s="15"/>
     </row>
-    <row r="181" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="181" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F181" s="15"/>
     </row>
-    <row r="182" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="182" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F182" s="15"/>
     </row>
-    <row r="183" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F183" s="15"/>
     </row>
-    <row r="184" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="184" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F184" s="15"/>
     </row>
-    <row r="185" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="185" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F185" s="15"/>
     </row>
-    <row r="186" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F186" s="15"/>
     </row>
-    <row r="187" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F187" s="15"/>
     </row>
-    <row r="188" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="188" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F188" s="15"/>
     </row>
-    <row r="189" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="189" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F189" s="15"/>
     </row>
-    <row r="190" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="190" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F190" s="15"/>
     </row>
-    <row r="191" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="191" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F191" s="15"/>
     </row>
-    <row r="192" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="192" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F192" s="15"/>
       <c r="H192" s="15" t="s">
         <v>68</v>
@@ -4940,22 +4914,22 @@
         <v>58</v>
       </c>
     </row>
-    <row r="193" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="193" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F193" s="15"/>
       <c r="I193" s="21" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="194" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="194" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F194" s="15"/>
     </row>
-    <row r="195" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="195" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F195" s="15"/>
     </row>
-    <row r="196" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="196" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F196" s="15"/>
     </row>
-    <row r="197" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="197" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F197" s="15"/>
       <c r="H197" s="15" t="s">
         <v>70</v>
@@ -4964,85 +4938,85 @@
         <v>34</v>
       </c>
     </row>
-    <row r="198" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="198" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F198" s="15"/>
       <c r="I198" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="199" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="199" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F199" s="15"/>
     </row>
-    <row r="200" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="200" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F200" s="15"/>
     </row>
-    <row r="201" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="201" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F201" s="15"/>
     </row>
-    <row r="202" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="202" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F202" s="15"/>
     </row>
-    <row r="203" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="203" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F203" s="15"/>
     </row>
-    <row r="204" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="204" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F204" s="15"/>
     </row>
-    <row r="205" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="205" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F205" s="15"/>
     </row>
-    <row r="206" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="206" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F206" s="15"/>
     </row>
-    <row r="207" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="207" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F207" s="15"/>
     </row>
-    <row r="208" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="208" spans="6:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F208" s="15"/>
     </row>
-    <row r="209" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="209" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F209" s="15"/>
     </row>
-    <row r="210" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="210" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F210" s="15"/>
     </row>
-    <row r="211" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="211" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F211" s="15"/>
     </row>
-    <row r="212" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="212" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F212" s="15"/>
     </row>
-    <row r="213" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="213" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F213" s="15"/>
     </row>
-    <row r="214" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="214" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F214" s="15"/>
     </row>
-    <row r="215" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="215" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F215" s="15"/>
     </row>
-    <row r="216" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="216" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F216" s="15"/>
     </row>
-    <row r="217" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="217" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F217" s="15"/>
     </row>
-    <row r="218" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="218" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F218" s="15"/>
     </row>
-    <row r="219" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="219" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F219" s="15"/>
     </row>
-    <row r="220" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="220" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F220" s="15"/>
     </row>
-    <row r="221" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="221" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F221" s="15"/>
     </row>
-    <row r="222" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="222" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F222" s="15"/>
     </row>
-    <row r="223" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="223" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F223" s="15"/>
       <c r="H223" s="15" t="s">
         <v>71</v>
@@ -5051,7 +5025,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="224" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="224" spans="6:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F224" s="15"/>
       <c r="I224" s="15" t="s">
         <v>72</v>
@@ -5060,28 +5034,28 @@
         <v>36</v>
       </c>
     </row>
-    <row r="225" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="225" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F225" s="15"/>
       <c r="J225" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="226" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="226" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F226" s="15"/>
       <c r="J226" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="227" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="227" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F227" s="15"/>
       <c r="J227" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="228" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="228" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F228" s="15"/>
     </row>
-    <row r="229" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="229" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F229" s="15"/>
       <c r="I229" s="15" t="s">
         <v>73</v>
@@ -5090,25 +5064,25 @@
         <v>139</v>
       </c>
     </row>
-    <row r="230" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="230" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F230" s="15"/>
       <c r="J230" s="4" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="231" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="231" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F231" s="15"/>
       <c r="J231" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="232" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="232" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F232" s="15"/>
     </row>
-    <row r="233" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="233" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F233" s="15"/>
     </row>
-    <row r="234" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="234" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D234" s="15" t="str">
         <f>$C$7&amp;"2."</f>
         <v>7.5.2.</v>
@@ -5117,7 +5091,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="235" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="235" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D235" s="15"/>
       <c r="E235" s="15" t="str">
         <f>$D$234&amp;"1."</f>
@@ -5128,22 +5102,22 @@
         <v>認可機能概要</v>
       </c>
     </row>
-    <row r="236" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="236" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D236" s="15"/>
       <c r="F236" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="237" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="237" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D237" s="15"/>
       <c r="F237" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="238" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="238" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D238" s="15"/>
     </row>
-    <row r="239" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="239" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D239" s="15"/>
       <c r="E239" s="15" t="str">
         <f>$D$234&amp;"2."</f>
@@ -5154,7 +5128,7 @@
         <v>認可方法</v>
       </c>
     </row>
-    <row r="240" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="240" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F240" s="17"/>
       <c r="G240" s="17"/>
       <c r="H240" s="17"/>
@@ -5185,7 +5159,7 @@
       <c r="AG240" s="17"/>
       <c r="AH240" s="17"/>
     </row>
-    <row r="241" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="241" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F241" s="17"/>
       <c r="G241" s="17"/>
       <c r="H241" s="17"/>
@@ -5216,7 +5190,7 @@
       <c r="AG241" s="17"/>
       <c r="AH241" s="17"/>
     </row>
-    <row r="242" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="242" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F242" s="18" t="s">
         <v>27</v>
       </c>
@@ -5253,7 +5227,7 @@
       <c r="AG242" s="19"/>
       <c r="AH242" s="20"/>
     </row>
-    <row r="243" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="243" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F243" s="29" t="s">
         <v>15</v>
       </c>
@@ -5290,7 +5264,7 @@
       <c r="AG243" s="30"/>
       <c r="AH243" s="31"/>
     </row>
-    <row r="244" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="244" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F244" s="29"/>
       <c r="G244" s="30"/>
       <c r="H244" s="30"/>
@@ -5321,7 +5295,7 @@
       <c r="AG244" s="30"/>
       <c r="AH244" s="31"/>
     </row>
-    <row r="245" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="245" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F245" s="29"/>
       <c r="G245" s="30"/>
       <c r="H245" s="30"/>
@@ -5352,7 +5326,7 @@
       <c r="AG245" s="30"/>
       <c r="AH245" s="31"/>
     </row>
-    <row r="246" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="246" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F246" s="35" t="s">
         <v>91</v>
       </c>
@@ -5389,7 +5363,7 @@
       <c r="AG246" s="36"/>
       <c r="AH246" s="37"/>
     </row>
-    <row r="247" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="247" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F247" s="29"/>
       <c r="G247" s="30"/>
       <c r="H247" s="30"/>
@@ -5420,7 +5394,7 @@
       <c r="AG247" s="30"/>
       <c r="AH247" s="31"/>
     </row>
-    <row r="248" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="248" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F248" s="32"/>
       <c r="G248" s="33"/>
       <c r="H248" s="33"/>
@@ -5451,7 +5425,7 @@
       <c r="AG248" s="33"/>
       <c r="AH248" s="34"/>
     </row>
-    <row r="249" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="249" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F249" s="17"/>
       <c r="G249" s="17"/>
       <c r="H249" s="17"/>
@@ -5482,7 +5456,7 @@
       <c r="AG249" s="17"/>
       <c r="AH249" s="17"/>
     </row>
-    <row r="250" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="250" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F250" s="17"/>
       <c r="G250" s="17"/>
       <c r="H250" s="17"/>
@@ -5513,10 +5487,10 @@
       <c r="AG250" s="17"/>
       <c r="AH250" s="17"/>
     </row>
-    <row r="251" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="251" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D251" s="15"/>
     </row>
-    <row r="252" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="252" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D252" s="15"/>
       <c r="E252" s="15" t="str">
         <f>$D$234&amp;"3."</f>
@@ -5527,91 +5501,91 @@
         <v>認可機能詳細</v>
       </c>
     </row>
-    <row r="253" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="253" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D253" s="15"/>
       <c r="E253" s="15"/>
       <c r="F253" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="254" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="254" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D254" s="15"/>
       <c r="E254" s="15"/>
       <c r="F254" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="255" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="255" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D255" s="15"/>
       <c r="E255" s="15"/>
     </row>
-    <row r="256" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="256" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D256" s="15"/>
       <c r="E256" s="15"/>
     </row>
-    <row r="257" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="257" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D257" s="15"/>
       <c r="E257" s="15"/>
     </row>
-    <row r="258" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="258" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D258" s="15"/>
       <c r="E258" s="15"/>
     </row>
-    <row r="259" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="259" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D259" s="15"/>
       <c r="E259" s="15"/>
     </row>
-    <row r="260" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="260" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D260" s="15"/>
       <c r="E260" s="15"/>
     </row>
-    <row r="261" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="261" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D261" s="15"/>
       <c r="E261" s="15"/>
     </row>
-    <row r="262" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="262" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D262" s="15"/>
       <c r="E262" s="15"/>
     </row>
-    <row r="263" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="263" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D263" s="15"/>
       <c r="E263" s="15"/>
     </row>
-    <row r="264" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="264" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D264" s="15"/>
       <c r="E264" s="15"/>
     </row>
-    <row r="265" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="265" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D265" s="15"/>
       <c r="E265" s="15"/>
     </row>
-    <row r="266" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="266" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D266" s="15"/>
       <c r="E266" s="15"/>
     </row>
-    <row r="267" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="267" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D267" s="15"/>
       <c r="E267" s="15"/>
       <c r="G267" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="268" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="268" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D268" s="15"/>
       <c r="E268" s="15"/>
     </row>
-    <row r="269" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="269" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D269" s="15"/>
       <c r="E269" s="15"/>
-      <c r="G269" s="38" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="270" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G269" s="42" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="270" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D270" s="15"/>
       <c r="E270" s="15"/>
     </row>
-    <row r="271" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="271" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D271" s="15"/>
       <c r="E271" s="15"/>
       <c r="F271" s="21" t="s">
@@ -5621,39 +5595,39 @@
         <v>56</v>
       </c>
     </row>
-    <row r="272" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="272" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D272" s="15"/>
       <c r="E272" s="15"/>
       <c r="G272" s="4" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="273" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="273" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D273" s="15"/>
       <c r="E273" s="15"/>
       <c r="G273" s="4" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="274" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="274" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D274" s="15"/>
       <c r="E274" s="15"/>
       <c r="G274" s="4" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="275" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="275" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D275" s="15"/>
       <c r="E275" s="15"/>
       <c r="G275" s="4" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="276" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="276" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D276" s="15"/>
       <c r="E276" s="15"/>
     </row>
-    <row r="277" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="277" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D277" s="15"/>
       <c r="E277" s="15"/>
       <c r="F277" s="21" t="s">
@@ -5663,49 +5637,49 @@
         <v>96</v>
       </c>
     </row>
-    <row r="278" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="278" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D278" s="15"/>
       <c r="E278" s="15"/>
       <c r="G278" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="279" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="279" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D279" s="15"/>
       <c r="E279" s="15"/>
       <c r="G279" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="280" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="280" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D280" s="15"/>
       <c r="E280" s="15"/>
       <c r="G280" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="281" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="281" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D281" s="15"/>
       <c r="E281" s="15"/>
     </row>
-    <row r="282" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="282" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D282" s="15"/>
       <c r="E282" s="15"/>
       <c r="G282" s="22" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="283" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="283" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D283" s="15"/>
       <c r="E283" s="15"/>
       <c r="H283" s="46" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I283" s="46"/>
       <c r="J283" s="46"/>
       <c r="K283" s="46"/>
       <c r="L283" s="46" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="M283" s="46"/>
       <c r="N283" s="46"/>
@@ -5723,17 +5697,17 @@
       <c r="Z283" s="46"/>
       <c r="AA283" s="46"/>
     </row>
-    <row r="284" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="284" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D284" s="15"/>
       <c r="E284" s="15"/>
       <c r="H284" s="45" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I284" s="45"/>
       <c r="J284" s="45"/>
       <c r="K284" s="45"/>
       <c r="L284" s="45" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="M284" s="45"/>
       <c r="N284" s="45"/>
@@ -5751,11 +5725,11 @@
       <c r="Z284" s="45"/>
       <c r="AA284" s="45"/>
     </row>
-    <row r="285" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="285" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D285" s="15"/>
       <c r="E285" s="15"/>
       <c r="H285" s="45" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I285" s="45"/>
       <c r="J285" s="45"/>
@@ -5777,17 +5751,17 @@
       <c r="Z285" s="45"/>
       <c r="AA285" s="45"/>
     </row>
-    <row r="286" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="286" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D286" s="15"/>
       <c r="E286" s="15"/>
       <c r="H286" s="45" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I286" s="45"/>
       <c r="J286" s="45"/>
       <c r="K286" s="45"/>
       <c r="L286" s="45" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="M286" s="45"/>
       <c r="N286" s="45"/>
@@ -5805,11 +5779,11 @@
       <c r="Z286" s="45"/>
       <c r="AA286" s="45"/>
     </row>
-    <row r="287" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="287" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D287" s="15"/>
       <c r="E287" s="15"/>
       <c r="H287" s="45" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I287" s="45"/>
       <c r="J287" s="45"/>
@@ -5831,17 +5805,17 @@
       <c r="Z287" s="45"/>
       <c r="AA287" s="45"/>
     </row>
-    <row r="288" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="288" spans="4:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D288" s="15"/>
       <c r="E288" s="15"/>
       <c r="H288" s="45" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I288" s="45"/>
       <c r="J288" s="45"/>
       <c r="K288" s="45"/>
       <c r="L288" s="45" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="M288" s="45"/>
       <c r="N288" s="45"/>
@@ -5859,27 +5833,27 @@
       <c r="Z288" s="45"/>
       <c r="AA288" s="45"/>
     </row>
-    <row r="289" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="289" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D289" s="15"/>
       <c r="E289" s="15"/>
     </row>
-    <row r="290" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="290" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D290" s="15"/>
       <c r="E290" s="15"/>
       <c r="G290" s="22" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="291" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="291" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D291" s="15"/>
       <c r="E291" s="15"/>
       <c r="H291" s="46" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I291" s="46"/>
       <c r="J291" s="46"/>
       <c r="K291" s="46" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L291" s="46"/>
       <c r="M291" s="46"/>
@@ -5892,16 +5866,16 @@
       <c r="T291" s="46"/>
       <c r="U291" s="46"/>
     </row>
-    <row r="292" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="292" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D292" s="15"/>
       <c r="E292" s="15"/>
       <c r="H292" s="45" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I292" s="45"/>
       <c r="J292" s="45"/>
       <c r="K292" s="45" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L292" s="45"/>
       <c r="M292" s="45"/>
@@ -5914,16 +5888,16 @@
       <c r="T292" s="45"/>
       <c r="U292" s="45"/>
     </row>
-    <row r="293" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="293" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D293" s="15"/>
       <c r="E293" s="15"/>
       <c r="H293" s="45" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I293" s="45"/>
       <c r="J293" s="45"/>
       <c r="K293" s="45" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L293" s="45"/>
       <c r="M293" s="45"/>
@@ -5936,16 +5910,16 @@
       <c r="T293" s="45"/>
       <c r="U293" s="45"/>
     </row>
-    <row r="294" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="294" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D294" s="15"/>
       <c r="E294" s="15"/>
       <c r="H294" s="45" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I294" s="45"/>
       <c r="J294" s="45"/>
       <c r="K294" s="45" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L294" s="45"/>
       <c r="M294" s="45"/>
@@ -5958,16 +5932,16 @@
       <c r="T294" s="45"/>
       <c r="U294" s="45"/>
     </row>
-    <row r="295" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="295" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D295" s="15"/>
       <c r="E295" s="15"/>
       <c r="H295" s="45" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I295" s="45"/>
       <c r="J295" s="45"/>
       <c r="K295" s="45" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="L295" s="45"/>
       <c r="M295" s="45"/>
@@ -5980,27 +5954,27 @@
       <c r="T295" s="45"/>
       <c r="U295" s="45"/>
     </row>
-    <row r="296" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="296" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D296" s="15"/>
       <c r="E296" s="15"/>
     </row>
-    <row r="297" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="297" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D297" s="15"/>
       <c r="E297" s="15"/>
       <c r="G297" s="22" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="298" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="298" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D298" s="15"/>
       <c r="E298" s="15"/>
       <c r="H298" s="46" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I298" s="46"/>
       <c r="J298" s="46"/>
       <c r="K298" s="46" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L298" s="46"/>
       <c r="M298" s="46"/>
@@ -6013,16 +5987,16 @@
       <c r="T298" s="46"/>
       <c r="U298" s="46"/>
     </row>
-    <row r="299" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="299" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D299" s="15"/>
       <c r="E299" s="15"/>
       <c r="H299" s="45" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I299" s="45"/>
       <c r="J299" s="45"/>
       <c r="K299" s="45" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L299" s="45"/>
       <c r="M299" s="45"/>
@@ -6035,16 +6009,16 @@
       <c r="T299" s="45"/>
       <c r="U299" s="45"/>
     </row>
-    <row r="300" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="300" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D300" s="15"/>
       <c r="E300" s="15"/>
       <c r="H300" s="45" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I300" s="45"/>
       <c r="J300" s="45"/>
       <c r="K300" s="45" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="L300" s="45"/>
       <c r="M300" s="45"/>
@@ -6057,16 +6031,16 @@
       <c r="T300" s="45"/>
       <c r="U300" s="45"/>
     </row>
-    <row r="301" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="301" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D301" s="15"/>
       <c r="E301" s="15"/>
       <c r="H301" s="45" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I301" s="45"/>
       <c r="J301" s="45"/>
       <c r="K301" s="45" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L301" s="45"/>
       <c r="M301" s="45"/>
@@ -6079,191 +6053,191 @@
       <c r="T301" s="45"/>
       <c r="U301" s="45"/>
     </row>
-    <row r="302" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="302" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D302" s="15"/>
       <c r="E302" s="15"/>
     </row>
-    <row r="303" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="303" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D303" s="15"/>
       <c r="E303" s="15"/>
       <c r="G303" s="4" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="304" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="304" spans="4:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D304" s="15"/>
       <c r="E304" s="15"/>
     </row>
-    <row r="305" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="305" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D305" s="15"/>
       <c r="E305" s="15"/>
       <c r="F305" s="15"/>
-      <c r="H305" s="40"/>
+      <c r="H305" s="39"/>
       <c r="I305" s="43" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J305" s="43"/>
       <c r="K305" s="43"/>
       <c r="L305" s="43"/>
       <c r="M305" s="43"/>
     </row>
-    <row r="306" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="306" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D306" s="15"/>
       <c r="E306" s="15"/>
       <c r="F306" s="15"/>
       <c r="H306" s="44" t="s">
-        <v>175</v>
-      </c>
-      <c r="I306" s="39"/>
-      <c r="J306" s="39" t="s">
-        <v>169</v>
-      </c>
-      <c r="K306" s="39" t="s">
+        <v>173</v>
+      </c>
+      <c r="I306" s="38"/>
+      <c r="J306" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="K306" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="L306" s="38" t="s">
         <v>170</v>
       </c>
-      <c r="L306" s="39" t="s">
-        <v>172</v>
-      </c>
-      <c r="M306" s="39" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="307" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M306" s="38" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="307" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D307" s="15"/>
       <c r="E307" s="15"/>
       <c r="F307" s="15"/>
       <c r="H307" s="44"/>
-      <c r="I307" s="39" t="s">
-        <v>177</v>
-      </c>
-      <c r="J307" s="41" t="s">
-        <v>184</v>
-      </c>
-      <c r="K307" s="41" t="s">
-        <v>184</v>
-      </c>
-      <c r="L307" s="41" t="s">
-        <v>184</v>
-      </c>
-      <c r="M307" s="41" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="308" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I307" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="J307" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="K307" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="L307" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="M307" s="40" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="308" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D308" s="15"/>
       <c r="E308" s="15"/>
       <c r="F308" s="15"/>
       <c r="H308" s="44"/>
-      <c r="I308" s="39" t="s">
-        <v>179</v>
-      </c>
-      <c r="J308" s="41" t="s">
-        <v>185</v>
-      </c>
-      <c r="K308" s="41" t="s">
+      <c r="I308" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="J308" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="K308" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="L308" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="M308" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="P308" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="L308" s="41" t="s">
-        <v>185</v>
-      </c>
-      <c r="M308" s="41" t="s">
-        <v>184</v>
-      </c>
-      <c r="P308" s="4" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="309" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="309" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D309" s="15"/>
       <c r="E309" s="15"/>
       <c r="F309" s="15"/>
       <c r="H309" s="44"/>
-      <c r="I309" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="J309" s="41" t="s">
+      <c r="I309" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="J309" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="K309" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="L309" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="M309" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="P309" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="K309" s="41" t="s">
-        <v>184</v>
-      </c>
-      <c r="L309" s="41" t="s">
-        <v>185</v>
-      </c>
-      <c r="M309" s="41" t="s">
-        <v>185</v>
-      </c>
-      <c r="P309" s="4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="310" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="310" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D310" s="15"/>
       <c r="E310" s="15"/>
       <c r="F310" s="15"/>
       <c r="H310" s="15"/>
       <c r="I310" s="15"/>
-      <c r="J310" s="42"/>
-      <c r="K310" s="42"/>
-      <c r="L310" s="42"/>
-      <c r="M310" s="42"/>
-    </row>
-    <row r="311" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J310" s="41"/>
+      <c r="K310" s="41"/>
+      <c r="L310" s="41"/>
+      <c r="M310" s="41"/>
+    </row>
+    <row r="311" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D311" s="15"/>
       <c r="E311" s="15"/>
       <c r="G311" s="22" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="312" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="312" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D312" s="15"/>
       <c r="E312" s="15"/>
       <c r="G312" s="22"/>
     </row>
-    <row r="313" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="313" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D313" s="15"/>
       <c r="E313" s="15"/>
     </row>
-    <row r="314" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="314" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D314" s="15"/>
       <c r="E314" s="15"/>
     </row>
-    <row r="315" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="315" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D315" s="15"/>
       <c r="E315" s="15"/>
     </row>
-    <row r="316" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="316" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D316" s="15"/>
       <c r="E316" s="15"/>
     </row>
-    <row r="317" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="317" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D317" s="15"/>
       <c r="E317" s="15"/>
     </row>
-    <row r="318" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="318" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D318" s="15"/>
       <c r="E318" s="15"/>
     </row>
-    <row r="319" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="319" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D319" s="15"/>
       <c r="E319" s="15"/>
     </row>
-    <row r="320" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="320" spans="4:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D320" s="15"/>
       <c r="E320" s="15"/>
     </row>
-    <row r="321" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="321" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D321" s="15"/>
       <c r="E321" s="15"/>
     </row>
-    <row r="322" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="322" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D322" s="15"/>
       <c r="E322" s="15"/>
     </row>
-    <row r="323" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="323" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D323" s="15"/>
     </row>
-    <row r="324" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="324" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D324" s="15" t="str">
         <f>$C$7&amp;"3."</f>
         <v>7.5.3.</v>
@@ -6272,16 +6246,16 @@
         <v>19</v>
       </c>
     </row>
-    <row r="325" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="325" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D325" s="15"/>
       <c r="E325" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="326" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="326" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D326" s="15"/>
     </row>
-    <row r="327" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="327" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D327" s="15"/>
       <c r="E327" s="23"/>
       <c r="F327" s="24"/>
@@ -6317,7 +6291,7 @@
       <c r="AF327" s="43"/>
       <c r="AG327" s="43"/>
     </row>
-    <row r="328" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="328" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D328" s="15"/>
       <c r="E328" s="26"/>
       <c r="F328" s="27"/>
@@ -6355,7 +6329,7 @@
       <c r="AF328" s="46"/>
       <c r="AG328" s="46"/>
     </row>
-    <row r="329" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="329" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D329" s="15"/>
       <c r="E329" s="75" t="s">
         <v>143</v>
@@ -6397,7 +6371,7 @@
       <c r="AF329" s="57"/>
       <c r="AG329" s="58"/>
     </row>
-    <row r="330" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="330" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D330" s="15"/>
       <c r="E330" s="76"/>
       <c r="F330" s="76"/>
@@ -6433,7 +6407,7 @@
       <c r="AF330" s="60"/>
       <c r="AG330" s="61"/>
     </row>
-    <row r="331" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="331" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D331" s="15"/>
       <c r="E331" s="76"/>
       <c r="F331" s="76"/>
@@ -6469,7 +6443,7 @@
       <c r="AF331" s="60"/>
       <c r="AG331" s="61"/>
     </row>
-    <row r="332" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="332" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D332" s="15"/>
       <c r="E332" s="77"/>
       <c r="F332" s="77"/>
@@ -6505,7 +6479,7 @@
       <c r="AF332" s="63"/>
       <c r="AG332" s="64"/>
     </row>
-    <row r="333" spans="4:33" ht="29.45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="333" spans="4:33" ht="29.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D333" s="15"/>
       <c r="E333" s="54" t="s">
         <v>77</v>
@@ -6545,7 +6519,7 @@
       <c r="AF333" s="50"/>
       <c r="AG333" s="50"/>
     </row>
-    <row r="334" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="334" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D334" s="15"/>
       <c r="E334" s="54" t="s">
         <v>80</v>
@@ -6585,7 +6559,7 @@
       <c r="AF334" s="50"/>
       <c r="AG334" s="50"/>
     </row>
-    <row r="335" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="335" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D335" s="15"/>
       <c r="E335" s="75" t="s">
         <v>83</v>
@@ -6625,7 +6599,7 @@
       <c r="AF335" s="48"/>
       <c r="AG335" s="49"/>
     </row>
-    <row r="336" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="336" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D336" s="15"/>
       <c r="E336" s="76"/>
       <c r="F336" s="76"/>
@@ -6659,7 +6633,7 @@
       <c r="AF336" s="48"/>
       <c r="AG336" s="49"/>
     </row>
-    <row r="337" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="337" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D337" s="15"/>
       <c r="E337" s="77"/>
       <c r="F337" s="77"/>
@@ -6693,446 +6667,446 @@
       <c r="AF337" s="48"/>
       <c r="AG337" s="49"/>
     </row>
-    <row r="338" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="338" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D338" s="15"/>
     </row>
-    <row r="339" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="339" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D339" s="15"/>
     </row>
-    <row r="340" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="340" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D340" s="15"/>
     </row>
-    <row r="341" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" spans="4:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="78">
     <mergeCell ref="J18:M18"/>
